--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -1966,10 +1966,10 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>30.032</v>
+        <v>30.224</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>4.858</v>
+        <v>4.895</v>
       </c>
       <c r="D3" s="15" t="inlineStr"/>
       <c r="E3" s="15" t="n">
@@ -1999,14 +1999,14 @@
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>0.514</v>
+        <v>0.503</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>0.5</v>
+        <v>0.501</v>
       </c>
       <c r="D4" s="15" t="inlineStr"/>
       <c r="E4" s="15" t="n">
-        <v>-0.024</v>
+        <v>0.012</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>1</v>
@@ -2034,17 +2034,17 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>3.082</v>
+        <v>3.111</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>0.891</v>
+        <v>0.945</v>
       </c>
       <c r="D5" s="15" t="inlineStr"/>
       <c r="E5" s="15" t="n">
-        <v>0.036</v>
+        <v>0.024</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>-0.064</v>
+        <v>0.029</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>1</v>
@@ -2071,17 +2071,17 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>3.082</v>
+        <v>3.111</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>0.891</v>
+        <v>0.945</v>
       </c>
       <c r="D6" s="15" t="inlineStr"/>
       <c r="E6" s="15" t="n">
-        <v>0.036</v>
+        <v>0.024</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>-0.064</v>
+        <v>0.029</v>
       </c>
       <c r="G6" s="15" t="n">
         <v>1</v>
@@ -2110,23 +2110,23 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>8.1</v>
+        <v>8.367000000000001</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>5.157</v>
+        <v>5.029</v>
       </c>
       <c r="D7" s="15" t="inlineStr"/>
       <c r="E7" s="15" t="n">
-        <v>0.926</v>
+        <v>0.925</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>-0.016</v>
+        <v>0.051</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0.013</v>
+        <v>0.023</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>0.013</v>
+        <v>0.023</v>
       </c>
       <c r="I7" s="15" t="n">
         <v>1</v>
@@ -2151,26 +2151,26 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>2.635</v>
+        <v>4.38</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>2.389</v>
+        <v>2.379</v>
       </c>
       <c r="D8" s="15" t="inlineStr"/>
       <c r="E8" s="15" t="n">
-        <v>-0.042</v>
+        <v>0.016</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0.005</v>
+        <v>-0.068</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.052</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.052</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-0.045</v>
+        <v>-0.015</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>1</v>
@@ -2194,29 +2194,29 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>3.377</v>
+        <v>3.343</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>1.088</v>
+        <v>1.047</v>
       </c>
       <c r="D9" s="15" t="inlineStr"/>
       <c r="E9" s="15" t="n">
-        <v>-0.053</v>
+        <v>-0.05</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>-0.033</v>
+        <v>0.04</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0.032</v>
+        <v>0.043</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>0.032</v>
+        <v>0.043</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-0.039</v>
+        <v>-0.018</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>-0.056</v>
+        <v>0.006</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>1</v>
@@ -2239,34 +2239,34 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>3.202</v>
+        <v>3.982</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.727</v>
+        <v>0.867</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0.91</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>-0.024</v>
+        <v>-0.042</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>-0.061</v>
+        <v>0.04</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>-0.043</v>
+        <v>0.012</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-0.043</v>
+        <v>0.012</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-0.02</v>
+        <v>-0.075</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>0.053</v>
+        <v>0.11</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.031</v>
       </c>
       <c r="L10" s="15" t="n">
         <v>1</v>
@@ -2288,37 +2288,37 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>3.585</v>
+        <v>5.007</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0.62</v>
+        <v>0.804</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>0.93</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>0.064</v>
+        <v>0.1</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>-0.037</v>
+        <v>-0.035</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.011</v>
+        <v>0.053</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>0.011</v>
+        <v>0.053</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.055</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>-0.055</v>
+        <v>-0.016</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>-0.047</v>
+        <v>0.016</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>0.032</v>
+        <v>-0.061</v>
       </c>
       <c r="M11" s="15" t="n">
         <v>1</v>
@@ -2339,40 +2339,40 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>2.82</v>
+        <v>3.562</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.715</v>
+        <v>0.923</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>0.054</v>
+        <v>-0.022</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0.029</v>
+        <v>0.037</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>-0.021</v>
+        <v>0.006</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-0.021</v>
+        <v>0.006</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>0.059</v>
+        <v>-0.017</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>-0.064</v>
+        <v>-0.02</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>0.06</v>
+        <v>-0.039</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>0.008</v>
+        <v>-0.026</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.026</v>
       </c>
       <c r="N12" s="15" t="n">
         <v>1</v>
@@ -2392,43 +2392,43 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>3.019</v>
+        <v>4.502</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.627</v>
+        <v>0.951</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>0.84</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>-0.001</v>
+        <v>0.016</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0.052</v>
+        <v>0.037</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0.018</v>
+        <v>0.055</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>0.018</v>
+        <v>0.055</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-0.025</v>
+        <v>0.017</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>-0.02</v>
+        <v>-0.061</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>-0.034</v>
+        <v>-0.045</v>
       </c>
       <c r="L13" s="15" t="n">
-        <v>-0.037</v>
+        <v>0.029</v>
       </c>
       <c r="M13" s="15" t="n">
-        <v>0.029</v>
+        <v>-0.106</v>
       </c>
       <c r="N13" s="15" t="n">
-        <v>0.05</v>
+        <v>-0.073</v>
       </c>
       <c r="O13" s="15" t="n">
         <v>1</v>
@@ -2447,46 +2447,46 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>3.054</v>
+        <v>4.235</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>1.034</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>0.88</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>-0.003</v>
+        <v>0.053</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>-0.018</v>
+        <v>-0.079</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0.016</v>
+        <v>0.011</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>0.016</v>
+        <v>0.011</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>0.006</v>
+        <v>0.046</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>-0.04</v>
+        <v>-0.061</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>0.037</v>
+        <v>0.007</v>
       </c>
       <c r="L14" s="15" t="n">
-        <v>-0.373</v>
+        <v>-0.351</v>
       </c>
       <c r="M14" s="15" t="n">
-        <v>0.497</v>
+        <v>0.405</v>
       </c>
       <c r="N14" s="15" t="n">
-        <v>0.043</v>
+        <v>-0.024</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>0.023</v>
+        <v>-0.054</v>
       </c>
       <c r="P14" s="15" t="n">
         <v>1</v>
@@ -2504,49 +2504,49 @@
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>2.273</v>
+        <v>2.978</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>0.878</v>
+        <v>1.048</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>0.87</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>-0.123</v>
+        <v>-0.052</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>-0.029</v>
+        <v>-0.082</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-0.029</v>
+        <v>-0.082</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-0.132</v>
+        <v>-0.055</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>0.008</v>
+        <v>0.063</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>-0.044</v>
+        <v>0.005</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>0.533</v>
+        <v>0.539</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.347</v>
+        <v>-0.379</v>
       </c>
       <c r="N15" s="15" t="n">
-        <v>-0.025</v>
+        <v>-0.006</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.066</v>
+        <v>0.016</v>
       </c>
       <c r="P15" s="15" t="n">
-        <v>-0.386</v>
+        <v>-0.28</v>
       </c>
       <c r="Q15" s="15" t="n">
         <v>1</v>
@@ -2563,52 +2563,52 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>3.435</v>
+        <v>4.549</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>0.365</v>
+        <v>0.462</v>
       </c>
       <c r="D16" s="15" t="n">
         <v>0.9</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>-0.077</v>
+        <v>-0.01</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>0.035</v>
+        <v>-0.052</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>-0.066</v>
+        <v>-0.103</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-0.066</v>
+        <v>-0.103</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-0.101</v>
+        <v>-0.02</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>-0.001</v>
+        <v>-0.045</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>0.059</v>
+        <v>0.032</v>
       </c>
       <c r="L16" s="15" t="n">
-        <v>0.051</v>
+        <v>-0.017</v>
       </c>
       <c r="M16" s="15" t="n">
-        <v>-0.076</v>
+        <v>0.065</v>
       </c>
       <c r="N16" s="15" t="n">
-        <v>-0.063</v>
+        <v>-0.105</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>-0.059</v>
+        <v>0.003</v>
       </c>
       <c r="P16" s="15" t="n">
-        <v>-0.056</v>
+        <v>0.052</v>
       </c>
       <c r="Q16" s="15" t="n">
-        <v>0.016</v>
+        <v>-0.079</v>
       </c>
       <c r="R16" s="15" t="n">
         <v>1</v>
@@ -2624,55 +2624,55 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>3.366</v>
+        <v>4.275</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>0.958</v>
+        <v>0.646</v>
       </c>
       <c r="D17" s="15" t="n">
         <v>0.9</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>0.038</v>
+        <v>0.017</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>-0.032</v>
+        <v>-0.035</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>0.043</v>
+        <v>0.027</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>0.043</v>
+        <v>0.027</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>0.048</v>
+        <v>0.03</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.057</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>-0.005</v>
+        <v>0.002</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>-0.434</v>
+        <v>-0.481</v>
       </c>
       <c r="M17" s="15" t="n">
-        <v>0.425</v>
+        <v>0.379</v>
       </c>
       <c r="N17" s="15" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.007</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>0.026</v>
+        <v>-0.048</v>
       </c>
       <c r="P17" s="15" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.671</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>-0.715</v>
+        <v>-0.602</v>
       </c>
       <c r="R17" s="15" t="n">
-        <v>-0.051</v>
+        <v>0.065</v>
       </c>
       <c r="S17" s="15" t="n">
         <v>1</v>
@@ -2687,58 +2687,58 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>3.481</v>
+        <v>4.311</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>0.902</v>
+        <v>0.828</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>0.92</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>0.035</v>
+        <v>0.001</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>-0.011</v>
+        <v>0.057</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>0.029</v>
+        <v>0.081</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>0.029</v>
+        <v>0.081</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>0.025</v>
+        <v>0.034</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>-0.049</v>
+        <v>-0.131</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>0.039</v>
+        <v>-0.041</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>-0.319</v>
+        <v>-0.264</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>0.323</v>
+        <v>0.178</v>
       </c>
       <c r="N18" s="15" t="n">
-        <v>0.019</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>-0.051</v>
+        <v>-0.019</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0.402</v>
+        <v>0.362</v>
       </c>
       <c r="Q18" s="15" t="n">
-        <v>-0.398</v>
+        <v>-0.226</v>
       </c>
       <c r="R18" s="15" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.044</v>
       </c>
       <c r="S18" s="15" t="n">
-        <v>0.371</v>
+        <v>0.299</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>1</v>
@@ -2752,61 +2752,61 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>2.109</v>
+        <v>2.424</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>0.766</v>
+        <v>1.096</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>0.89</v>
       </c>
       <c r="E19" s="15" t="n">
+        <v>-0.048</v>
+      </c>
+      <c r="F19" s="15" t="n">
         <v>-0.029</v>
       </c>
-      <c r="F19" s="15" t="n">
-        <v>0.032</v>
-      </c>
       <c r="G19" s="15" t="n">
-        <v>-0.082</v>
+        <v>-0.143</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-0.082</v>
+        <v>-0.143</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-0.034</v>
+        <v>-0.068</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>0.065</v>
+        <v>0.092</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.041</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>0.284</v>
+        <v>0.24</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>-0.311</v>
+        <v>-0.214</v>
       </c>
       <c r="N19" s="15" t="n">
-        <v>-0.018</v>
+        <v>0.012</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>-0.068</v>
+        <v>-0.028</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>-0.37</v>
+        <v>-0.281</v>
       </c>
       <c r="Q19" s="15" t="n">
-        <v>0.39</v>
+        <v>0.354</v>
       </c>
       <c r="R19" s="15" t="n">
-        <v>0.048</v>
+        <v>0.002</v>
       </c>
       <c r="S19" s="15" t="n">
-        <v>-0.338</v>
+        <v>-0.307</v>
       </c>
       <c r="T19" s="15" t="n">
-        <v>-0.757</v>
+        <v>-0.551</v>
       </c>
       <c r="U19" s="15" t="n">
         <v>1</v>

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -1697,7 +1697,7 @@
       </c>
       <c r="H3" s="15" t="inlineStr">
         <is>
-          <t>Two-factor model retained: distinct OCBS / CWBS dimensions</t>
+          <t>Focal model</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="H4" s="15" t="inlineStr">
         <is>
-          <t>Single-factor model rejected: substantially worse fit</t>
+          <t>Worse fit</t>
         </is>
       </c>
     </row>

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -1422,22 +1422,22 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>286.4</v>
+        <v>609.2</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>254</v>
+        <v>539</v>
       </c>
       <c r="D3" s="15" t="n">
-        <v>0.078</v>
+        <v>0.018</v>
       </c>
       <c r="E3" s="15" t="n">
-        <v>0.965</v>
+        <v>0.968</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>0.029</v>
+        <v>0.02</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>12450.3</v>
+        <v>12586.4</v>
       </c>
       <c r="H3" s="15" t="n"/>
       <c r="I3" s="15" t="n"/>
@@ -1449,22 +1449,22 @@
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>341.8</v>
+        <v>719.4</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>259</v>
+        <v>545</v>
       </c>
       <c r="D4" s="15" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>0.946</v>
+        <v>0.945</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>0.041</v>
+        <v>0.03</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>12515.7</v>
+        <v>12694.6</v>
       </c>
       <c r="H4" s="15" t="n"/>
       <c r="I4" s="15" t="n"/>
@@ -1476,22 +1476,22 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>412.6</v>
+        <v>875</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>264</v>
+        <v>550</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>0.918</v>
+        <v>0.916</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0.054</v>
+        <v>0.041</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>12604.2</v>
+        <v>12848.2</v>
       </c>
       <c r="H5" s="15" t="n"/>
       <c r="I5" s="15" t="n"/>
@@ -1503,22 +1503,22 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>489.1</v>
+        <v>1051.6</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>268</v>
+        <v>554</v>
       </c>
       <c r="D6" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>0.892</v>
+        <v>0.881</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0.064</v>
+        <v>0.05</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>12692.9</v>
+        <v>13022.8</v>
       </c>
       <c r="H6" s="15" t="n"/>
       <c r="I6" s="15" t="n"/>
@@ -1530,22 +1530,22 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>568.2</v>
+        <v>1226.5</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>271</v>
+        <v>557</v>
       </c>
       <c r="D7" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>0.864</v>
+        <v>0.846</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0.073</v>
+        <v>0.058</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>12781.5</v>
+        <v>13195.7</v>
       </c>
       <c r="H7" s="15" t="n"/>
       <c r="I7" s="15" t="n"/>
@@ -1557,22 +1557,22 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>646.3</v>
+        <v>1397.5</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>273</v>
+        <v>559</v>
       </c>
       <c r="D8" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>0.835</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0.082</v>
+        <v>0.064</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>12867.1</v>
+        <v>13364.7</v>
       </c>
       <c r="H8" s="15" t="n"/>
       <c r="I8" s="15" t="n"/>
@@ -1584,22 +1584,22 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>812.7</v>
+        <v>1736</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>274</v>
+        <v>560</v>
       </c>
       <c r="D9" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>0.768</v>
+        <v>0.741</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.103</v>
+        <v>0.075</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>13042.9</v>
+        <v>13701.2</v>
       </c>
     </row>
   </sheetData>
@@ -1966,10 +1966,10 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>30.224</v>
+        <v>30.237</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>4.895</v>
+        <v>5.003</v>
       </c>
       <c r="D3" s="15" t="inlineStr"/>
       <c r="E3" s="15" t="n">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="D4" s="15" t="inlineStr"/>
       <c r="E4" s="15" t="n">
-        <v>0.012</v>
+        <v>-0.03</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>1</v>
@@ -2034,17 +2034,17 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>3.111</v>
+        <v>3.147</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>0.945</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="D5" s="15" t="inlineStr"/>
       <c r="E5" s="15" t="n">
-        <v>0.024</v>
+        <v>0.051</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0.029</v>
+        <v>0.021</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>1</v>
@@ -2071,17 +2071,17 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>3.111</v>
+        <v>3.147</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>0.945</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="D6" s="15" t="inlineStr"/>
       <c r="E6" s="15" t="n">
-        <v>0.024</v>
+        <v>0.051</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0.029</v>
+        <v>0.021</v>
       </c>
       <c r="G6" s="15" t="n">
         <v>1</v>
@@ -2110,23 +2110,23 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>8.367000000000001</v>
+        <v>8.387</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>5.029</v>
+        <v>5.127</v>
       </c>
       <c r="D7" s="15" t="inlineStr"/>
       <c r="E7" s="15" t="n">
-        <v>0.925</v>
+        <v>0.928</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0.051</v>
+        <v>0.001</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0.023</v>
+        <v>0.046</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>0.023</v>
+        <v>0.046</v>
       </c>
       <c r="I7" s="15" t="n">
         <v>1</v>
@@ -2151,26 +2151,26 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>4.38</v>
+        <v>4.378</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>2.379</v>
+        <v>2.383</v>
       </c>
       <c r="D8" s="15" t="inlineStr"/>
       <c r="E8" s="15" t="n">
-        <v>0.016</v>
+        <v>0.019</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>-0.068</v>
+        <v>-0.051</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.052</v>
+        <v>0.033</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>0.052</v>
+        <v>0.033</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-0.015</v>
+        <v>-0.026</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>1</v>
@@ -2194,29 +2194,29 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>3.343</v>
+        <v>3.376</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>1.047</v>
+        <v>1.072</v>
       </c>
       <c r="D9" s="15" t="inlineStr"/>
       <c r="E9" s="15" t="n">
-        <v>-0.05</v>
+        <v>-0.037</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.04</v>
+        <v>0.039</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0.043</v>
+        <v>-0.002</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>0.043</v>
+        <v>-0.002</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-0.018</v>
+        <v>0.004</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>0.006</v>
+        <v>-0.021</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>1</v>
@@ -2239,34 +2239,34 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>3.982</v>
+        <v>3.969</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.867</v>
+        <v>0.855</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0.91</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>-0.042</v>
+        <v>-0.048</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0.04</v>
+        <v>0.055</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.012</v>
+        <v>0.038</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>0.012</v>
+        <v>0.038</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-0.075</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>0.11</v>
+        <v>0.116</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>-0.031</v>
+        <v>-0.036</v>
       </c>
       <c r="L10" s="15" t="n">
         <v>1</v>
@@ -2288,37 +2288,37 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>5.007</v>
+        <v>4.979</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0.804</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>0.93</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>0.1</v>
+        <v>0.134</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>-0.035</v>
+        <v>-0.001</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.053</v>
+        <v>0.029</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>0.053</v>
+        <v>0.029</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>0.055</v>
+        <v>0.102</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>-0.016</v>
+        <v>0.01</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>0.016</v>
+        <v>0.02</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>-0.061</v>
+        <v>-0.112</v>
       </c>
       <c r="M11" s="15" t="n">
         <v>1</v>
@@ -2339,40 +2339,40 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>3.562</v>
+        <v>3.579</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.923</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>-0.022</v>
+        <v>-0.061</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0.037</v>
+        <v>0.073</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0.006</v>
+        <v>0.022</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>0.006</v>
+        <v>0.022</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-0.017</v>
+        <v>-0.053</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>-0.02</v>
+        <v>-0.052</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>-0.039</v>
+        <v>-0.019</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>-0.026</v>
+        <v>-0.075</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>-0.026</v>
+        <v>-0.04</v>
       </c>
       <c r="N12" s="15" t="n">
         <v>1</v>
@@ -2392,43 +2392,43 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>4.502</v>
+        <v>4.498</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.951</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>0.84</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>0.016</v>
+        <v>0.007</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0.037</v>
+        <v>-0.01</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0.055</v>
+        <v>0.011</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>0.055</v>
+        <v>0.011</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>0.017</v>
+        <v>0.006</v>
       </c>
       <c r="J13" s="15" t="n">
         <v>-0.061</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>-0.045</v>
+        <v>-0.08</v>
       </c>
       <c r="L13" s="15" t="n">
-        <v>0.029</v>
+        <v>0.032</v>
       </c>
       <c r="M13" s="15" t="n">
-        <v>-0.106</v>
+        <v>-0.089</v>
       </c>
       <c r="N13" s="15" t="n">
-        <v>-0.073</v>
+        <v>-0.022</v>
       </c>
       <c r="O13" s="15" t="n">
         <v>1</v>
@@ -2447,46 +2447,46 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>4.235</v>
+        <v>4.503</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>0.8179999999999999</v>
+        <v>1.164</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>0.88</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>0.053</v>
+        <v>0.092</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>-0.079</v>
+        <v>-0.063</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0.011</v>
+        <v>-0.049</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>0.011</v>
+        <v>-0.049</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>0.046</v>
+        <v>0.089</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>-0.061</v>
+        <v>-0.048</v>
       </c>
       <c r="K14" s="15" t="n">
         <v>0.007</v>
       </c>
       <c r="L14" s="15" t="n">
-        <v>-0.351</v>
+        <v>-0.426</v>
       </c>
       <c r="M14" s="15" t="n">
-        <v>0.405</v>
+        <v>0.449</v>
       </c>
       <c r="N14" s="15" t="n">
-        <v>-0.024</v>
+        <v>0.014</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>-0.054</v>
+        <v>-0.049</v>
       </c>
       <c r="P14" s="15" t="n">
         <v>1</v>
@@ -2504,49 +2504,49 @@
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>2.978</v>
+        <v>2.999</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>1.048</v>
+        <v>1.127</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>0.87</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>-0.052</v>
+        <v>-0.063</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>-0.01</v>
+        <v>0.011</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>-0.082</v>
+        <v>-0.036</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-0.082</v>
+        <v>-0.036</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-0.055</v>
+        <v>-0.074</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>0.063</v>
+        <v>0.039</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>0.539</v>
+        <v>0.544</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.379</v>
+        <v>-0.414</v>
       </c>
       <c r="N15" s="15" t="n">
-        <v>-0.006</v>
+        <v>0.01</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>0.016</v>
+        <v>0.012</v>
       </c>
       <c r="P15" s="15" t="n">
-        <v>-0.28</v>
+        <v>-0.328</v>
       </c>
       <c r="Q15" s="15" t="n">
         <v>1</v>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>4.549</v>
+        <v>4.552</v>
       </c>
       <c r="C16" s="15" t="n">
         <v>0.462</v>
@@ -2572,43 +2572,43 @@
         <v>0.9</v>
       </c>
       <c r="E16" s="15" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>-0.065</v>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>-0.126</v>
+      </c>
+      <c r="H16" s="15" t="n">
+        <v>-0.126</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>-0.034</v>
+      </c>
+      <c r="J16" s="15" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="K16" s="15" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="L16" s="15" t="n">
+        <v>-0.022</v>
+      </c>
+      <c r="M16" s="15" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="N16" s="15" t="n">
+        <v>-0.134</v>
+      </c>
+      <c r="O16" s="15" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F16" s="15" t="n">
-        <v>-0.052</v>
-      </c>
-      <c r="G16" s="15" t="n">
-        <v>-0.103</v>
-      </c>
-      <c r="H16" s="15" t="n">
-        <v>-0.103</v>
-      </c>
-      <c r="I16" s="15" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="J16" s="15" t="n">
-        <v>-0.045</v>
-      </c>
-      <c r="K16" s="15" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="L16" s="15" t="n">
-        <v>-0.017</v>
-      </c>
-      <c r="M16" s="15" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="N16" s="15" t="n">
-        <v>-0.105</v>
-      </c>
-      <c r="O16" s="15" t="n">
-        <v>0.003</v>
-      </c>
       <c r="P16" s="15" t="n">
-        <v>0.052</v>
+        <v>0.037</v>
       </c>
       <c r="Q16" s="15" t="n">
-        <v>-0.079</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="R16" s="15" t="n">
         <v>1</v>
@@ -2624,55 +2624,55 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>4.275</v>
+        <v>4.741</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>0.646</v>
+        <v>1.001</v>
       </c>
       <c r="D17" s="15" t="n">
         <v>0.9</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>0.017</v>
+        <v>0.067</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>-0.035</v>
+        <v>-0.024</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>0.027</v>
+        <v>0.044</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>0.027</v>
+        <v>0.044</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>0.03</v>
+        <v>0.062</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>-0.057</v>
+        <v>-0.068</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>0.002</v>
+        <v>-0.042</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>-0.481</v>
+        <v>-0.485</v>
       </c>
       <c r="M17" s="15" t="n">
-        <v>0.379</v>
+        <v>0.412</v>
       </c>
       <c r="N17" s="15" t="n">
-        <v>-0.007</v>
+        <v>-0.037</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>-0.048</v>
+        <v>0.013</v>
       </c>
       <c r="P17" s="15" t="n">
-        <v>0.671</v>
+        <v>0.635</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>-0.602</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="R17" s="15" t="n">
-        <v>0.065</v>
+        <v>0.062</v>
       </c>
       <c r="S17" s="15" t="n">
         <v>1</v>
@@ -2687,58 +2687,58 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>4.311</v>
+        <v>4.838</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>0.828</v>
+        <v>1.151</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>0.92</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>0.001</v>
+        <v>0.052</v>
       </c>
       <c r="F18" s="15" t="n">
+        <v>-0.034</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="J18" s="15" t="n">
+        <v>-0.126</v>
+      </c>
+      <c r="K18" s="15" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="L18" s="15" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="M18" s="15" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="N18" s="15" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="O18" s="15" t="n">
         <v>0.057</v>
       </c>
-      <c r="G18" s="15" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="H18" s="15" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="I18" s="15" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="J18" s="15" t="n">
-        <v>-0.131</v>
-      </c>
-      <c r="K18" s="15" t="n">
-        <v>-0.041</v>
-      </c>
-      <c r="L18" s="15" t="n">
-        <v>-0.264</v>
-      </c>
-      <c r="M18" s="15" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="N18" s="15" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="O18" s="15" t="n">
-        <v>-0.019</v>
-      </c>
       <c r="P18" s="15" t="n">
-        <v>0.362</v>
+        <v>0.367</v>
       </c>
       <c r="Q18" s="15" t="n">
-        <v>-0.226</v>
+        <v>-0.253</v>
       </c>
       <c r="R18" s="15" t="n">
-        <v>-0.044</v>
+        <v>-0.056</v>
       </c>
       <c r="S18" s="15" t="n">
-        <v>0.299</v>
+        <v>0.273</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>1</v>
@@ -2752,61 +2752,61 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>2.424</v>
+        <v>2.456</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>1.096</v>
+        <v>1.029</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>0.89</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>-0.048</v>
+        <v>-0.081</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>-0.029</v>
+        <v>-0.006</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>-0.143</v>
+        <v>-0.09</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-0.143</v>
+        <v>-0.09</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-0.068</v>
+        <v>-0.107</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>0.092</v>
+        <v>0.08</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>0.041</v>
+        <v>-0.013</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>0.24</v>
+        <v>0.277</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>-0.214</v>
+        <v>-0.248</v>
       </c>
       <c r="N19" s="15" t="n">
-        <v>0.012</v>
+        <v>-0.014</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>-0.028</v>
+        <v>0.007</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>-0.281</v>
+        <v>-0.325</v>
       </c>
       <c r="Q19" s="15" t="n">
-        <v>0.354</v>
+        <v>0.334</v>
       </c>
       <c r="R19" s="15" t="n">
-        <v>0.002</v>
+        <v>0.055</v>
       </c>
       <c r="S19" s="15" t="n">
-        <v>-0.307</v>
+        <v>-0.338</v>
       </c>
       <c r="T19" s="15" t="n">
-        <v>-0.551</v>
+        <v>-0.533</v>
       </c>
       <c r="U19" s="15" t="n">
         <v>1</v>

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -1966,10 +1966,10 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>30.237</v>
+        <v>30.861</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>5.003</v>
+        <v>4.52</v>
       </c>
       <c r="D3" s="15" t="inlineStr"/>
       <c r="E3" s="15" t="n">
@@ -1999,14 +1999,14 @@
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>0.503</v>
+        <v>0.544</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>0.501</v>
+        <v>0.499</v>
       </c>
       <c r="D4" s="15" t="inlineStr"/>
       <c r="E4" s="15" t="n">
-        <v>-0.03</v>
+        <v>0.021</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>1</v>
@@ -2034,17 +2034,17 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>3.147</v>
+        <v>3.107</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="D5" s="15" t="inlineStr"/>
       <c r="E5" s="15" t="n">
-        <v>0.051</v>
+        <v>-0.001</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0.021</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>1</v>
@@ -2071,20 +2071,20 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>3.147</v>
+        <v>2.567</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>0.9340000000000001</v>
+        <v>1.135</v>
       </c>
       <c r="D6" s="15" t="inlineStr"/>
       <c r="E6" s="15" t="n">
-        <v>0.051</v>
+        <v>-0.068</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0.021</v>
+        <v>-0.047</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>1</v>
+        <v>-0.01</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>1</v>
@@ -2110,23 +2110,23 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>8.387</v>
+        <v>9.036</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>5.127</v>
+        <v>4.828</v>
       </c>
       <c r="D7" s="15" t="inlineStr"/>
       <c r="E7" s="15" t="n">
-        <v>0.928</v>
+        <v>0.898</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0.001</v>
+        <v>-0.004</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0.046</v>
+        <v>-0.004</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>0.046</v>
+        <v>-0.029</v>
       </c>
       <c r="I7" s="15" t="n">
         <v>1</v>
@@ -2151,26 +2151,26 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>4.378</v>
+        <v>4.336</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>2.383</v>
+        <v>2.329</v>
       </c>
       <c r="D8" s="15" t="inlineStr"/>
       <c r="E8" s="15" t="n">
-        <v>0.019</v>
+        <v>0.011</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>-0.051</v>
+        <v>-0.058</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.033</v>
+        <v>-0.024</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>0.033</v>
+        <v>0.027</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-0.026</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>1</v>
@@ -2194,29 +2194,29 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>3.376</v>
+        <v>3.306</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>1.072</v>
+        <v>1.056</v>
       </c>
       <c r="D9" s="15" t="inlineStr"/>
       <c r="E9" s="15" t="n">
-        <v>-0.037</v>
+        <v>-0.048</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.039</v>
+        <v>0.059</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>-0.002</v>
+        <v>-0.021</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-0.002</v>
+        <v>-0.091</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>0.004</v>
+        <v>-0.033</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>-0.021</v>
+        <v>-0.048</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>1</v>
@@ -2239,34 +2239,34 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>3.969</v>
+        <v>4.037</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.855</v>
+        <v>0.614</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0.91</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>-0.048</v>
+        <v>-0.015</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0.055</v>
+        <v>0.008</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.038</v>
+        <v>0.074</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>0.038</v>
+        <v>-0.081</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.066</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>0.116</v>
+        <v>0.073</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>-0.036</v>
+        <v>0.068</v>
       </c>
       <c r="L10" s="15" t="n">
         <v>1</v>
@@ -2288,37 +2288,37 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>4.979</v>
+        <v>5.016</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.577</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>0.93</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>0.134</v>
+        <v>-0.023</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>-0.001</v>
+        <v>0.015</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.029</v>
+        <v>0.048</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>0.029</v>
+        <v>-0.051</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>0.102</v>
+        <v>0.023</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>0.01</v>
+        <v>-0.061</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>0.02</v>
+        <v>-0.041</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>-0.112</v>
+        <v>-0.119</v>
       </c>
       <c r="M11" s="15" t="n">
         <v>1</v>
@@ -2339,40 +2339,40 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>3.579</v>
+        <v>3.448</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.911</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>-0.061</v>
+        <v>0.01</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0.073</v>
+        <v>-0.064</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0.022</v>
+        <v>-0.036</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>0.022</v>
+        <v>0.082</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-0.053</v>
+        <v>0.076</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>-0.052</v>
+        <v>0.105</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>-0.019</v>
+        <v>-0.021</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>-0.075</v>
+        <v>0.037</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>-0.04</v>
+        <v>-0.015</v>
       </c>
       <c r="N12" s="15" t="n">
         <v>1</v>
@@ -2392,43 +2392,43 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>4.498</v>
+        <v>4.583</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>0.84</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>0.007</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>-0.01</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0.011</v>
+        <v>-0.053</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>0.011</v>
+        <v>0.067</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>0.006</v>
+        <v>-0.049</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>-0.061</v>
+        <v>-0.052</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>-0.08</v>
+        <v>-0.081</v>
       </c>
       <c r="L13" s="15" t="n">
-        <v>0.032</v>
+        <v>-0.033</v>
       </c>
       <c r="M13" s="15" t="n">
-        <v>-0.089</v>
+        <v>-0.043</v>
       </c>
       <c r="N13" s="15" t="n">
-        <v>-0.022</v>
+        <v>-0.005</v>
       </c>
       <c r="O13" s="15" t="n">
         <v>1</v>
@@ -2447,46 +2447,46 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>4.503</v>
+        <v>4.51</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>1.164</v>
+        <v>1.215</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>0.88</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>0.092</v>
+        <v>-0.012</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>-0.063</v>
+        <v>-0.041</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>-0.049</v>
+        <v>-0.051</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-0.049</v>
+        <v>0.055</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>0.089</v>
+        <v>0.045</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>-0.048</v>
+        <v>-0.067</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>0.007</v>
+        <v>-0.074</v>
       </c>
       <c r="L14" s="15" t="n">
-        <v>-0.426</v>
+        <v>-0.345</v>
       </c>
       <c r="M14" s="15" t="n">
-        <v>0.449</v>
+        <v>0.347</v>
       </c>
       <c r="N14" s="15" t="n">
-        <v>0.014</v>
+        <v>-0.034</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>-0.049</v>
+        <v>-0.043</v>
       </c>
       <c r="P14" s="15" t="n">
         <v>1</v>
@@ -2504,49 +2504,49 @@
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>2.999</v>
+        <v>2.996</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>1.127</v>
+        <v>1.142</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>0.87</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>-0.063</v>
+        <v>-0.023</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0.011</v>
+        <v>0.001</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>-0.036</v>
+        <v>-0.005</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-0.036</v>
+        <v>-0.082</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-0.074</v>
+        <v>-0.076</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>0.039</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>0.006</v>
+        <v>0.073</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>0.544</v>
+        <v>0.305</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.414</v>
+        <v>-0.27</v>
       </c>
       <c r="N15" s="15" t="n">
-        <v>0.01</v>
+        <v>0.061</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>0.012</v>
+        <v>-0.101</v>
       </c>
       <c r="P15" s="15" t="n">
-        <v>-0.328</v>
+        <v>-0.449</v>
       </c>
       <c r="Q15" s="15" t="n">
         <v>1</v>
@@ -2563,52 +2563,52 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>4.552</v>
+        <v>4.576</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>0.462</v>
+        <v>0.464</v>
       </c>
       <c r="D16" s="15" t="n">
         <v>0.9</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>-0.024</v>
+        <v>-0.06</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>-0.065</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>-0.126</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-0.126</v>
+        <v>0.01</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-0.034</v>
+        <v>-0.081</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>-0.018</v>
+        <v>0.04</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>0.052</v>
+        <v>-0.001</v>
       </c>
       <c r="L16" s="15" t="n">
-        <v>-0.022</v>
+        <v>0.015</v>
       </c>
       <c r="M16" s="15" t="n">
-        <v>0.046</v>
+        <v>0.062</v>
       </c>
       <c r="N16" s="15" t="n">
         <v>-0.134</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>-0.01</v>
+        <v>0.037</v>
       </c>
       <c r="P16" s="15" t="n">
-        <v>0.037</v>
+        <v>0.081</v>
       </c>
       <c r="Q16" s="15" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.078</v>
       </c>
       <c r="R16" s="15" t="n">
         <v>1</v>
@@ -2624,55 +2624,55 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>4.741</v>
+        <v>4.753</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>1.001</v>
+        <v>1.029</v>
       </c>
       <c r="D17" s="15" t="n">
         <v>0.9</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>0.067</v>
+        <v>-0.018</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>-0.024</v>
+        <v>0.048</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>0.044</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>0.044</v>
+        <v>0.075</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>0.062</v>
+        <v>0.05</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>-0.068</v>
+        <v>-0.021</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>-0.042</v>
+        <v>-0.065</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>-0.485</v>
+        <v>-0.275</v>
       </c>
       <c r="M17" s="15" t="n">
-        <v>0.412</v>
+        <v>0.223</v>
       </c>
       <c r="N17" s="15" t="n">
-        <v>-0.037</v>
+        <v>-0.016</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>0.013</v>
+        <v>0.02</v>
       </c>
       <c r="P17" s="15" t="n">
-        <v>0.635</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.675</v>
       </c>
       <c r="R17" s="15" t="n">
-        <v>0.062</v>
+        <v>0.09</v>
       </c>
       <c r="S17" s="15" t="n">
         <v>1</v>
@@ -2687,58 +2687,58 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>4.838</v>
+        <v>4.744</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>1.151</v>
+        <v>1.155</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>0.92</v>
       </c>
       <c r="E18" s="15" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>-0.079</v>
+      </c>
+      <c r="H18" s="15" t="n">
         <v>0.052</v>
       </c>
-      <c r="F18" s="15" t="n">
-        <v>-0.034</v>
-      </c>
-      <c r="G18" s="15" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="H18" s="15" t="n">
-        <v>0.066</v>
-      </c>
       <c r="I18" s="15" t="n">
-        <v>0.076</v>
+        <v>-0.021</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>-0.126</v>
+        <v>-0.064</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>-0.006</v>
+        <v>-0.024</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>-0.24</v>
+        <v>-0.425</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>0.217</v>
+        <v>0.359</v>
       </c>
       <c r="N18" s="15" t="n">
-        <v>0.119</v>
+        <v>-0.054</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>0.057</v>
+        <v>0.014</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0.367</v>
+        <v>0.363</v>
       </c>
       <c r="Q18" s="15" t="n">
-        <v>-0.253</v>
+        <v>-0.407</v>
       </c>
       <c r="R18" s="15" t="n">
-        <v>-0.056</v>
+        <v>0.067</v>
       </c>
       <c r="S18" s="15" t="n">
-        <v>0.273</v>
+        <v>0.31</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>1</v>
@@ -2752,61 +2752,61 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>2.456</v>
+        <v>2.579</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>1.029</v>
+        <v>1.122</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>0.89</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>-0.081</v>
+        <v>0.007</v>
       </c>
       <c r="F19" s="15" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="G19" s="15" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>-0.089</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>-0.032</v>
+      </c>
+      <c r="J19" s="15" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="K19" s="15" t="n">
+        <v>-0.017</v>
+      </c>
+      <c r="L19" s="15" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="M19" s="15" t="n">
+        <v>-0.193</v>
+      </c>
+      <c r="N19" s="15" t="n">
         <v>-0.006</v>
       </c>
-      <c r="G19" s="15" t="n">
+      <c r="O19" s="15" t="n">
+        <v>-0.056</v>
+      </c>
+      <c r="P19" s="15" t="n">
+        <v>-0.339</v>
+      </c>
+      <c r="Q19" s="15" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="R19" s="15" t="n">
         <v>-0.09</v>
       </c>
-      <c r="H19" s="15" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="I19" s="15" t="n">
-        <v>-0.107</v>
-      </c>
-      <c r="J19" s="15" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="K19" s="15" t="n">
-        <v>-0.013</v>
-      </c>
-      <c r="L19" s="15" t="n">
-        <v>0.277</v>
-      </c>
-      <c r="M19" s="15" t="n">
-        <v>-0.248</v>
-      </c>
-      <c r="N19" s="15" t="n">
-        <v>-0.014</v>
-      </c>
-      <c r="O19" s="15" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="P19" s="15" t="n">
-        <v>-0.325</v>
-      </c>
-      <c r="Q19" s="15" t="n">
-        <v>0.334</v>
-      </c>
-      <c r="R19" s="15" t="n">
-        <v>0.055</v>
-      </c>
       <c r="S19" s="15" t="n">
-        <v>-0.338</v>
+        <v>-0.344</v>
       </c>
       <c r="T19" s="15" t="n">
-        <v>-0.533</v>
+        <v>-0.471</v>
       </c>
       <c r="U19" s="15" t="n">
         <v>1</v>

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -1966,10 +1966,10 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>30.861</v>
+        <v>30.712</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>4.52</v>
+        <v>4.72</v>
       </c>
       <c r="D3" s="15" t="inlineStr"/>
       <c r="E3" s="15" t="n">
@@ -1999,14 +1999,14 @@
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>0.544</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>0.499</v>
+        <v>0.497</v>
       </c>
       <c r="D4" s="15" t="inlineStr"/>
       <c r="E4" s="15" t="n">
-        <v>0.021</v>
+        <v>0.029</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>1</v>
@@ -2034,17 +2034,17 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>3.107</v>
+        <v>3.079</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="D5" s="15" t="inlineStr"/>
       <c r="E5" s="15" t="n">
-        <v>-0.001</v>
+        <v>-0</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.046</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>1</v>
@@ -2071,20 +2071,20 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>2.567</v>
+        <v>2.555</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>1.135</v>
+        <v>1.132</v>
       </c>
       <c r="D6" s="15" t="inlineStr"/>
       <c r="E6" s="15" t="n">
-        <v>-0.068</v>
+        <v>-0.045</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>-0.047</v>
+        <v>-0.034</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>-0.01</v>
+        <v>-0.017</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>1</v>
@@ -2110,23 +2110,23 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>9.036</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>4.828</v>
+        <v>4.991</v>
       </c>
       <c r="D7" s="15" t="inlineStr"/>
       <c r="E7" s="15" t="n">
-        <v>0.898</v>
+        <v>0.909</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>-0.004</v>
+        <v>0.014</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>-0.004</v>
+        <v>-0.003</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-0.029</v>
+        <v>-0.017</v>
       </c>
       <c r="I7" s="15" t="n">
         <v>1</v>
@@ -2151,26 +2151,26 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>4.336</v>
+        <v>3.737</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>2.329</v>
+        <v>2.285</v>
       </c>
       <c r="D8" s="15" t="inlineStr"/>
       <c r="E8" s="15" t="n">
-        <v>0.011</v>
+        <v>0.352</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>-0.058</v>
+        <v>0.016</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>-0.024</v>
+        <v>-0.059</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>0.027</v>
+        <v>0.025</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.341</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>1</v>
@@ -2194,29 +2194,29 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>3.306</v>
+        <v>3.247</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>1.056</v>
+        <v>1.081</v>
       </c>
       <c r="D9" s="15" t="inlineStr"/>
       <c r="E9" s="15" t="n">
-        <v>-0.048</v>
+        <v>-0.008</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.059</v>
+        <v>0.095</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>-0.021</v>
+        <v>-0.043</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-0.091</v>
+        <v>-0.05</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-0.033</v>
+        <v>0.008</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>-0.048</v>
+        <v>-0.026</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>1</v>
@@ -2239,34 +2239,34 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>4.037</v>
+        <v>4</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.614</v>
+        <v>0.612</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0.91</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>-0.015</v>
+        <v>0.012</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0.008</v>
+        <v>0.029</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.074</v>
+        <v>0.047</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-0.081</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-0.066</v>
+        <v>-0.025</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>0.073</v>
+        <v>0.036</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>0.068</v>
+        <v>-0.011</v>
       </c>
       <c r="L10" s="15" t="n">
         <v>1</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>5.016</v>
+        <v>5.023</v>
       </c>
       <c r="C11" s="15" t="n">
         <v>0.577</v>
@@ -2297,25 +2297,25 @@
         <v>0.93</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>-0.023</v>
+        <v>-0.024</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0.015</v>
+        <v>-0.02</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.048</v>
+        <v>0.05</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-0.051</v>
+        <v>-0.079</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>0.023</v>
+        <v>0.026</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>-0.061</v>
+        <v>-0.08</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>-0.041</v>
+        <v>-0.046</v>
       </c>
       <c r="L11" s="15" t="n">
         <v>-0.119</v>
@@ -2339,40 +2339,40 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>3.448</v>
+        <v>3.467</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.911</v>
+        <v>0.899</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>0.01</v>
+        <v>-0.016</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>-0.064</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>-0.036</v>
+        <v>-0.028</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>0.082</v>
+        <v>0.057</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>0.076</v>
+        <v>0.037</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>0.105</v>
+        <v>0.081</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>-0.021</v>
+        <v>-0.039</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>0.037</v>
+        <v>0.055</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>-0.015</v>
+        <v>0.042</v>
       </c>
       <c r="N12" s="15" t="n">
         <v>1</v>
@@ -2392,43 +2392,43 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>4.583</v>
+        <v>4.562</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.89</v>
+        <v>0.902</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>0.84</v>
       </c>
       <c r="E13" s="15" t="n">
+        <v>-0.079</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>-0.118</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>-0.045</v>
+      </c>
+      <c r="J13" s="15" t="n">
         <v>-0.07199999999999999</v>
       </c>
-      <c r="F13" s="15" t="n">
-        <v>-0.08699999999999999</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>-0.053</v>
-      </c>
-      <c r="H13" s="15" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="I13" s="15" t="n">
+      <c r="K13" s="15" t="n">
+        <v>-0.089</v>
+      </c>
+      <c r="L13" s="15" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="M13" s="15" t="n">
         <v>-0.049</v>
       </c>
-      <c r="J13" s="15" t="n">
-        <v>-0.052</v>
-      </c>
-      <c r="K13" s="15" t="n">
-        <v>-0.081</v>
-      </c>
-      <c r="L13" s="15" t="n">
-        <v>-0.033</v>
-      </c>
-      <c r="M13" s="15" t="n">
-        <v>-0.043</v>
-      </c>
       <c r="N13" s="15" t="n">
-        <v>-0.005</v>
+        <v>0.018</v>
       </c>
       <c r="O13" s="15" t="n">
         <v>1</v>
@@ -2447,46 +2447,46 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>4.51</v>
+        <v>4.526</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>1.215</v>
+        <v>1.178</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>0.88</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>-0.012</v>
+        <v>-0.017</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>-0.041</v>
+        <v>-0.016</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>-0.051</v>
+        <v>-0.035</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>0.055</v>
+        <v>0.024</v>
       </c>
       <c r="I14" s="15" t="n">
         <v>0.045</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>-0.067</v>
+        <v>-0.1</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>-0.074</v>
+        <v>-0.041</v>
       </c>
       <c r="L14" s="15" t="n">
-        <v>-0.345</v>
+        <v>-0.34</v>
       </c>
       <c r="M14" s="15" t="n">
-        <v>0.347</v>
+        <v>0.33</v>
       </c>
       <c r="N14" s="15" t="n">
-        <v>-0.034</v>
+        <v>-0.022</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>-0.043</v>
+        <v>-0.045</v>
       </c>
       <c r="P14" s="15" t="n">
         <v>1</v>
@@ -2504,49 +2504,49 @@
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>2.996</v>
+        <v>2.956</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>1.142</v>
+        <v>1.111</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>0.87</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>-0.023</v>
+        <v>-0.012</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0.001</v>
+        <v>-0.013</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>-0.005</v>
+        <v>0.006</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-0.082</v>
+        <v>-0.044</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-0.076</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.058</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>0.073</v>
+        <v>0.059</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>0.305</v>
+        <v>0.299</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.27</v>
+        <v>-0.268</v>
       </c>
       <c r="N15" s="15" t="n">
-        <v>0.061</v>
+        <v>0.028</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.101</v>
+        <v>-0.117</v>
       </c>
       <c r="P15" s="15" t="n">
-        <v>-0.449</v>
+        <v>-0.45</v>
       </c>
       <c r="Q15" s="15" t="n">
         <v>1</v>
@@ -2563,52 +2563,52 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>4.576</v>
+        <v>4.587</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>0.464</v>
+        <v>0.459</v>
       </c>
       <c r="D16" s="15" t="n">
         <v>0.9</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>-0.06</v>
+        <v>-0.039</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.111</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>0.01</v>
+        <v>0.023</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-0.081</v>
+        <v>-0.044</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>0.04</v>
+        <v>0.002</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>-0.001</v>
+        <v>-0.016</v>
       </c>
       <c r="L16" s="15" t="n">
-        <v>0.015</v>
+        <v>0.031</v>
       </c>
       <c r="M16" s="15" t="n">
-        <v>0.062</v>
+        <v>-0.004</v>
       </c>
       <c r="N16" s="15" t="n">
-        <v>-0.134</v>
+        <v>-0.129</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>0.037</v>
+        <v>0.014</v>
       </c>
       <c r="P16" s="15" t="n">
-        <v>0.081</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="Q16" s="15" t="n">
-        <v>-0.078</v>
+        <v>-0.083</v>
       </c>
       <c r="R16" s="15" t="n">
         <v>1</v>
@@ -2624,55 +2624,55 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>4.753</v>
+        <v>4.742</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>1.029</v>
+        <v>1.019</v>
       </c>
       <c r="D17" s="15" t="n">
         <v>0.9</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>-0.018</v>
+        <v>-0.036</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>0.048</v>
+        <v>0</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.019</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>0.075</v>
+        <v>0.026</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>0.05</v>
+        <v>-0.001</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>-0.021</v>
+        <v>-0.041</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>-0.065</v>
+        <v>-0.052</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>-0.275</v>
+        <v>-0.204</v>
       </c>
       <c r="M17" s="15" t="n">
-        <v>0.223</v>
+        <v>0.233</v>
       </c>
       <c r="N17" s="15" t="n">
-        <v>-0.016</v>
+        <v>-0.007</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>0.02</v>
+        <v>0.026</v>
       </c>
       <c r="P17" s="15" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.675</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>-0.675</v>
+        <v>-0.653</v>
       </c>
       <c r="R17" s="15" t="n">
-        <v>0.09</v>
+        <v>0.064</v>
       </c>
       <c r="S17" s="15" t="n">
         <v>1</v>
@@ -2687,58 +2687,58 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>4.744</v>
+        <v>4.625</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>1.155</v>
+        <v>1.152</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>0.92</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>-0.06</v>
+        <v>-0.013</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>-0.079</v>
+        <v>-0.028</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>0.052</v>
+        <v>-0.025</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-0.021</v>
+        <v>0.011</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>-0.064</v>
+        <v>-0.008</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>-0.024</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>-0.425</v>
+        <v>-0.401</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>0.359</v>
+        <v>0.367</v>
       </c>
       <c r="N18" s="15" t="n">
-        <v>-0.054</v>
+        <v>-0.056</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>0.014</v>
+        <v>0.02</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0.363</v>
+        <v>0.353</v>
       </c>
       <c r="Q18" s="15" t="n">
-        <v>-0.407</v>
+        <v>-0.343</v>
       </c>
       <c r="R18" s="15" t="n">
-        <v>0.067</v>
+        <v>0.082</v>
       </c>
       <c r="S18" s="15" t="n">
-        <v>0.31</v>
+        <v>0.268</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>1</v>
@@ -2752,61 +2752,61 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>2.579</v>
+        <v>2.596</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>1.122</v>
+        <v>1.057</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>0.89</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>0.007</v>
+        <v>0.024</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>0.024</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="G19" s="15" t="n">
         <v>0.082</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-0.089</v>
+        <v>-0.012</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-0.032</v>
+        <v>-0.02</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>0.027</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>-0.017</v>
+        <v>-0.007</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>0.342</v>
+        <v>0.455</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>-0.193</v>
+        <v>-0.43</v>
       </c>
       <c r="N19" s="15" t="n">
-        <v>-0.006</v>
+        <v>0.054</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>-0.056</v>
+        <v>-0.065</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>-0.339</v>
+        <v>-0.43</v>
       </c>
       <c r="Q19" s="15" t="n">
-        <v>0.338</v>
+        <v>0.35</v>
       </c>
       <c r="R19" s="15" t="n">
-        <v>-0.09</v>
+        <v>-0.031</v>
       </c>
       <c r="S19" s="15" t="n">
-        <v>-0.344</v>
+        <v>-0.302</v>
       </c>
       <c r="T19" s="15" t="n">
-        <v>-0.471</v>
+        <v>-0.416</v>
       </c>
       <c r="U19" s="15" t="n">
         <v>1</v>

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -1966,10 +1966,10 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>30.712</v>
+        <v>30.773</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>4.72</v>
+        <v>4.638</v>
       </c>
       <c r="D3" s="15" t="inlineStr"/>
       <c r="E3" s="15" t="n">
@@ -1999,14 +1999,14 @@
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="C4" s="15" t="n">
         <v>0.497</v>
       </c>
       <c r="D4" s="15" t="inlineStr"/>
       <c r="E4" s="15" t="n">
-        <v>0.029</v>
+        <v>0.024</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>1</v>
@@ -2034,17 +2034,17 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>3.079</v>
+        <v>3.104</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="D5" s="15" t="inlineStr"/>
       <c r="E5" s="15" t="n">
-        <v>-0</v>
+        <v>-0.005</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>-0.046</v>
+        <v>-0.054</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>1</v>
@@ -2071,20 +2071,20 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>2.555</v>
+        <v>2.577</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>1.132</v>
+        <v>1.145</v>
       </c>
       <c r="D6" s="15" t="inlineStr"/>
       <c r="E6" s="15" t="n">
-        <v>-0.045</v>
+        <v>-0.038</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>-0.034</v>
+        <v>-0.041</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>-0.017</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>1</v>
@@ -2110,23 +2110,23 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>8.970000000000001</v>
+        <v>8.989000000000001</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>4.991</v>
+        <v>4.945</v>
       </c>
       <c r="D7" s="15" t="inlineStr"/>
       <c r="E7" s="15" t="n">
-        <v>0.909</v>
+        <v>0.906</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0.014</v>
+        <v>0.003</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>-0.003</v>
+        <v>-0.02</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-0.017</v>
+        <v>-0.016</v>
       </c>
       <c r="I7" s="15" t="n">
         <v>1</v>
@@ -2151,26 +2151,26 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>3.737</v>
+        <v>3.766</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>2.285</v>
+        <v>2.268</v>
       </c>
       <c r="D8" s="15" t="inlineStr"/>
       <c r="E8" s="15" t="n">
-        <v>0.352</v>
+        <v>0.345</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0.016</v>
+        <v>0.021</v>
       </c>
       <c r="G8" s="15" t="n">
         <v>-0.059</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>0.025</v>
+        <v>0.016</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>0.341</v>
+        <v>0.336</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>1</v>
@@ -2194,29 +2194,29 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>3.247</v>
+        <v>3.271</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>1.081</v>
+        <v>1.074</v>
       </c>
       <c r="D9" s="15" t="inlineStr"/>
       <c r="E9" s="15" t="n">
-        <v>-0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.095</v>
+        <v>0.104</v>
       </c>
       <c r="G9" s="15" t="n">
+        <v>-0.057</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>-0.07099999999999999</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J9" s="15" t="n">
         <v>-0.043</v>
-      </c>
-      <c r="H9" s="15" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="I9" s="15" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="J9" s="15" t="n">
-        <v>-0.026</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>1</v>
@@ -2239,34 +2239,34 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>4</v>
+        <v>4.062</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.612</v>
+        <v>0.62</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0.91</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>0.012</v>
+        <v>0.022</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0.029</v>
+        <v>0.031</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.047</v>
+        <v>0.06</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.083</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-0.025</v>
+        <v>-0.028</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>0.036</v>
+        <v>0.021</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>-0.011</v>
+        <v>0.05</v>
       </c>
       <c r="L10" s="15" t="n">
         <v>1</v>
@@ -2288,37 +2288,37 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>5.023</v>
+        <v>5.046</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0.577</v>
+        <v>0.573</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>0.93</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>-0.024</v>
+        <v>-0.058</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>-0.02</v>
+        <v>-0.035</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.05</v>
+        <v>0.065</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-0.079</v>
+        <v>-0.089</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>0.026</v>
+        <v>-0.014</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>-0.08</v>
+        <v>-0.083</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>-0.046</v>
+        <v>-0.051</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>-0.119</v>
+        <v>-0.149</v>
       </c>
       <c r="M11" s="15" t="n">
         <v>1</v>
@@ -2339,40 +2339,40 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>3.467</v>
+        <v>3.469</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.899</v>
+        <v>0.918</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>-0.016</v>
+        <v>-0.007</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.047</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>-0.028</v>
+        <v>-0.036</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>0.057</v>
+        <v>0.054</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>0.037</v>
+        <v>0.061</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>0.081</v>
+        <v>0.08</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>-0.039</v>
+        <v>-0.076</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>0.055</v>
+        <v>0.023</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>0.042</v>
+        <v>0.04</v>
       </c>
       <c r="N12" s="15" t="n">
         <v>1</v>
@@ -2392,43 +2392,43 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>4.562</v>
+        <v>4.601</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.902</v>
+        <v>0.893</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>0.84</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>-0.079</v>
+        <v>-0.077</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>-0.118</v>
+        <v>-0.077</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>-0.049</v>
+        <v>-0.073</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>0.055</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-0.045</v>
+        <v>-0.054</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.083</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>-0.089</v>
+        <v>-0.059</v>
       </c>
       <c r="L13" s="15" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="M13" s="15" t="n">
-        <v>-0.049</v>
+        <v>-0.093</v>
       </c>
       <c r="N13" s="15" t="n">
-        <v>0.018</v>
+        <v>0.004</v>
       </c>
       <c r="O13" s="15" t="n">
         <v>1</v>
@@ -2447,46 +2447,46 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>4.526</v>
+        <v>4.515</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>1.178</v>
+        <v>1.195</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>0.88</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>-0.017</v>
+        <v>-0.001</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>-0.016</v>
+        <v>-0.029</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>-0.035</v>
+        <v>-0.043</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>0.024</v>
+        <v>0.04</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>0.045</v>
+        <v>0.056</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>-0.1</v>
+        <v>-0.064</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>-0.041</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="L14" s="15" t="n">
         <v>-0.34</v>
       </c>
       <c r="M14" s="15" t="n">
-        <v>0.33</v>
+        <v>0.357</v>
       </c>
       <c r="N14" s="15" t="n">
-        <v>-0.022</v>
+        <v>-0.013</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>-0.045</v>
+        <v>-0.044</v>
       </c>
       <c r="P14" s="15" t="n">
         <v>1</v>
@@ -2504,49 +2504,49 @@
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>2.956</v>
+        <v>2.996</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>1.111</v>
+        <v>1.138</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>0.87</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>-0.012</v>
+        <v>-0.008</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>-0.013</v>
+        <v>0.006</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0.006</v>
+        <v>-0.014</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>-0.044</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.063</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>0.058</v>
+        <v>0.037</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>0.059</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>0.299</v>
+        <v>0.312</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.268</v>
+        <v>-0.262</v>
       </c>
       <c r="N15" s="15" t="n">
-        <v>0.028</v>
+        <v>0.022</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.117</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="P15" s="15" t="n">
-        <v>-0.45</v>
+        <v>-0.446</v>
       </c>
       <c r="Q15" s="15" t="n">
         <v>1</v>
@@ -2563,52 +2563,52 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>4.587</v>
+        <v>4.591</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>0.459</v>
+        <v>0.47</v>
       </c>
       <c r="D16" s="15" t="n">
         <v>0.9</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>-0.039</v>
+        <v>-0.025</v>
       </c>
       <c r="F16" s="15" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>-0.057</v>
+      </c>
+      <c r="H16" s="15" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>-0.038</v>
+      </c>
+      <c r="J16" s="15" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="G16" s="15" t="n">
-        <v>-0.111</v>
-      </c>
-      <c r="H16" s="15" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="I16" s="15" t="n">
-        <v>-0.044</v>
-      </c>
-      <c r="J16" s="15" t="n">
-        <v>0.002</v>
-      </c>
       <c r="K16" s="15" t="n">
-        <v>-0.016</v>
+        <v>-0.045</v>
       </c>
       <c r="L16" s="15" t="n">
-        <v>0.031</v>
+        <v>0.041</v>
       </c>
       <c r="M16" s="15" t="n">
-        <v>-0.004</v>
+        <v>0.036</v>
       </c>
       <c r="N16" s="15" t="n">
-        <v>-0.129</v>
+        <v>-0.148</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>0.014</v>
+        <v>0.038</v>
       </c>
       <c r="P16" s="15" t="n">
         <v>0.06900000000000001</v>
       </c>
       <c r="Q16" s="15" t="n">
-        <v>-0.083</v>
+        <v>-0.037</v>
       </c>
       <c r="R16" s="15" t="n">
         <v>1</v>
@@ -2624,55 +2624,55 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>4.742</v>
+        <v>4.766</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>1.019</v>
+        <v>1.016</v>
       </c>
       <c r="D17" s="15" t="n">
         <v>0.9</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>-0.036</v>
+        <v>-0.047</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>0</v>
+        <v>-0.024</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>0.019</v>
+        <v>-0.062</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>0.026</v>
+        <v>0.039</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-0.001</v>
+        <v>0.015</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>-0.041</v>
+        <v>-0.033</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>-0.052</v>
+        <v>-0.099</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>-0.204</v>
+        <v>-0.325</v>
       </c>
       <c r="M17" s="15" t="n">
-        <v>0.233</v>
+        <v>0.311</v>
       </c>
       <c r="N17" s="15" t="n">
-        <v>-0.007</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>0.026</v>
+        <v>0.059</v>
       </c>
       <c r="P17" s="15" t="n">
-        <v>0.675</v>
+        <v>0.711</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>-0.653</v>
+        <v>-0.66</v>
       </c>
       <c r="R17" s="15" t="n">
-        <v>0.064</v>
+        <v>0.035</v>
       </c>
       <c r="S17" s="15" t="n">
         <v>1</v>
@@ -2687,58 +2687,58 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>4.625</v>
+        <v>4.859</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>1.152</v>
+        <v>1.346</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>0.92</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>-0.013</v>
+        <v>-0.077</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>-0.04</v>
+        <v>-0.003</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>-0.028</v>
+        <v>-0.094</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-0.025</v>
+        <v>-0.029</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>0.011</v>
+        <v>-0.056</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>-0.008</v>
+        <v>-0.03</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.032</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>-0.401</v>
+        <v>-0.435</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>0.367</v>
+        <v>0.52</v>
       </c>
       <c r="N18" s="15" t="n">
-        <v>-0.056</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>0.02</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0.353</v>
+        <v>0.427</v>
       </c>
       <c r="Q18" s="15" t="n">
-        <v>-0.343</v>
+        <v>-0.375</v>
       </c>
       <c r="R18" s="15" t="n">
-        <v>0.082</v>
+        <v>0.095</v>
       </c>
       <c r="S18" s="15" t="n">
-        <v>0.268</v>
+        <v>0.405</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>1</v>
@@ -2752,61 +2752,61 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>2.596</v>
+        <v>2.386</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>1.057</v>
+        <v>1.024</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>0.89</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>0.024</v>
+        <v>-0.056</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>0.082</v>
+        <v>0.034</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-0.012</v>
+        <v>0</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-0.02</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.056</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>-0.007</v>
+        <v>-0.005</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>0.455</v>
+        <v>0.504</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>-0.43</v>
+        <v>-0.436</v>
       </c>
       <c r="N19" s="15" t="n">
-        <v>0.054</v>
+        <v>-0.013</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>-0.065</v>
+        <v>0.021</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>-0.43</v>
+        <v>-0.381</v>
       </c>
       <c r="Q19" s="15" t="n">
-        <v>0.35</v>
+        <v>0.325</v>
       </c>
       <c r="R19" s="15" t="n">
-        <v>-0.031</v>
+        <v>0.001</v>
       </c>
       <c r="S19" s="15" t="n">
-        <v>-0.302</v>
+        <v>-0.348</v>
       </c>
       <c r="T19" s="15" t="n">
-        <v>-0.416</v>
+        <v>-0.592</v>
       </c>
       <c r="U19" s="15" t="n">
         <v>1</v>

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -1678,22 +1678,22 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>76.40000000000001</v>
+        <v>51.6</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="D3" s="15" t="n">
-        <v>0.992</v>
+        <v>0.984</v>
       </c>
       <c r="E3" s="15" t="n">
-        <v>0.989</v>
+        <v>0.979</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>0.018</v>
+        <v>0.024</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>0.041</v>
+        <v>0.03</v>
       </c>
       <c r="H3" s="15" t="inlineStr">
         <is>
@@ -1708,22 +1708,22 @@
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>162.3</v>
+        <v>132</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="D4" s="15" t="n">
-        <v>0.831</v>
+        <v>0.836</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>0.794</v>
+        <v>0.795</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>0.108</v>
+        <v>0.094</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.093</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H4" s="15" t="inlineStr">
         <is>
@@ -3839,17 +3839,17 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>-0.024</v>
+        <v>-0.015</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>-0.044</v>
+        <v>-0.051</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>-0.02</v>
+        <v>-0.037</v>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>[-0.041, -0.001]</t>
+          <t>[-0.072, -0.002]</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
@@ -3865,17 +3865,17 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>-0.021</v>
+        <v>-0.013</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>-0.038</v>
+        <v>-0.045</v>
       </c>
       <c r="D17" s="15" t="n">
-        <v>-0.017</v>
+        <v>-0.032</v>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>[-0.036, -0.002]</t>
+          <t>[-0.064, -0.000]</t>
         </is>
       </c>
       <c r="F17" s="15" t="inlineStr">
@@ -3891,17 +3891,17 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
       <c r="D18" s="15" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.017</v>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>[-0.001, 0.020]</t>
+          <t>[-0.004, +0.038]</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
@@ -3917,17 +3917,17 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>0.038</v>
+        <v>0.04</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>0.064</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>0.026</v>
+        <v>0.046</v>
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>[0.005, 0.052]</t>
+          <t>[+0.005, +0.087]</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
@@ -3943,17 +3943,17 @@
         </is>
       </c>
       <c r="B20" s="15" t="n">
-        <v>0.033</v>
+        <v>0.034</v>
       </c>
       <c r="C20" s="15" t="n">
-        <v>0.056</v>
+        <v>0.074</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>0.023</v>
+        <v>0.04</v>
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>[0.003, 0.047]</t>
+          <t>[+0.003, +0.077]</t>
         </is>
       </c>
       <c r="F20" s="15" t="inlineStr">
@@ -3969,17 +3969,17 @@
         </is>
       </c>
       <c r="B21" s="15" t="n">
-        <v>-0.018</v>
+        <v>-0.019</v>
       </c>
       <c r="C21" s="15" t="n">
-        <v>-0.03</v>
+        <v>-0.041</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>-0.012</v>
+        <v>-0.022</v>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>[-0.026, 0.001]</t>
+          <t>[-0.047, +0.003]</t>
         </is>
       </c>
       <c r="F21" s="15" t="inlineStr">
@@ -4034,17 +4034,17 @@
         </is>
       </c>
       <c r="B24" s="15" t="n">
-        <v>-0.052</v>
+        <v>-0.04</v>
       </c>
       <c r="C24" s="15" t="n">
-        <v>-0.089</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="D24" s="15" t="n">
-        <v>-0.037</v>
+        <v>-0.044</v>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>[-0.072, -0.008]</t>
+          <t>[-0.084, -0.004]</t>
         </is>
       </c>
       <c r="F24" s="15" t="inlineStr">
@@ -4060,17 +4060,17 @@
         </is>
       </c>
       <c r="B25" s="15" t="n">
-        <v>-0.041</v>
+        <v>-0.031</v>
       </c>
       <c r="C25" s="15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.066</v>
       </c>
       <c r="D25" s="15" t="n">
-        <v>-0.029</v>
+        <v>-0.035</v>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>[-0.058, -0.004]</t>
+          <t>[-0.069, -0.001]</t>
         </is>
       </c>
       <c r="F25" s="15" t="inlineStr">
@@ -4086,17 +4086,17 @@
         </is>
       </c>
       <c r="B26" s="15" t="n">
-        <v>0.058</v>
+        <v>0.056</v>
       </c>
       <c r="C26" s="15" t="n">
-        <v>0.099</v>
+        <v>0.118</v>
       </c>
       <c r="D26" s="15" t="n">
-        <v>0.041</v>
+        <v>0.062</v>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>[0.011, 0.077]</t>
+          <t>[+0.010, +0.114]</t>
         </is>
       </c>
       <c r="F26" s="15" t="inlineStr">
@@ -4112,17 +4112,17 @@
         </is>
       </c>
       <c r="B27" s="15" t="n">
-        <v>0.024</v>
+        <v>0.015</v>
       </c>
       <c r="C27" s="15" t="n">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
       <c r="D27" s="15" t="n">
-        <v>0.017</v>
+        <v>0.027</v>
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>[-0.003, 0.038]</t>
+          <t>[-0.001, +0.055]</t>
         </is>
       </c>
       <c r="F27" s="15" t="inlineStr">
@@ -4138,17 +4138,17 @@
         </is>
       </c>
       <c r="B28" s="15" t="n">
-        <v>0.019</v>
+        <v>0.012</v>
       </c>
       <c r="C28" s="15" t="n">
         <v>0.033</v>
       </c>
       <c r="D28" s="15" t="n">
-        <v>0.014</v>
+        <v>0.021</v>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>[-0.002, 0.032]</t>
+          <t>[-0.003, +0.045]</t>
         </is>
       </c>
       <c r="F28" s="15" t="inlineStr">
@@ -4164,22 +4164,22 @@
         </is>
       </c>
       <c r="B29" s="15" t="n">
-        <v>-0.027</v>
+        <v>-0.022</v>
       </c>
       <c r="C29" s="15" t="n">
-        <v>-0.046</v>
+        <v>-0.059</v>
       </c>
       <c r="D29" s="15" t="n">
-        <v>-0.019</v>
+        <v>-0.037</v>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>[-0.041, 0.001]</t>
+          <t>[-0.072, -0.002]</t>
         </is>
       </c>
       <c r="F29" s="15" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4232,14 +4232,14 @@
         <v>-0.03</v>
       </c>
       <c r="C32" s="15" t="n">
-        <v>-0.034</v>
+        <v>-0.036</v>
       </c>
       <c r="D32" s="15" t="n">
-        <v>-0.004</v>
+        <v>-0.006</v>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>[-0.025, 0.018]</t>
+          <t>[-0.020, +0.008]</t>
         </is>
       </c>
       <c r="F32" s="15" t="inlineStr">
@@ -4258,14 +4258,14 @@
         <v>-0.026</v>
       </c>
       <c r="C33" s="15" t="n">
-        <v>-0.029</v>
+        <v>-0.031</v>
       </c>
       <c r="D33" s="15" t="n">
-        <v>-0.003</v>
+        <v>-0.005</v>
       </c>
       <c r="E33" s="15" t="inlineStr">
         <is>
-          <t>[-0.022, 0.016]</t>
+          <t>[-0.018, +0.008]</t>
         </is>
       </c>
       <c r="F33" s="15" t="inlineStr">
@@ -4281,17 +4281,17 @@
         </is>
       </c>
       <c r="B34" s="15" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
       <c r="C34" s="15" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="D34" s="15" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t>[-0.012, 0.017]</t>
+          <t>[-0.009, +0.015]</t>
         </is>
       </c>
       <c r="F34" s="15" t="inlineStr">
@@ -4307,17 +4307,17 @@
         </is>
       </c>
       <c r="B35" s="15" t="n">
-        <v>0.048</v>
+        <v>0.058</v>
       </c>
       <c r="C35" s="15" t="n">
-        <v>0.054</v>
+        <v>0.067</v>
       </c>
       <c r="D35" s="15" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="E35" s="15" t="inlineStr">
         <is>
-          <t>[-0.014, 0.026]</t>
+          <t>[-0.007, +0.023]</t>
         </is>
       </c>
       <c r="F35" s="15" t="inlineStr">
@@ -4333,17 +4333,17 @@
         </is>
       </c>
       <c r="B36" s="15" t="n">
-        <v>0.041</v>
+        <v>0.051</v>
       </c>
       <c r="C36" s="15" t="n">
-        <v>0.046</v>
+        <v>0.058</v>
       </c>
       <c r="D36" s="15" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>[-0.013, 0.024]</t>
+          <t>[-0.008, +0.022]</t>
         </is>
       </c>
       <c r="F36" s="15" t="inlineStr">
@@ -4359,17 +4359,17 @@
         </is>
       </c>
       <c r="B37" s="15" t="n">
-        <v>-0.022</v>
+        <v>-0.028</v>
       </c>
       <c r="C37" s="15" t="n">
-        <v>-0.025</v>
+        <v>-0.032</v>
       </c>
       <c r="D37" s="15" t="n">
-        <v>-0.003</v>
+        <v>-0.004</v>
       </c>
       <c r="E37" s="15" t="inlineStr">
         <is>
-          <t>[-0.020, 0.014]</t>
+          <t>[-0.017, +0.009]</t>
         </is>
       </c>
       <c r="F37" s="15" t="inlineStr">
@@ -4424,17 +4424,17 @@
         </is>
       </c>
       <c r="B40" s="15" t="n">
+        <v>-0.057</v>
+      </c>
+      <c r="C40" s="15" t="n">
         <v>-0.067</v>
       </c>
-      <c r="C40" s="15" t="n">
-        <v>-0.073</v>
-      </c>
       <c r="D40" s="15" t="n">
-        <v>-0.006</v>
+        <v>-0.01</v>
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
-          <t>[-0.028, 0.015]</t>
+          <t>[-0.027, +0.007]</t>
         </is>
       </c>
       <c r="F40" s="15" t="inlineStr">
@@ -4450,17 +4450,17 @@
         </is>
       </c>
       <c r="B41" s="15" t="n">
-        <v>-0.054</v>
+        <v>-0.045</v>
       </c>
       <c r="C41" s="15" t="n">
-        <v>-0.058</v>
+        <v>-0.052</v>
       </c>
       <c r="D41" s="15" t="n">
-        <v>-0.004</v>
+        <v>-0.007</v>
       </c>
       <c r="E41" s="15" t="inlineStr">
         <is>
-          <t>[-0.022, 0.014]</t>
+          <t>[-0.022, +0.008]</t>
         </is>
       </c>
       <c r="F41" s="15" t="inlineStr">
@@ -4476,17 +4476,17 @@
         </is>
       </c>
       <c r="B42" s="15" t="n">
-        <v>0.075</v>
+        <v>0.08</v>
       </c>
       <c r="C42" s="15" t="n">
-        <v>0.082</v>
+        <v>0.093</v>
       </c>
       <c r="D42" s="15" t="n">
-        <v>0.007</v>
+        <v>0.013</v>
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t>[-0.014, 0.029]</t>
+          <t>[-0.006, +0.032]</t>
         </is>
       </c>
       <c r="F42" s="15" t="inlineStr">
@@ -4502,17 +4502,17 @@
         </is>
       </c>
       <c r="B43" s="15" t="n">
-        <v>0.031</v>
+        <v>0.025</v>
       </c>
       <c r="C43" s="15" t="n">
-        <v>0.034</v>
+        <v>0.032</v>
       </c>
       <c r="D43" s="15" t="n">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="E43" s="15" t="inlineStr">
         <is>
-          <t>[-0.014, 0.020]</t>
+          <t>[-0.007, +0.023]</t>
         </is>
       </c>
       <c r="F43" s="15" t="inlineStr">
@@ -4528,17 +4528,17 @@
         </is>
       </c>
       <c r="B44" s="15" t="n">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="C44" s="15" t="n">
-        <v>0.027</v>
+        <v>0.026</v>
       </c>
       <c r="D44" s="15" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t>[-0.013, 0.018]</t>
+          <t>[-0.008, +0.020]</t>
         </is>
       </c>
       <c r="F44" s="15" t="inlineStr">
@@ -4557,14 +4557,14 @@
         <v>-0.035</v>
       </c>
       <c r="C45" s="15" t="n">
-        <v>-0.038</v>
+        <v>-0.046</v>
       </c>
       <c r="D45" s="15" t="n">
-        <v>-0.003</v>
+        <v>-0.011</v>
       </c>
       <c r="E45" s="15" t="inlineStr">
         <is>
-          <t>[-0.022, 0.015]</t>
+          <t>[-0.028, +0.006]</t>
         </is>
       </c>
       <c r="F45" s="15" t="inlineStr">

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -3582,14 +3582,14 @@
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>-0.078</v>
+        <v>0.078</v>
       </c>
       <c r="C4" s="15" t="n">
         <v>0.038</v>
       </c>
       <c r="D4" s="15" t="inlineStr">
         <is>
-          <t>[-0.152, -0.004]</t>
+          <t>[0.004, 0.152]</t>
         </is>
       </c>
       <c r="E4" s="15" t="inlineStr">
@@ -3605,14 +3605,14 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>0.098</v>
+        <v>-0.098</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>0.039</v>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>[0.022, 0.174]</t>
+          <t>[-0.174, -0.022]</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -3708,14 +3708,14 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>0.111</v>
+        <v>-0.111</v>
       </c>
       <c r="C10" s="15" t="n">
         <v>0.041</v>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>[0.031, 0.191]</t>
+          <t>[-0.191, -0.031]</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
@@ -3731,14 +3731,14 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>-0.067</v>
+        <v>0.067</v>
       </c>
       <c r="C11" s="15" t="n">
         <v>0.038</v>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>[-0.141, 0.007]</t>
+          <t>[-0.007, 0.141]</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -3839,17 +3839,17 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
+        <v>-0.051</v>
+      </c>
+      <c r="C16" s="15" t="n">
         <v>-0.015</v>
       </c>
-      <c r="C16" s="15" t="n">
-        <v>-0.051</v>
-      </c>
       <c r="D16" s="15" t="n">
-        <v>-0.037</v>
+        <v>0.037</v>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>[-0.072, -0.002]</t>
+          <t>[+0.002, +0.072]</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
@@ -3865,17 +3865,17 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
+        <v>-0.045</v>
+      </c>
+      <c r="C17" s="15" t="n">
         <v>-0.013</v>
       </c>
-      <c r="C17" s="15" t="n">
-        <v>-0.045</v>
-      </c>
       <c r="D17" s="15" t="n">
-        <v>-0.032</v>
+        <v>0.032</v>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>[-0.064, -0.000]</t>
+          <t>[+0.000, +0.064]</t>
         </is>
       </c>
       <c r="F17" s="15" t="inlineStr">
@@ -3891,17 +3891,17 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="C18" s="15" t="n">
         <v>0.007</v>
       </c>
-      <c r="C18" s="15" t="n">
-        <v>0.025</v>
-      </c>
       <c r="D18" s="15" t="n">
-        <v>0.017</v>
+        <v>-0.017</v>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>[-0.004, +0.038]</t>
+          <t>[-0.038, +0.004]</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
@@ -3917,17 +3917,17 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="C19" s="15" t="n">
         <v>0.04</v>
       </c>
-      <c r="C19" s="15" t="n">
-        <v>0.08500000000000001</v>
-      </c>
       <c r="D19" s="15" t="n">
-        <v>0.046</v>
+        <v>-0.046</v>
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>[+0.005, +0.087]</t>
+          <t>[-0.087, -0.005]</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
@@ -3943,17 +3943,17 @@
         </is>
       </c>
       <c r="B20" s="15" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="C20" s="15" t="n">
         <v>0.034</v>
       </c>
-      <c r="C20" s="15" t="n">
-        <v>0.074</v>
-      </c>
       <c r="D20" s="15" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>[+0.003, +0.077]</t>
+          <t>[-0.077, -0.003]</t>
         </is>
       </c>
       <c r="F20" s="15" t="inlineStr">
@@ -3969,17 +3969,17 @@
         </is>
       </c>
       <c r="B21" s="15" t="n">
+        <v>-0.041</v>
+      </c>
+      <c r="C21" s="15" t="n">
         <v>-0.019</v>
       </c>
-      <c r="C21" s="15" t="n">
-        <v>-0.041</v>
-      </c>
       <c r="D21" s="15" t="n">
-        <v>-0.022</v>
+        <v>0.022</v>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>[-0.047, +0.003]</t>
+          <t>[-0.003, +0.047]</t>
         </is>
       </c>
       <c r="F21" s="15" t="inlineStr">
@@ -4034,17 +4034,17 @@
         </is>
       </c>
       <c r="B24" s="15" t="n">
+        <v>-0.08400000000000001</v>
+      </c>
+      <c r="C24" s="15" t="n">
         <v>-0.04</v>
       </c>
-      <c r="C24" s="15" t="n">
-        <v>-0.08400000000000001</v>
-      </c>
       <c r="D24" s="15" t="n">
-        <v>-0.044</v>
+        <v>0.044</v>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>[-0.084, -0.004]</t>
+          <t>[+0.004, +0.084]</t>
         </is>
       </c>
       <c r="F24" s="15" t="inlineStr">
@@ -4060,17 +4060,17 @@
         </is>
       </c>
       <c r="B25" s="15" t="n">
+        <v>-0.066</v>
+      </c>
+      <c r="C25" s="15" t="n">
         <v>-0.031</v>
       </c>
-      <c r="C25" s="15" t="n">
-        <v>-0.066</v>
-      </c>
       <c r="D25" s="15" t="n">
-        <v>-0.035</v>
+        <v>0.035</v>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>[-0.069, -0.001]</t>
+          <t>[+0.001, +0.069]</t>
         </is>
       </c>
       <c r="F25" s="15" t="inlineStr">
@@ -4086,17 +4086,17 @@
         </is>
       </c>
       <c r="B26" s="15" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="C26" s="15" t="n">
         <v>0.056</v>
       </c>
-      <c r="C26" s="15" t="n">
-        <v>0.118</v>
-      </c>
       <c r="D26" s="15" t="n">
-        <v>0.062</v>
+        <v>-0.062</v>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>[+0.010, +0.114]</t>
+          <t>[-0.114, -0.010]</t>
         </is>
       </c>
       <c r="F26" s="15" t="inlineStr">
@@ -4112,17 +4112,17 @@
         </is>
       </c>
       <c r="B27" s="15" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="C27" s="15" t="n">
         <v>0.015</v>
       </c>
-      <c r="C27" s="15" t="n">
-        <v>0.042</v>
-      </c>
       <c r="D27" s="15" t="n">
-        <v>0.027</v>
+        <v>-0.027</v>
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>[-0.001, +0.055]</t>
+          <t>[-0.055, +0.001]</t>
         </is>
       </c>
       <c r="F27" s="15" t="inlineStr">
@@ -4138,17 +4138,17 @@
         </is>
       </c>
       <c r="B28" s="15" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="C28" s="15" t="n">
         <v>0.012</v>
       </c>
-      <c r="C28" s="15" t="n">
-        <v>0.033</v>
-      </c>
       <c r="D28" s="15" t="n">
-        <v>0.021</v>
+        <v>-0.021</v>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>[-0.003, +0.045]</t>
+          <t>[-0.045, +0.003]</t>
         </is>
       </c>
       <c r="F28" s="15" t="inlineStr">
@@ -4164,17 +4164,17 @@
         </is>
       </c>
       <c r="B29" s="15" t="n">
+        <v>-0.059</v>
+      </c>
+      <c r="C29" s="15" t="n">
         <v>-0.022</v>
       </c>
-      <c r="C29" s="15" t="n">
-        <v>-0.059</v>
-      </c>
       <c r="D29" s="15" t="n">
-        <v>-0.037</v>
+        <v>0.037</v>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>[-0.072, -0.002]</t>
+          <t>[+0.002, +0.072]</t>
         </is>
       </c>
       <c r="F29" s="15" t="inlineStr">

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -1454,8 +1454,10 @@
       <c r="C4" s="15" t="n">
         <v>545</v>
       </c>
-      <c r="D4" s="15" t="n">
-        <v>0</v>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>&lt;.001</t>
+        </is>
       </c>
       <c r="E4" s="15" t="n">
         <v>0.945</v>
@@ -1481,8 +1483,10 @@
       <c r="C5" s="15" t="n">
         <v>550</v>
       </c>
-      <c r="D5" s="15" t="n">
-        <v>0</v>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>&lt;.001</t>
+        </is>
       </c>
       <c r="E5" s="15" t="n">
         <v>0.916</v>
@@ -1508,8 +1512,10 @@
       <c r="C6" s="15" t="n">
         <v>554</v>
       </c>
-      <c r="D6" s="15" t="n">
-        <v>0</v>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>&lt;.001</t>
+        </is>
       </c>
       <c r="E6" s="15" t="n">
         <v>0.881</v>
@@ -1535,8 +1541,10 @@
       <c r="C7" s="15" t="n">
         <v>557</v>
       </c>
-      <c r="D7" s="15" t="n">
-        <v>0</v>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>&lt;.001</t>
+        </is>
       </c>
       <c r="E7" s="15" t="n">
         <v>0.846</v>
@@ -1562,8 +1570,10 @@
       <c r="C8" s="15" t="n">
         <v>559</v>
       </c>
-      <c r="D8" s="15" t="n">
-        <v>0</v>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>&lt;.001</t>
+        </is>
       </c>
       <c r="E8" s="15" t="n">
         <v>0.8110000000000001</v>
@@ -1589,8 +1599,10 @@
       <c r="C9" s="15" t="n">
         <v>560</v>
       </c>
-      <c r="D9" s="15" t="n">
-        <v>0</v>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>&lt;.001</t>
+        </is>
       </c>
       <c r="E9" s="15" t="n">
         <v>0.741</v>
@@ -1966,10 +1978,10 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>30.773</v>
+        <v>30.767</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>4.638</v>
+        <v>4.683</v>
       </c>
       <c r="D3" s="15" t="inlineStr"/>
       <c r="E3" s="15" t="n">
@@ -1999,14 +2011,14 @@
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.529</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>0.497</v>
+        <v>0.5</v>
       </c>
       <c r="D4" s="15" t="inlineStr"/>
       <c r="E4" s="15" t="n">
-        <v>0.024</v>
+        <v>0.037</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>1</v>
@@ -2034,17 +2046,17 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>3.104</v>
+        <v>3.107</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.922</v>
       </c>
       <c r="D5" s="15" t="inlineStr"/>
       <c r="E5" s="15" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>-0.054</v>
+        <v>-0.099</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>1</v>
@@ -2071,20 +2083,20 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>2.577</v>
+        <v>2.521</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>1.145</v>
+        <v>1.121</v>
       </c>
       <c r="D6" s="15" t="inlineStr"/>
       <c r="E6" s="15" t="n">
-        <v>-0.038</v>
+        <v>-0.032</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>-0.041</v>
+        <v>-0.075</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.011</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>1</v>
@@ -2110,23 +2122,23 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>8.989000000000001</v>
+        <v>9</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>4.945</v>
+        <v>4.967</v>
       </c>
       <c r="D7" s="15" t="inlineStr"/>
       <c r="E7" s="15" t="n">
-        <v>0.906</v>
+        <v>0.907</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0.003</v>
+        <v>0.026</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-0.016</v>
+        <v>-0.004</v>
       </c>
       <c r="I7" s="15" t="n">
         <v>1</v>
@@ -2151,26 +2163,26 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>3.766</v>
+        <v>3.774</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>2.268</v>
+        <v>2.273</v>
       </c>
       <c r="D8" s="15" t="inlineStr"/>
       <c r="E8" s="15" t="n">
-        <v>0.345</v>
+        <v>0.351</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0.021</v>
+        <v>0.027</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>-0.059</v>
+        <v>-0.077</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>0.336</v>
+        <v>0.33</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>1</v>
@@ -2194,29 +2206,29 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>3.271</v>
+        <v>3.283</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>1.074</v>
+        <v>1.084</v>
       </c>
       <c r="D9" s="15" t="inlineStr"/>
       <c r="E9" s="15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>-0.064</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="I9" s="15" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="F9" s="15" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="G9" s="15" t="n">
-        <v>-0.057</v>
-      </c>
-      <c r="H9" s="15" t="n">
-        <v>-0.07099999999999999</v>
-      </c>
-      <c r="I9" s="15" t="n">
-        <v>0.025</v>
-      </c>
       <c r="J9" s="15" t="n">
-        <v>-0.043</v>
+        <v>-0.049</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>1</v>
@@ -2239,34 +2251,34 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>4.062</v>
+        <v>4.06</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.62</v>
+        <v>0.611</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0.91</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>0.022</v>
+        <v>0.041</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0.031</v>
+        <v>0.024</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.06</v>
+        <v>0.061</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-0.083</v>
+        <v>-0.075</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-0.028</v>
+        <v>-0.004</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>0.05</v>
+        <v>0.052</v>
       </c>
       <c r="L10" s="15" t="n">
         <v>1</v>
@@ -2288,37 +2300,37 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>5.046</v>
+        <v>5.026</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0.573</v>
+        <v>0.581</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>0.93</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>-0.058</v>
+        <v>-0.076</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>-0.035</v>
+        <v>-0.008</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.065</v>
+        <v>0.061</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-0.089</v>
+        <v>-0.075</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-0.014</v>
+        <v>-0.025</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>-0.083</v>
+        <v>-0.053</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>-0.051</v>
+        <v>-0.059</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>-0.149</v>
+        <v>-0.078</v>
       </c>
       <c r="M11" s="15" t="n">
         <v>1</v>
@@ -2339,40 +2351,40 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>3.469</v>
+        <v>3.439</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.918</v>
+        <v>0.902</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>-0.007</v>
+        <v>-0.04</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>-0.047</v>
+        <v>-0.058</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>-0.036</v>
+        <v>-0.002</v>
       </c>
       <c r="H12" s="15" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="J12" s="15" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="K12" s="15" t="n">
+        <v>-0.062</v>
+      </c>
+      <c r="L12" s="15" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="M12" s="15" t="n">
         <v>0.054</v>
-      </c>
-      <c r="I12" s="15" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="J12" s="15" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="K12" s="15" t="n">
-        <v>-0.076</v>
-      </c>
-      <c r="L12" s="15" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="M12" s="15" t="n">
-        <v>0.04</v>
       </c>
       <c r="N12" s="15" t="n">
         <v>1</v>
@@ -2392,43 +2404,43 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>4.601</v>
+        <v>4.583</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.893</v>
+        <v>0.883</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>0.84</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>-0.077</v>
+        <v>-0.073</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>-0.077</v>
+        <v>-0.096</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>-0.073</v>
+        <v>-0.043</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>0.055</v>
+        <v>0.04</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-0.054</v>
+        <v>-0.044</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>-0.083</v>
+        <v>-0.074</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>-0.059</v>
+        <v>-0.049</v>
       </c>
       <c r="L13" s="15" t="n">
-        <v>-0.05</v>
+        <v>-0.006</v>
       </c>
       <c r="M13" s="15" t="n">
-        <v>-0.093</v>
+        <v>-0.063</v>
       </c>
       <c r="N13" s="15" t="n">
-        <v>0.004</v>
+        <v>-0.019</v>
       </c>
       <c r="O13" s="15" t="n">
         <v>1</v>
@@ -2447,46 +2459,46 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>4.515</v>
+        <v>4.476</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>1.195</v>
+        <v>1.207</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>0.88</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>-0.001</v>
+        <v>-0.028</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>-0.029</v>
+        <v>-0.035</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>-0.043</v>
+        <v>-0.012</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>0.04</v>
+        <v>0.027</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>0.056</v>
+        <v>0.026</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>-0.064</v>
+        <v>-0.068</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="L14" s="15" t="n">
-        <v>-0.34</v>
+        <v>-0.327</v>
       </c>
       <c r="M14" s="15" t="n">
-        <v>0.357</v>
+        <v>0.341</v>
       </c>
       <c r="N14" s="15" t="n">
-        <v>-0.013</v>
+        <v>-0.025</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>-0.044</v>
+        <v>-0.061</v>
       </c>
       <c r="P14" s="15" t="n">
         <v>1</v>
@@ -2504,46 +2516,46 @@
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>2.996</v>
+        <v>2.983</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>1.138</v>
+        <v>1.137</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>0.87</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>-0.008</v>
+        <v>0.03</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>-0.014</v>
+        <v>-0.048</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-0.044</v>
+        <v>-0.035</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-0.063</v>
+        <v>-0.018</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>0.037</v>
+        <v>0.03</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.096</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>0.312</v>
+        <v>0.284</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.262</v>
+        <v>-0.273</v>
       </c>
       <c r="N15" s="15" t="n">
-        <v>0.022</v>
+        <v>0.056</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.079</v>
       </c>
       <c r="P15" s="15" t="n">
         <v>-0.446</v>
@@ -2563,52 +2575,52 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>4.591</v>
+        <v>4.656</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>0.47</v>
+        <v>0.506</v>
       </c>
       <c r="D16" s="15" t="n">
         <v>0.9</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>-0.025</v>
+        <v>-0.039</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>-0.014</v>
+        <v>0.017</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>-0.057</v>
+        <v>-0.068</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>0.027</v>
+        <v>-0.018</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-0.038</v>
+        <v>-0.066</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.003</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>-0.045</v>
+        <v>-0.011</v>
       </c>
       <c r="L16" s="15" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M16" s="15" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="N16" s="15" t="n">
+        <v>-0.143</v>
+      </c>
+      <c r="O16" s="15" t="n">
         <v>0.041</v>
       </c>
-      <c r="M16" s="15" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="N16" s="15" t="n">
-        <v>-0.148</v>
-      </c>
-      <c r="O16" s="15" t="n">
-        <v>0.038</v>
-      </c>
       <c r="P16" s="15" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="Q16" s="15" t="n">
-        <v>-0.037</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="R16" s="15" t="n">
         <v>1</v>
@@ -2624,55 +2636,55 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>4.766</v>
+        <v>4.724</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>1.016</v>
+        <v>0.897</v>
       </c>
       <c r="D17" s="15" t="n">
         <v>0.9</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>-0.047</v>
+        <v>-0.02</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>-0.024</v>
+        <v>-0.02</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>-0.062</v>
+        <v>0.003</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>0.039</v>
+        <v>0.051</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>0.015</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>-0.033</v>
+        <v>-0.029</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>-0.099</v>
+        <v>-0.133</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>-0.325</v>
+        <v>-0.261</v>
       </c>
       <c r="M17" s="15" t="n">
-        <v>0.311</v>
+        <v>0.239</v>
       </c>
       <c r="N17" s="15" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.006</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>0.059</v>
+        <v>0.011</v>
       </c>
       <c r="P17" s="15" t="n">
-        <v>0.711</v>
+        <v>0.673</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>-0.66</v>
+        <v>-0.65</v>
       </c>
       <c r="R17" s="15" t="n">
-        <v>0.035</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="S17" s="15" t="n">
         <v>1</v>
@@ -2687,58 +2699,58 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>4.859</v>
+        <v>4.823</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>1.346</v>
+        <v>1.302</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>0.92</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>-0.077</v>
+        <v>-0.059</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>-0.003</v>
+        <v>-0.012</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>-0.094</v>
+        <v>-0.12</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-0.029</v>
+        <v>-0.059</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-0.056</v>
+        <v>-0.007</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>-0.03</v>
+        <v>0.046</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>-0.032</v>
+        <v>-0.005</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>-0.435</v>
+        <v>-0.409</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>0.52</v>
+        <v>0.359</v>
       </c>
       <c r="N18" s="15" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.033</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0.427</v>
+        <v>0.412</v>
       </c>
       <c r="Q18" s="15" t="n">
-        <v>-0.375</v>
+        <v>-0.381</v>
       </c>
       <c r="R18" s="15" t="n">
-        <v>0.095</v>
+        <v>0.052</v>
       </c>
       <c r="S18" s="15" t="n">
-        <v>0.405</v>
+        <v>0.322</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>1</v>
@@ -2752,58 +2764,58 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>2.386</v>
+        <v>2.351</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>1.024</v>
+        <v>0.973</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>0.89</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>-0.056</v>
+        <v>0.038</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>0.092</v>
+        <v>0.049</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>0</v>
+        <v>-0.013</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-0.07199999999999999</v>
+        <v>0.02</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>-0.056</v>
+        <v>-0.049</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>-0.005</v>
+        <v>0.04</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>0.504</v>
+        <v>0.279</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>-0.436</v>
+        <v>-0.486</v>
       </c>
       <c r="N19" s="15" t="n">
-        <v>-0.013</v>
+        <v>0.058</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>0.021</v>
+        <v>0.075</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>-0.381</v>
+        <v>-0.401</v>
       </c>
       <c r="Q19" s="15" t="n">
-        <v>0.325</v>
+        <v>0.356</v>
       </c>
       <c r="R19" s="15" t="n">
         <v>0.001</v>
       </c>
       <c r="S19" s="15" t="n">
-        <v>-0.348</v>
+        <v>-0.339</v>
       </c>
       <c r="T19" s="15" t="n">
         <v>-0.592</v>

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>30.767</v>
+        <v>29.641</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>4.683</v>
+        <v>4.691</v>
       </c>
       <c r="D3" s="15" t="inlineStr"/>
       <c r="E3" s="15" t="n">
@@ -2011,14 +2011,14 @@
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>0.529</v>
+        <v>0.605</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="D4" s="15" t="inlineStr"/>
       <c r="E4" s="15" t="n">
-        <v>0.037</v>
+        <v>-0.026</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>1</v>
@@ -2046,17 +2046,17 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>3.107</v>
+        <v>3.154</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>0.922</v>
+        <v>0.895</v>
       </c>
       <c r="D5" s="15" t="inlineStr"/>
       <c r="E5" s="15" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>-0.099</v>
+        <v>0.023</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>1</v>
@@ -2083,20 +2083,20 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>2.521</v>
+        <v>2.509</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>1.121</v>
+        <v>1.075</v>
       </c>
       <c r="D6" s="15" t="inlineStr"/>
       <c r="E6" s="15" t="n">
-        <v>-0.032</v>
+        <v>-0.028</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>-0.075</v>
+        <v>0.039</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>-0.011</v>
+        <v>-0.066</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>1</v>
@@ -2122,23 +2122,23 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>9</v>
+        <v>7.655</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>4.967</v>
+        <v>4.879</v>
       </c>
       <c r="D7" s="15" t="inlineStr"/>
       <c r="E7" s="15" t="n">
-        <v>0.907</v>
+        <v>0.923</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0.026</v>
+        <v>-0.039</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>-0.007</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-0.004</v>
+        <v>-0.058</v>
       </c>
       <c r="I7" s="15" t="n">
         <v>1</v>
@@ -2163,26 +2163,26 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>3.774</v>
+        <v>3.497</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>2.273</v>
+        <v>2.334</v>
       </c>
       <c r="D8" s="15" t="inlineStr"/>
       <c r="E8" s="15" t="n">
-        <v>0.351</v>
+        <v>0.423</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0.027</v>
+        <v>-0.017</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>-0.077</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>0.017</v>
+        <v>0.015</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>0.33</v>
+        <v>0.447</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>1</v>
@@ -2206,29 +2206,29 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>3.283</v>
+        <v>3.223</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>1.084</v>
+        <v>1.098</v>
       </c>
       <c r="D9" s="15" t="inlineStr"/>
       <c r="E9" s="15" t="n">
-        <v>-0</v>
+        <v>0.061</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.098</v>
+        <v>-0.03</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>-0.064</v>
+        <v>-0.016</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-0.08</v>
+        <v>0.073</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.066</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>-0.049</v>
+        <v>0.082</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>1</v>
@@ -2251,34 +2251,34 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>4.06</v>
+        <v>4.03</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.611</v>
+        <v>0.622</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0.91</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>0.041</v>
+        <v>0.061</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0.024</v>
+        <v>0.039</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.061</v>
+        <v>0.108</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-0.075</v>
+        <v>-0.032</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-0.004</v>
+        <v>0.073</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>0.02</v>
+        <v>-0.011</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>0.052</v>
+        <v>-0.079</v>
       </c>
       <c r="L10" s="15" t="n">
         <v>1</v>
@@ -2300,37 +2300,37 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>5.026</v>
+        <v>5.043</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0.581</v>
+        <v>0.599</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>0.93</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>-0.076</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>-0.008</v>
+        <v>0.083</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.061</v>
+        <v>0.055</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-0.075</v>
+        <v>-0.078</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-0.025</v>
+        <v>-0.062</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>-0.053</v>
+        <v>0.012</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>-0.059</v>
+        <v>0.006</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>-0.078</v>
+        <v>-0.165</v>
       </c>
       <c r="M11" s="15" t="n">
         <v>1</v>
@@ -2351,40 +2351,40 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>3.439</v>
+        <v>3.47</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.902</v>
+        <v>0.915</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>-0.04</v>
+        <v>0.005</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>-0.058</v>
+        <v>0.023</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>-0.002</v>
+        <v>0.018</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>0.082</v>
+        <v>0.015</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>0.032</v>
+        <v>0.054</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>0.079</v>
+        <v>-0.018</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>-0.062</v>
+        <v>0.049</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>0.057</v>
+        <v>0.042</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>0.054</v>
+        <v>0.059</v>
       </c>
       <c r="N12" s="15" t="n">
         <v>1</v>
@@ -2404,43 +2404,43 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>4.583</v>
+        <v>4.568</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.883</v>
+        <v>0.898</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>0.84</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>-0.073</v>
+        <v>-0.021</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>-0.096</v>
+        <v>-0.04</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>-0.043</v>
+        <v>0.033</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>0.04</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-0.044</v>
+        <v>-0.02</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>-0.074</v>
+        <v>-0.102</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>-0.049</v>
+        <v>-0.002</v>
       </c>
       <c r="L13" s="15" t="n">
-        <v>-0.006</v>
+        <v>0.053</v>
       </c>
       <c r="M13" s="15" t="n">
-        <v>-0.063</v>
+        <v>-0.062</v>
       </c>
       <c r="N13" s="15" t="n">
-        <v>-0.019</v>
+        <v>-0.018</v>
       </c>
       <c r="O13" s="15" t="n">
         <v>1</v>
@@ -2459,46 +2459,46 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>4.476</v>
+        <v>4.545</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>1.207</v>
+        <v>1.156</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>0.88</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>-0.028</v>
+        <v>-0.036</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>-0.035</v>
+        <v>-0.003</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>-0.012</v>
+        <v>-0.066</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>0.027</v>
+        <v>0.021</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>0.026</v>
+        <v>-0.044</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>-0.068</v>
+        <v>0.008</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.021</v>
       </c>
       <c r="L14" s="15" t="n">
-        <v>-0.327</v>
+        <v>-0.282</v>
       </c>
       <c r="M14" s="15" t="n">
-        <v>0.341</v>
+        <v>0.268</v>
       </c>
       <c r="N14" s="15" t="n">
-        <v>-0.025</v>
+        <v>0.028</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>-0.061</v>
+        <v>0.023</v>
       </c>
       <c r="P14" s="15" t="n">
         <v>1</v>
@@ -2516,49 +2516,49 @@
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>2.983</v>
+        <v>2.86</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>1.137</v>
+        <v>1.088</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>0.87</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>0.03</v>
+        <v>-0.047</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0.003</v>
+        <v>0.057</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>-0.048</v>
+        <v>0.011</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-0.035</v>
+        <v>0.011</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-0.018</v>
+        <v>-0.029</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>0.03</v>
+        <v>0.068</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>0.096</v>
+        <v>-0.062</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>0.284</v>
+        <v>0.288</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.273</v>
+        <v>-0.242</v>
       </c>
       <c r="N15" s="15" t="n">
-        <v>0.056</v>
+        <v>-0.02</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.079</v>
+        <v>-0.039</v>
       </c>
       <c r="P15" s="15" t="n">
-        <v>-0.446</v>
+        <v>-0.344</v>
       </c>
       <c r="Q15" s="15" t="n">
         <v>1</v>
@@ -2575,52 +2575,52 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>4.656</v>
+        <v>4.663</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>0.506</v>
+        <v>0.503</v>
       </c>
       <c r="D16" s="15" t="n">
         <v>0.9</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>-0.039</v>
+        <v>0.05</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>0.017</v>
+        <v>0.122</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>-0.068</v>
+        <v>-0.012</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-0.018</v>
+        <v>-0.041</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-0.066</v>
+        <v>0.029</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>0.003</v>
+        <v>0.133</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>-0.011</v>
+        <v>-0.04</v>
       </c>
       <c r="L16" s="15" t="n">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="M16" s="15" t="n">
-        <v>0.047</v>
+        <v>0.041</v>
       </c>
       <c r="N16" s="15" t="n">
-        <v>-0.143</v>
+        <v>-0.147</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>0.041</v>
+        <v>0.016</v>
       </c>
       <c r="P16" s="15" t="n">
-        <v>0.083</v>
+        <v>-0.015</v>
       </c>
       <c r="Q16" s="15" t="n">
-        <v>-0.08799999999999999</v>
+        <v>0.057</v>
       </c>
       <c r="R16" s="15" t="n">
         <v>1</v>
@@ -2636,55 +2636,55 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>4.724</v>
+        <v>4.714</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>0.897</v>
+        <v>0.91</v>
       </c>
       <c r="D17" s="15" t="n">
         <v>0.9</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>-0.02</v>
+        <v>0.058</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>-0.02</v>
+        <v>-0.031</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>0.003</v>
+        <v>-0.003</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>0.051</v>
+        <v>-0.057</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.019</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>-0.029</v>
+        <v>-0.006</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>-0.133</v>
+        <v>0.036</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>-0.261</v>
+        <v>-0.279</v>
       </c>
       <c r="M17" s="15" t="n">
-        <v>0.239</v>
+        <v>0.319</v>
       </c>
       <c r="N17" s="15" t="n">
-        <v>-0.006</v>
+        <v>0.025</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>0.011</v>
+        <v>0.062</v>
       </c>
       <c r="P17" s="15" t="n">
-        <v>0.673</v>
+        <v>0.591</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>-0.65</v>
+        <v>-0.659</v>
       </c>
       <c r="R17" s="15" t="n">
-        <v>0.07099999999999999</v>
+        <v>-0.003</v>
       </c>
       <c r="S17" s="15" t="n">
         <v>1</v>
@@ -2699,58 +2699,58 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>4.823</v>
+        <v>4.805</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>1.302</v>
+        <v>1.259</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>0.92</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>-0.059</v>
+        <v>-0.099</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>-0.012</v>
+        <v>0.014</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>-0.12</v>
+        <v>0.015</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-0.059</v>
+        <v>0.001</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-0.007</v>
+        <v>-0.077</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>0.046</v>
+        <v>-0.062</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>-0.005</v>
+        <v>-0.051</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>-0.409</v>
+        <v>-0.459</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>0.359</v>
+        <v>0.339</v>
       </c>
       <c r="N18" s="15" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.047</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>-0.033</v>
+        <v>0.057</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0.412</v>
+        <v>0.433</v>
       </c>
       <c r="Q18" s="15" t="n">
-        <v>-0.381</v>
+        <v>-0.299</v>
       </c>
       <c r="R18" s="15" t="n">
-        <v>0.052</v>
+        <v>0.018</v>
       </c>
       <c r="S18" s="15" t="n">
-        <v>0.322</v>
+        <v>0.338</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>1</v>
@@ -2764,61 +2764,61 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>2.351</v>
+        <v>2.511</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>0.973</v>
+        <v>1.062</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>0.89</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>0.038</v>
+        <v>0.01</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>0.049</v>
+        <v>-0.057</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>0.035</v>
+        <v>0.054</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-0.013</v>
+        <v>0.08</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>-0.049</v>
+        <v>-0.018</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>0.04</v>
+        <v>-0.059</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>0.279</v>
+        <v>0.343</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>-0.486</v>
+        <v>-0.357</v>
       </c>
       <c r="N19" s="15" t="n">
-        <v>0.058</v>
+        <v>-0.017</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>0.075</v>
+        <v>-0.011</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>-0.401</v>
+        <v>-0.251</v>
       </c>
       <c r="Q19" s="15" t="n">
-        <v>0.356</v>
+        <v>0.401</v>
       </c>
       <c r="R19" s="15" t="n">
-        <v>0.001</v>
+        <v>-0.064</v>
       </c>
       <c r="S19" s="15" t="n">
-        <v>-0.339</v>
+        <v>-0.352</v>
       </c>
       <c r="T19" s="15" t="n">
-        <v>-0.592</v>
+        <v>-0.289</v>
       </c>
       <c r="U19" s="15" t="n">
         <v>1</v>

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>29.641</v>
+        <v>29.756</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>4.691</v>
+        <v>4.813</v>
       </c>
       <c r="D3" s="15" t="inlineStr"/>
       <c r="E3" s="15" t="n">
@@ -2011,14 +2011,14 @@
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>0.605</v>
+        <v>0.581</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>0.49</v>
+        <v>0.494</v>
       </c>
       <c r="D4" s="15" t="inlineStr"/>
       <c r="E4" s="15" t="n">
-        <v>-0.026</v>
+        <v>-0.015</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>1</v>
@@ -2046,17 +2046,17 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>3.154</v>
+        <v>3.176</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>0.895</v>
+        <v>0.888</v>
       </c>
       <c r="D5" s="15" t="inlineStr"/>
       <c r="E5" s="15" t="n">
-        <v>0.027</v>
+        <v>0.026</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0.023</v>
+        <v>0.065</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>1</v>
@@ -2083,20 +2083,20 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>2.509</v>
+        <v>2.482</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>1.075</v>
+        <v>1.085</v>
       </c>
       <c r="D6" s="15" t="inlineStr"/>
       <c r="E6" s="15" t="n">
-        <v>-0.028</v>
+        <v>-0.037</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0.039</v>
+        <v>0.041</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>-0.066</v>
+        <v>-0.043</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>1</v>
@@ -2122,23 +2122,23 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>7.655</v>
+        <v>7.806</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>4.879</v>
+        <v>4.922</v>
       </c>
       <c r="D7" s="15" t="inlineStr"/>
       <c r="E7" s="15" t="n">
-        <v>0.923</v>
+        <v>0.922</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>-0.039</v>
+        <v>-0.045</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>-0.007</v>
+        <v>0.013</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-0.058</v>
+        <v>-0.062</v>
       </c>
       <c r="I7" s="15" t="n">
         <v>1</v>
@@ -2163,26 +2163,26 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>3.497</v>
+        <v>3.579</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>2.334</v>
+        <v>2.429</v>
       </c>
       <c r="D8" s="15" t="inlineStr"/>
       <c r="E8" s="15" t="n">
-        <v>0.423</v>
+        <v>0.384</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>-0.017</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.083</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>0.015</v>
+        <v>0.066</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>0.447</v>
+        <v>0.418</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>1</v>
@@ -2206,29 +2206,29 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>3.223</v>
+        <v>3.222</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>1.098</v>
+        <v>1.133</v>
       </c>
       <c r="D9" s="15" t="inlineStr"/>
       <c r="E9" s="15" t="n">
-        <v>0.061</v>
+        <v>0.066</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>-0.03</v>
+        <v>-0.025</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>-0.016</v>
+        <v>-0.06</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>0.073</v>
+        <v>0.089</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>0.066</v>
+        <v>0.074</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>0.082</v>
+        <v>0.124</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>1</v>
@@ -2251,34 +2251,34 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>4.03</v>
+        <v>4.045</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.622</v>
+        <v>0.613</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0.91</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>0.061</v>
+        <v>0.039</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0.039</v>
+        <v>0.036</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.108</v>
+        <v>0.107</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-0.032</v>
+        <v>-0.061</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>0.073</v>
+        <v>0.06</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>-0.011</v>
+        <v>-0.042</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>-0.079</v>
+        <v>-0.047</v>
       </c>
       <c r="L10" s="15" t="n">
         <v>1</v>
@@ -2300,37 +2300,37 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>5.043</v>
+        <v>5.006</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0.599</v>
+        <v>0.585</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>0.93</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.091</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0.083</v>
+        <v>0.059</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.055</v>
+        <v>0.068</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>-0.078</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-0.062</v>
+        <v>-0.08</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>0.012</v>
+        <v>0.023</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>0.006</v>
+        <v>-0.019</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>-0.165</v>
+        <v>-0.147</v>
       </c>
       <c r="M11" s="15" t="n">
         <v>1</v>
@@ -2351,40 +2351,40 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>3.47</v>
+        <v>3.444</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.915</v>
+        <v>0.905</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>0.005</v>
+        <v>0.031</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0.023</v>
+        <v>0.018</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0.018</v>
+        <v>0.044</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>0.015</v>
+        <v>0.004</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>0.054</v>
+        <v>0.076</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>-0.018</v>
+        <v>-0.012</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>0.049</v>
+        <v>0.011</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>0.042</v>
+        <v>0.025</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>0.059</v>
+        <v>0.02</v>
       </c>
       <c r="N12" s="15" t="n">
         <v>1</v>
@@ -2404,43 +2404,43 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>4.568</v>
+        <v>4.56</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.898</v>
+        <v>0.884</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>0.84</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>-0.021</v>
+        <v>-0.046</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>-0.04</v>
+        <v>-0.016</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0.033</v>
+        <v>0.042</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.053</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-0.02</v>
+        <v>-0.046</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>-0.102</v>
+        <v>-0.074</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>-0.002</v>
+        <v>0.008</v>
       </c>
       <c r="L13" s="15" t="n">
-        <v>0.053</v>
+        <v>-0.011</v>
       </c>
       <c r="M13" s="15" t="n">
-        <v>-0.062</v>
+        <v>-0.05</v>
       </c>
       <c r="N13" s="15" t="n">
-        <v>-0.018</v>
+        <v>-0.007</v>
       </c>
       <c r="O13" s="15" t="n">
         <v>1</v>
@@ -2459,46 +2459,46 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>4.545</v>
+        <v>4.493</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>1.156</v>
+        <v>1.118</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>0.88</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>-0.036</v>
+        <v>-0.012</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>-0.003</v>
+        <v>0.044</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>-0.066</v>
+        <v>-0.096</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>0.021</v>
+        <v>0.011</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-0.044</v>
+        <v>-0.021</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>0.008</v>
+        <v>0.045</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>-0.021</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="L14" s="15" t="n">
         <v>-0.282</v>
       </c>
       <c r="M14" s="15" t="n">
-        <v>0.268</v>
+        <v>0.323</v>
       </c>
       <c r="N14" s="15" t="n">
-        <v>0.028</v>
+        <v>0.052</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>0.023</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="P14" s="15" t="n">
         <v>1</v>
@@ -2516,49 +2516,49 @@
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>2.86</v>
+        <v>2.898</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>1.088</v>
+        <v>1.091</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>0.87</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>-0.047</v>
+        <v>-0.03</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0.057</v>
+        <v>0.065</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0.011</v>
+        <v>0.031</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>0.011</v>
+        <v>-0.036</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-0.029</v>
+        <v>-0.012</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>0.068</v>
+        <v>0.015</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>-0.062</v>
+        <v>-0.022</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>0.288</v>
+        <v>0.255</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.242</v>
+        <v>-0.253</v>
       </c>
       <c r="N15" s="15" t="n">
-        <v>-0.02</v>
+        <v>-0.028</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.039</v>
+        <v>-0.08</v>
       </c>
       <c r="P15" s="15" t="n">
-        <v>-0.344</v>
+        <v>-0.381</v>
       </c>
       <c r="Q15" s="15" t="n">
         <v>1</v>
@@ -2575,52 +2575,52 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>4.663</v>
+        <v>4.671</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>0.503</v>
+        <v>0.493</v>
       </c>
       <c r="D16" s="15" t="n">
         <v>0.9</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>0.05</v>
+        <v>0.061</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>0.122</v>
+        <v>0.105</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>-0.012</v>
+        <v>-0.031</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-0.041</v>
+        <v>-0.019</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>0.133</v>
+        <v>0.142</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>-0.04</v>
+        <v>-0.033</v>
       </c>
       <c r="L16" s="15" t="n">
-        <v>0.025</v>
+        <v>0.06</v>
       </c>
       <c r="M16" s="15" t="n">
-        <v>0.041</v>
+        <v>-0.015</v>
       </c>
       <c r="N16" s="15" t="n">
-        <v>-0.147</v>
+        <v>-0.136</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>0.016</v>
+        <v>0.044</v>
       </c>
       <c r="P16" s="15" t="n">
-        <v>-0.015</v>
+        <v>-0.032</v>
       </c>
       <c r="Q16" s="15" t="n">
-        <v>0.057</v>
+        <v>0.051</v>
       </c>
       <c r="R16" s="15" t="n">
         <v>1</v>
@@ -2636,55 +2636,55 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>4.714</v>
+        <v>4.701</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="D17" s="15" t="n">
         <v>0.9</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>0.058</v>
+        <v>0.04</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>-0.031</v>
+        <v>-0.01</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>-0.003</v>
+        <v>0.023</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-0.057</v>
+        <v>0.03</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>0.019</v>
+        <v>0.008</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>-0.006</v>
+        <v>0.05</v>
       </c>
       <c r="K17" s="15" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="L17" s="15" t="n">
+        <v>-0.256</v>
+      </c>
+      <c r="M17" s="15" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="N17" s="15" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="O17" s="15" t="n">
         <v>0.036</v>
       </c>
-      <c r="L17" s="15" t="n">
-        <v>-0.279</v>
-      </c>
-      <c r="M17" s="15" t="n">
-        <v>0.319</v>
-      </c>
-      <c r="N17" s="15" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="O17" s="15" t="n">
-        <v>0.062</v>
-      </c>
       <c r="P17" s="15" t="n">
-        <v>0.591</v>
+        <v>0.678</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>-0.659</v>
+        <v>-0.643</v>
       </c>
       <c r="R17" s="15" t="n">
-        <v>-0.003</v>
+        <v>-0.077</v>
       </c>
       <c r="S17" s="15" t="n">
         <v>1</v>
@@ -2699,58 +2699,58 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>4.805</v>
+        <v>4.758</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>1.259</v>
+        <v>1.17</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>0.92</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>-0.099</v>
+        <v>-0.122</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>0.014</v>
+        <v>0.081</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>0.015</v>
+        <v>-0.074</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>0.001</v>
+        <v>0.036</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-0.077</v>
+        <v>-0.096</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>-0.062</v>
+        <v>0.033</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>-0.051</v>
+        <v>-0.074</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>-0.459</v>
+        <v>-0.365</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>0.339</v>
+        <v>0.43</v>
       </c>
       <c r="N18" s="15" t="n">
-        <v>-0.047</v>
+        <v>0.004</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>0.057</v>
+        <v>0.019</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0.433</v>
+        <v>0.398</v>
       </c>
       <c r="Q18" s="15" t="n">
-        <v>-0.299</v>
+        <v>-0.341</v>
       </c>
       <c r="R18" s="15" t="n">
-        <v>0.018</v>
+        <v>-0.022</v>
       </c>
       <c r="S18" s="15" t="n">
-        <v>0.338</v>
+        <v>0.332</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>1</v>
@@ -2764,61 +2764,61 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>2.511</v>
+        <v>2.381</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>1.062</v>
+        <v>1.007</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>0.89</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>0.01</v>
+        <v>0.105</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>-0.057</v>
+        <v>-0.017</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>0.054</v>
+        <v>-0.053</v>
       </c>
       <c r="H19" s="15" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="I19" s="15" t="n">
         <v>0.08</v>
       </c>
-      <c r="I19" s="15" t="n">
-        <v>0.01</v>
-      </c>
       <c r="J19" s="15" t="n">
-        <v>-0.018</v>
+        <v>-0.032</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>-0.059</v>
+        <v>0.068</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>0.343</v>
+        <v>0.317</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>-0.357</v>
+        <v>-0.336</v>
       </c>
       <c r="N19" s="15" t="n">
-        <v>-0.017</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>-0.011</v>
+        <v>0.019</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>-0.251</v>
+        <v>-0.286</v>
       </c>
       <c r="Q19" s="15" t="n">
-        <v>0.401</v>
+        <v>0.356</v>
       </c>
       <c r="R19" s="15" t="n">
-        <v>-0.064</v>
+        <v>-0.008</v>
       </c>
       <c r="S19" s="15" t="n">
-        <v>-0.352</v>
+        <v>-0.241</v>
       </c>
       <c r="T19" s="15" t="n">
-        <v>-0.289</v>
+        <v>-0.398</v>
       </c>
       <c r="U19" s="15" t="n">
         <v>1</v>

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>29.756</v>
+        <v>30.856</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>4.813</v>
+        <v>4.648</v>
       </c>
       <c r="D3" s="15" t="inlineStr"/>
       <c r="E3" s="15" t="n">
@@ -2011,14 +2011,14 @@
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>0.581</v>
+        <v>0.548</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>0.494</v>
+        <v>0.498</v>
       </c>
       <c r="D4" s="15" t="inlineStr"/>
       <c r="E4" s="15" t="n">
-        <v>-0.015</v>
+        <v>0.062</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>1</v>
@@ -2046,17 +2046,17 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>3.176</v>
+        <v>3.121</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>0.888</v>
+        <v>0.952</v>
       </c>
       <c r="D5" s="15" t="inlineStr"/>
       <c r="E5" s="15" t="n">
-        <v>0.026</v>
+        <v>0.002</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0.065</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>1</v>
@@ -2083,20 +2083,20 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>2.482</v>
+        <v>2.549</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>1.085</v>
+        <v>1.135</v>
       </c>
       <c r="D6" s="15" t="inlineStr"/>
       <c r="E6" s="15" t="n">
-        <v>-0.037</v>
+        <v>-0.021</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0.041</v>
+        <v>-0.03</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>-0.043</v>
+        <v>-0.028</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>1</v>
@@ -2122,23 +2122,23 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>7.806</v>
+        <v>9.093999999999999</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>4.922</v>
+        <v>4.842</v>
       </c>
       <c r="D7" s="15" t="inlineStr"/>
       <c r="E7" s="15" t="n">
-        <v>0.922</v>
+        <v>0.905</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>-0.045</v>
+        <v>0.04</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0.013</v>
+        <v>0.002</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-0.062</v>
+        <v>0.001</v>
       </c>
       <c r="I7" s="15" t="n">
         <v>1</v>
@@ -2163,26 +2163,26 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>3.579</v>
+        <v>2.334</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>2.429</v>
+        <v>1.506</v>
       </c>
       <c r="D8" s="15" t="inlineStr"/>
       <c r="E8" s="15" t="n">
-        <v>0.384</v>
+        <v>0.188</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.014</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>-0.083</v>
+        <v>-0.028</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>0.066</v>
+        <v>0.024</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>0.418</v>
+        <v>0.151</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>1</v>
@@ -2206,29 +2206,29 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>3.222</v>
+        <v>3.244</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>1.133</v>
+        <v>1.076</v>
       </c>
       <c r="D9" s="15" t="inlineStr"/>
       <c r="E9" s="15" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="F9" s="15" t="n">
         <v>0.066</v>
       </c>
-      <c r="F9" s="15" t="n">
-        <v>-0.025</v>
-      </c>
       <c r="G9" s="15" t="n">
-        <v>-0.06</v>
+        <v>-0.073</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>0.089</v>
+        <v>-0.066</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>0.074</v>
+        <v>-0.008</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>0.124</v>
+        <v>-0.042</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>1</v>
@@ -2251,34 +2251,34 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>4.045</v>
+        <v>4.06</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.613</v>
+        <v>0.593</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0.91</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>0.039</v>
+        <v>0.006</v>
       </c>
       <c r="F10" s="15" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>-0.093</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>-0.036</v>
+      </c>
+      <c r="J10" s="15" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="K10" s="15" t="n">
         <v>0.036</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="H10" s="15" t="n">
-        <v>-0.061</v>
-      </c>
-      <c r="I10" s="15" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="J10" s="15" t="n">
-        <v>-0.042</v>
-      </c>
-      <c r="K10" s="15" t="n">
-        <v>-0.047</v>
       </c>
       <c r="L10" s="15" t="n">
         <v>1</v>
@@ -2300,37 +2300,37 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>5.006</v>
+        <v>5.013</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0.585</v>
+        <v>0.575</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>0.93</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>-0.091</v>
+        <v>-0.042</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0.059</v>
+        <v>-0.025</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.068</v>
+        <v>0.035</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-0.078</v>
+        <v>-0.079</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-0.08</v>
+        <v>0.004</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>0.023</v>
+        <v>-0.067</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>-0.019</v>
+        <v>-0.063</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>-0.147</v>
+        <v>-0.052</v>
       </c>
       <c r="M11" s="15" t="n">
         <v>1</v>
@@ -2351,40 +2351,40 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>3.444</v>
+        <v>3.43</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.905</v>
+        <v>0.894</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>0.031</v>
+        <v>-0.01</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0.018</v>
+        <v>-0.047</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0.044</v>
+        <v>-0.018</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>0.004</v>
+        <v>0.05</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>0.076</v>
+        <v>0.055</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>-0.012</v>
+        <v>0.091</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>0.011</v>
+        <v>-0.02</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>0.025</v>
+        <v>0.063</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>0.02</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="N12" s="15" t="n">
         <v>1</v>
@@ -2404,43 +2404,43 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>4.56</v>
+        <v>4.599</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.884</v>
+        <v>0.888</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>0.84</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>-0.046</v>
+        <v>-0.083</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>-0.016</v>
+        <v>-0.101</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0.042</v>
+        <v>-0.04</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>0.053</v>
+        <v>0.049</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-0.046</v>
+        <v>-0.056</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>-0.074</v>
+        <v>-0.076</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>0.008</v>
+        <v>-0.075</v>
       </c>
       <c r="L13" s="15" t="n">
-        <v>-0.011</v>
+        <v>-0.049</v>
       </c>
       <c r="M13" s="15" t="n">
-        <v>-0.05</v>
+        <v>-0.032</v>
       </c>
       <c r="N13" s="15" t="n">
-        <v>-0.007</v>
+        <v>-0.024</v>
       </c>
       <c r="O13" s="15" t="n">
         <v>1</v>
@@ -2459,46 +2459,46 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>4.493</v>
+        <v>4.474</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>1.118</v>
+        <v>1.207</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>0.88</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>-0.012</v>
+        <v>-0.002</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0.044</v>
+        <v>-0.05</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>-0.096</v>
+        <v>-0.023</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>0.011</v>
+        <v>0.055</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-0.021</v>
+        <v>0.058</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>0.045</v>
+        <v>-0.078</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.079</v>
       </c>
       <c r="L14" s="15" t="n">
-        <v>-0.282</v>
+        <v>-0.324</v>
       </c>
       <c r="M14" s="15" t="n">
-        <v>0.323</v>
+        <v>0.343</v>
       </c>
       <c r="N14" s="15" t="n">
-        <v>0.052</v>
+        <v>-0.034</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>0.07199999999999999</v>
+        <v>-0.03</v>
       </c>
       <c r="P14" s="15" t="n">
         <v>1</v>
@@ -2516,49 +2516,49 @@
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>2.898</v>
+        <v>2.998</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>1.091</v>
+        <v>1.126</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>0.87</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>-0.03</v>
+        <v>0.016</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0.065</v>
+        <v>-0.002</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0.031</v>
+        <v>0.001</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-0.036</v>
+        <v>-0.039</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-0.012</v>
+        <v>-0.045</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>-0.022</v>
+        <v>0.082</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>0.255</v>
+        <v>0.259</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.253</v>
+        <v>-0.238</v>
       </c>
       <c r="N15" s="15" t="n">
-        <v>-0.028</v>
+        <v>0.064</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.08</v>
+        <v>-0.099</v>
       </c>
       <c r="P15" s="15" t="n">
-        <v>-0.381</v>
+        <v>-0.442</v>
       </c>
       <c r="Q15" s="15" t="n">
         <v>1</v>
@@ -2575,52 +2575,52 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>4.671</v>
+        <v>4.51</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>0.493</v>
+        <v>0.413</v>
       </c>
       <c r="D16" s="15" t="n">
         <v>0.9</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>0.061</v>
+        <v>-0.062</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>0.105</v>
+        <v>0.015</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>-0.031</v>
+        <v>-0.097</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-0.019</v>
+        <v>0.03</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>0.03</v>
+        <v>-0.074</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>0.142</v>
+        <v>0.01</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>-0.033</v>
+        <v>0.002</v>
       </c>
       <c r="L16" s="15" t="n">
-        <v>0.06</v>
+        <v>0.048</v>
       </c>
       <c r="M16" s="15" t="n">
-        <v>-0.015</v>
+        <v>0.044</v>
       </c>
       <c r="N16" s="15" t="n">
-        <v>-0.136</v>
+        <v>-0.152</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>0.044</v>
+        <v>0.037</v>
       </c>
       <c r="P16" s="15" t="n">
-        <v>-0.032</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="Q16" s="15" t="n">
-        <v>0.051</v>
+        <v>-0.096</v>
       </c>
       <c r="R16" s="15" t="n">
         <v>1</v>
@@ -2636,55 +2636,55 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>4.701</v>
+        <v>4.543</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>0.97</v>
+        <v>0.799</v>
       </c>
       <c r="D17" s="15" t="n">
         <v>0.9</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>0.04</v>
+        <v>-0.006</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>0.023</v>
+        <v>-0.014</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>0.03</v>
+        <v>0.092</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>0.008</v>
+        <v>0.052</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>0.05</v>
+        <v>-0.005</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>-0.012</v>
+        <v>-0.039</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>-0.256</v>
+        <v>-0.28</v>
       </c>
       <c r="M17" s="15" t="n">
-        <v>0.326</v>
+        <v>0.22</v>
       </c>
       <c r="N17" s="15" t="n">
-        <v>0.027</v>
+        <v>0.01</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>0.036</v>
+        <v>-0.005</v>
       </c>
       <c r="P17" s="15" t="n">
-        <v>0.678</v>
+        <v>0.706</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>-0.643</v>
+        <v>-0.657</v>
       </c>
       <c r="R17" s="15" t="n">
-        <v>-0.077</v>
+        <v>0.024</v>
       </c>
       <c r="S17" s="15" t="n">
         <v>1</v>
@@ -2699,58 +2699,58 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>4.758</v>
+        <v>4.866</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>1.17</v>
+        <v>1.239</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>0.92</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>-0.122</v>
+        <v>-0.079</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>0.081</v>
+        <v>0.008</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>-0.074</v>
+        <v>-0.003</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>0.036</v>
+        <v>0.04</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-0.096</v>
+        <v>-0.052</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>0.033</v>
+        <v>0.021</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>-0.074</v>
+        <v>-0.049</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>-0.365</v>
+        <v>-0.267</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>0.43</v>
+        <v>0.35</v>
       </c>
       <c r="N18" s="15" t="n">
-        <v>0.004</v>
+        <v>0.079</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>0.019</v>
+        <v>0.067</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0.398</v>
+        <v>0.302</v>
       </c>
       <c r="Q18" s="15" t="n">
-        <v>-0.341</v>
+        <v>-0.319</v>
       </c>
       <c r="R18" s="15" t="n">
-        <v>-0.022</v>
+        <v>0.02</v>
       </c>
       <c r="S18" s="15" t="n">
-        <v>0.332</v>
+        <v>0.307</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>1</v>
@@ -2764,61 +2764,61 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>2.381</v>
+        <v>2.361</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>1.007</v>
+        <v>1.062</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>0.89</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>0.105</v>
+        <v>0.027</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>-0.017</v>
+        <v>0.03</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>-0.053</v>
+        <v>0.033</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>0.065</v>
+        <v>0.022</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>0.08</v>
+        <v>0.019</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>-0.032</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>0.068</v>
+        <v>0.029</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>0.317</v>
+        <v>0.3</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>-0.336</v>
+        <v>-0.292</v>
       </c>
       <c r="N19" s="15" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.061</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>0.019</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>-0.286</v>
+        <v>-0.379</v>
       </c>
       <c r="Q19" s="15" t="n">
-        <v>0.356</v>
+        <v>0.333</v>
       </c>
       <c r="R19" s="15" t="n">
-        <v>-0.008</v>
+        <v>-0.157</v>
       </c>
       <c r="S19" s="15" t="n">
-        <v>-0.241</v>
+        <v>-0.315</v>
       </c>
       <c r="T19" s="15" t="n">
-        <v>-0.398</v>
+        <v>-0.463</v>
       </c>
       <c r="U19" s="15" t="n">
         <v>1</v>

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>30.856</v>
+        <v>30.536</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>4.648</v>
+        <v>4.571</v>
       </c>
       <c r="D3" s="15" t="inlineStr"/>
       <c r="E3" s="15" t="n">
@@ -2011,14 +2011,14 @@
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>0.548</v>
+        <v>0.536</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>0.498</v>
+        <v>0.499</v>
       </c>
       <c r="D4" s="15" t="inlineStr"/>
       <c r="E4" s="15" t="n">
-        <v>0.062</v>
+        <v>0.007</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>1</v>
@@ -2046,17 +2046,17 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>3.121</v>
+        <v>3.104</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>0.952</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="D5" s="15" t="inlineStr"/>
       <c r="E5" s="15" t="n">
-        <v>0.002</v>
+        <v>0.018</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.042</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>1</v>
@@ -2083,20 +2083,20 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>2.549</v>
+        <v>2.542</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>1.135</v>
+        <v>1.129</v>
       </c>
       <c r="D6" s="15" t="inlineStr"/>
       <c r="E6" s="15" t="n">
-        <v>-0.021</v>
+        <v>-0.046</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>-0.03</v>
+        <v>-0.062</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>-0.028</v>
+        <v>-0.014</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>1</v>
@@ -2122,23 +2122,23 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>9.093999999999999</v>
+        <v>8.704000000000001</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>4.842</v>
+        <v>4.727</v>
       </c>
       <c r="D7" s="15" t="inlineStr"/>
       <c r="E7" s="15" t="n">
-        <v>0.905</v>
+        <v>0.9</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0.04</v>
+        <v>-0.023</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0.002</v>
+        <v>0.016</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>0.001</v>
+        <v>-0.027</v>
       </c>
       <c r="I7" s="15" t="n">
         <v>1</v>
@@ -2163,26 +2163,26 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>2.334</v>
+        <v>2.315</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>1.506</v>
+        <v>1.481</v>
       </c>
       <c r="D8" s="15" t="inlineStr"/>
       <c r="E8" s="15" t="n">
-        <v>0.188</v>
+        <v>0.191</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0.014</v>
+        <v>0.002</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>-0.028</v>
+        <v>-0.038</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>0.024</v>
+        <v>0.013</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>0.151</v>
+        <v>0.157</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>1</v>
@@ -2206,29 +2206,29 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>3.244</v>
+        <v>3.282</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>1.076</v>
+        <v>1.083</v>
       </c>
       <c r="D9" s="15" t="inlineStr"/>
       <c r="E9" s="15" t="n">
-        <v>-0.025</v>
+        <v>-0.012</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.066</v>
+        <v>0.089</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>-0.073</v>
+        <v>-0.051</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-0.066</v>
+        <v>-0.061</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>-0.042</v>
+        <v>-0.043</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>1</v>
@@ -2251,34 +2251,34 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>4.06</v>
+        <v>4.051</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.593</v>
+        <v>0.609</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0.91</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>0.006</v>
+        <v>0.022</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>-0.007</v>
+        <v>0.041</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.064</v>
+        <v>0.066</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-0.093</v>
+        <v>-0.065</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-0.036</v>
+        <v>-0.029</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>0.034</v>
+        <v>0.026</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>0.036</v>
+        <v>0.051</v>
       </c>
       <c r="L10" s="15" t="n">
         <v>1</v>
@@ -2300,37 +2300,37 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>5.013</v>
+        <v>5.018</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0.575</v>
+        <v>0.53</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>0.93</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>-0.042</v>
+        <v>-0.04</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>-0.025</v>
+        <v>0.004</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.035</v>
+        <v>0.051</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-0.079</v>
+        <v>-0.077</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>0.004</v>
+        <v>-0.01</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>-0.067</v>
+        <v>-0.037</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>-0.063</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>-0.052</v>
+        <v>-0.131</v>
       </c>
       <c r="M11" s="15" t="n">
         <v>1</v>
@@ -2351,40 +2351,40 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>3.43</v>
+        <v>3.428</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.894</v>
+        <v>0.916</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>-0.01</v>
+        <v>0.001</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>-0.047</v>
+        <v>-0.062</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>-0.018</v>
+        <v>-0.048</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>0.05</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>0.055</v>
+        <v>0.06</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>0.091</v>
+        <v>0.059</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>-0.02</v>
+        <v>-0.028</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>0.063</v>
+        <v>0.03</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.017</v>
       </c>
       <c r="N12" s="15" t="n">
         <v>1</v>
@@ -2404,43 +2404,43 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>4.599</v>
+        <v>4.617</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.888</v>
+        <v>0.884</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>0.84</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>-0.083</v>
+        <v>-0.046</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>-0.101</v>
+        <v>-0.058</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>-0.04</v>
+        <v>-0.038</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>0.049</v>
+        <v>0.053</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-0.056</v>
+        <v>-0.027</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>-0.076</v>
+        <v>-0.082</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>-0.075</v>
+        <v>-0.06</v>
       </c>
       <c r="L13" s="15" t="n">
-        <v>-0.049</v>
+        <v>-0.033</v>
       </c>
       <c r="M13" s="15" t="n">
-        <v>-0.032</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="N13" s="15" t="n">
-        <v>-0.024</v>
+        <v>-0.014</v>
       </c>
       <c r="O13" s="15" t="n">
         <v>1</v>
@@ -2459,46 +2459,46 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>4.474</v>
+        <v>4.524</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>1.207</v>
+        <v>1.186</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>0.88</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>-0.002</v>
+        <v>-0.04</v>
       </c>
       <c r="F14" s="15" t="n">
+        <v>-0.029</v>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="H14" s="15" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J14" s="15" t="n">
+        <v>-0.048</v>
+      </c>
+      <c r="K14" s="15" t="n">
+        <v>-0.08599999999999999</v>
+      </c>
+      <c r="L14" s="15" t="n">
+        <v>-0.354</v>
+      </c>
+      <c r="M14" s="15" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="N14" s="15" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="O14" s="15" t="n">
         <v>-0.05</v>
-      </c>
-      <c r="G14" s="15" t="n">
-        <v>-0.023</v>
-      </c>
-      <c r="H14" s="15" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="I14" s="15" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="J14" s="15" t="n">
-        <v>-0.078</v>
-      </c>
-      <c r="K14" s="15" t="n">
-        <v>-0.079</v>
-      </c>
-      <c r="L14" s="15" t="n">
-        <v>-0.324</v>
-      </c>
-      <c r="M14" s="15" t="n">
-        <v>0.343</v>
-      </c>
-      <c r="N14" s="15" t="n">
-        <v>-0.034</v>
-      </c>
-      <c r="O14" s="15" t="n">
-        <v>-0.03</v>
       </c>
       <c r="P14" s="15" t="n">
         <v>1</v>
@@ -2516,49 +2516,49 @@
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>2.998</v>
+        <v>2.966</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>1.126</v>
+        <v>1.131</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>0.87</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>0.016</v>
+        <v>0.014</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>-0.002</v>
+        <v>0.007</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0.001</v>
+        <v>-0.019</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-0.039</v>
+        <v>-0.038</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-0.045</v>
+        <v>-0.038</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>0.01</v>
+        <v>0.039</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>0.082</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>0.259</v>
+        <v>0.321</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.238</v>
+        <v>-0.251</v>
       </c>
       <c r="N15" s="15" t="n">
-        <v>0.064</v>
+        <v>0.045</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.099</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="P15" s="15" t="n">
-        <v>-0.442</v>
+        <v>-0.444</v>
       </c>
       <c r="Q15" s="15" t="n">
         <v>1</v>
@@ -2575,52 +2575,52 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>4.51</v>
+        <v>4.501</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>0.413</v>
+        <v>0.403</v>
       </c>
       <c r="D16" s="15" t="n">
         <v>0.9</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>-0.062</v>
+        <v>-0.041</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>-0.097</v>
+        <v>-0.066</v>
       </c>
       <c r="H16" s="15" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>-0.059</v>
+      </c>
+      <c r="J16" s="15" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="K16" s="15" t="n">
+        <v>-0.031</v>
+      </c>
+      <c r="L16" s="15" t="n">
         <v>0.03</v>
       </c>
-      <c r="I16" s="15" t="n">
-        <v>-0.074</v>
-      </c>
-      <c r="J16" s="15" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K16" s="15" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="L16" s="15" t="n">
-        <v>0.048</v>
-      </c>
       <c r="M16" s="15" t="n">
-        <v>0.044</v>
+        <v>0.024</v>
       </c>
       <c r="N16" s="15" t="n">
-        <v>-0.152</v>
+        <v>-0.153</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>0.037</v>
+        <v>0.097</v>
       </c>
       <c r="P16" s="15" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.061</v>
       </c>
       <c r="Q16" s="15" t="n">
-        <v>-0.096</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="R16" s="15" t="n">
         <v>1</v>
@@ -2636,55 +2636,55 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>4.543</v>
+        <v>4.538</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>0.799</v>
+        <v>0.832</v>
       </c>
       <c r="D17" s="15" t="n">
         <v>0.9</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>-0.006</v>
+        <v>-0.027</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>-0.03</v>
+        <v>0.018</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>-0.014</v>
+        <v>-0.028</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>0.092</v>
+        <v>0.06</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>0.052</v>
+        <v>0.028</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>-0.005</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>-0.039</v>
+        <v>-0.053</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>-0.28</v>
+        <v>-0.309</v>
       </c>
       <c r="M17" s="15" t="n">
-        <v>0.22</v>
+        <v>0.247</v>
       </c>
       <c r="N17" s="15" t="n">
-        <v>0.01</v>
+        <v>0.034</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>-0.005</v>
+        <v>0.063</v>
       </c>
       <c r="P17" s="15" t="n">
-        <v>0.706</v>
+        <v>0.699</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>-0.657</v>
+        <v>-0.643</v>
       </c>
       <c r="R17" s="15" t="n">
-        <v>0.024</v>
+        <v>0.028</v>
       </c>
       <c r="S17" s="15" t="n">
         <v>1</v>
@@ -2699,58 +2699,58 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>4.866</v>
+        <v>4.785</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>1.239</v>
+        <v>1.261</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>0.92</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>-0.079</v>
+        <v>-0.013</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>0.008</v>
+        <v>-0.012</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>-0.003</v>
+        <v>-0.065</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-0.052</v>
+        <v>0.026</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>0.021</v>
+        <v>-0.017</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>-0.049</v>
+        <v>-0.038</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>-0.267</v>
+        <v>-0.407</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>0.35</v>
+        <v>0.342</v>
       </c>
       <c r="N18" s="15" t="n">
-        <v>0.079</v>
+        <v>-0.008</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>0.067</v>
+        <v>-0.028</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0.302</v>
+        <v>0.339</v>
       </c>
       <c r="Q18" s="15" t="n">
-        <v>-0.319</v>
+        <v>-0.375</v>
       </c>
       <c r="R18" s="15" t="n">
-        <v>0.02</v>
+        <v>-0.014</v>
       </c>
       <c r="S18" s="15" t="n">
-        <v>0.307</v>
+        <v>0.321</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>1</v>
@@ -2764,61 +2764,61 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>2.361</v>
+        <v>2.396</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>1.062</v>
+        <v>1.127</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>0.89</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>0.027</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>0.03</v>
+        <v>0.062</v>
       </c>
       <c r="G19" s="15" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>-0.052</v>
+      </c>
+      <c r="I19" s="15" t="n">
         <v>0.033</v>
       </c>
-      <c r="H19" s="15" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="I19" s="15" t="n">
-        <v>0.019</v>
-      </c>
       <c r="J19" s="15" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.078</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>0.029</v>
+        <v>0.025</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>0.3</v>
+        <v>0.469</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>-0.292</v>
+        <v>-0.279</v>
       </c>
       <c r="N19" s="15" t="n">
-        <v>0.061</v>
+        <v>-0.015</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.06</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>-0.379</v>
+        <v>-0.406</v>
       </c>
       <c r="Q19" s="15" t="n">
-        <v>0.333</v>
+        <v>0.364</v>
       </c>
       <c r="R19" s="15" t="n">
-        <v>-0.157</v>
+        <v>-0.11</v>
       </c>
       <c r="S19" s="15" t="n">
-        <v>-0.315</v>
+        <v>-0.409</v>
       </c>
       <c r="T19" s="15" t="n">
-        <v>-0.463</v>
+        <v>-0.441</v>
       </c>
       <c r="U19" s="15" t="n">
         <v>1</v>

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -672,7 +672,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -731,6 +731,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1421,7 +1424,7 @@
           <t>Seven-factor model: Autocratic leadership, empowering leadership, follower narcissism, power distance, benign envy, malicious envy, and thriving</t>
         </is>
       </c>
-      <c r="B3" s="15" t="n">
+      <c r="B3" s="20" t="n">
         <v>609.2</v>
       </c>
       <c r="C3" s="15" t="n">
@@ -1436,7 +1439,7 @@
       <c r="F3" s="15" t="n">
         <v>0.02</v>
       </c>
-      <c r="G3" s="15" t="n">
+      <c r="G3" s="20" t="n">
         <v>12586.4</v>
       </c>
       <c r="H3" s="15" t="n"/>
@@ -1448,7 +1451,7 @@
           <t>Six-factor model: benign envy and malicious envy as a single construct</t>
         </is>
       </c>
-      <c r="B4" s="15" t="n">
+      <c r="B4" s="20" t="n">
         <v>719.4</v>
       </c>
       <c r="C4" s="15" t="n">
@@ -1465,7 +1468,7 @@
       <c r="F4" s="15" t="n">
         <v>0.03</v>
       </c>
-      <c r="G4" s="15" t="n">
+      <c r="G4" s="20" t="n">
         <v>12694.6</v>
       </c>
       <c r="H4" s="15" t="n"/>
@@ -1477,7 +1480,7 @@
           <t>Five-factor model: autocratic leadership and empowering leadership as a single construct; benign envy and malicious envy as a single construct</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n">
+      <c r="B5" s="20" t="n">
         <v>875</v>
       </c>
       <c r="C5" s="15" t="n">
@@ -1494,7 +1497,7 @@
       <c r="F5" s="15" t="n">
         <v>0.041</v>
       </c>
-      <c r="G5" s="15" t="n">
+      <c r="G5" s="20" t="n">
         <v>12848.2</v>
       </c>
       <c r="H5" s="15" t="n"/>
@@ -1506,7 +1509,7 @@
           <t>Four-factor model: follower narcissism and power distance as a single construct; autocratic leadership and empowering leadership as a single construct; benign envy and malicious envy as a single construct</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B6" s="20" t="n">
         <v>1051.6</v>
       </c>
       <c r="C6" s="15" t="n">
@@ -1523,7 +1526,7 @@
       <c r="F6" s="15" t="n">
         <v>0.05</v>
       </c>
-      <c r="G6" s="15" t="n">
+      <c r="G6" s="20" t="n">
         <v>13022.8</v>
       </c>
       <c r="H6" s="15" t="n"/>
@@ -1535,7 +1538,7 @@
           <t>Three-factor model: follower narcissism, power distance, benign envy, and malicious envy as a single construct; autocratic leadership and empowering leadership as a single construct; thriving as a separate construct</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="20" t="n">
         <v>1226.5</v>
       </c>
       <c r="C7" s="15" t="n">
@@ -1552,7 +1555,7 @@
       <c r="F7" s="15" t="n">
         <v>0.058</v>
       </c>
-      <c r="G7" s="15" t="n">
+      <c r="G7" s="20" t="n">
         <v>13195.7</v>
       </c>
       <c r="H7" s="15" t="n"/>
@@ -1564,7 +1567,7 @@
           <t>Two-factor model: follower narcissism, power distance, benign envy, malicious envy, and thriving as a single construct; autocratic leadership and empowering leadership as a single construct</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="20" t="n">
         <v>1397.5</v>
       </c>
       <c r="C8" s="15" t="n">
@@ -1581,7 +1584,7 @@
       <c r="F8" s="15" t="n">
         <v>0.064</v>
       </c>
-      <c r="G8" s="15" t="n">
+      <c r="G8" s="20" t="n">
         <v>13364.7</v>
       </c>
       <c r="H8" s="15" t="n"/>
@@ -1593,7 +1596,7 @@
           <t>Single-factor model: all constructs as a single construct</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="20" t="n">
         <v>1736</v>
       </c>
       <c r="C9" s="15" t="n">
@@ -1610,7 +1613,7 @@
       <c r="F9" s="15" t="n">
         <v>0.075</v>
       </c>
-      <c r="G9" s="15" t="n">
+      <c r="G9" s="20" t="n">
         <v>13701.2</v>
       </c>
     </row>
@@ -1978,10 +1981,10 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>30.536</v>
+        <v>30.674</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>4.571</v>
+        <v>4.641</v>
       </c>
       <c r="D3" s="15" t="inlineStr"/>
       <c r="E3" s="15" t="n">
@@ -2011,14 +2014,14 @@
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>0.536</v>
+        <v>0.552</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>0.499</v>
+        <v>0.498</v>
       </c>
       <c r="D4" s="15" t="inlineStr"/>
       <c r="E4" s="15" t="n">
-        <v>0.007</v>
+        <v>0.048</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>1</v>
@@ -2046,17 +2049,17 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>3.104</v>
+        <v>3.106</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.944</v>
       </c>
       <c r="D5" s="15" t="inlineStr"/>
       <c r="E5" s="15" t="n">
-        <v>0.018</v>
+        <v>0.001</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>-0.042</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>1</v>
@@ -2083,20 +2086,20 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>2.542</v>
+        <v>2.543</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>1.129</v>
+        <v>1.13</v>
       </c>
       <c r="D6" s="15" t="inlineStr"/>
       <c r="E6" s="15" t="n">
-        <v>-0.046</v>
+        <v>-0.017</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>-0.062</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>-0.014</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>1</v>
@@ -2122,23 +2125,23 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>8.704000000000001</v>
+        <v>8.895</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>4.727</v>
+        <v>4.843</v>
       </c>
       <c r="D7" s="15" t="inlineStr"/>
       <c r="E7" s="15" t="n">
         <v>0.9</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>-0.023</v>
+        <v>0.015</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0.016</v>
+        <v>0.001</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-0.027</v>
+        <v>0.005</v>
       </c>
       <c r="I7" s="15" t="n">
         <v>1</v>
@@ -2163,26 +2166,26 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>2.315</v>
+        <v>2.314</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>1.481</v>
+        <v>1.504</v>
       </c>
       <c r="D8" s="15" t="inlineStr"/>
       <c r="E8" s="15" t="n">
-        <v>0.191</v>
+        <v>0.202</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0.002</v>
+        <v>-0.014</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>-0.038</v>
+        <v>-0.043</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>0.013</v>
+        <v>0.005</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>0.157</v>
+        <v>0.163</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>1</v>
@@ -2206,29 +2209,29 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>3.282</v>
+        <v>3.296</v>
       </c>
       <c r="C9" s="15" t="n">
         <v>1.083</v>
       </c>
       <c r="D9" s="15" t="inlineStr"/>
       <c r="E9" s="15" t="n">
-        <v>-0.012</v>
+        <v>0.004</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.089</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>-0.051</v>
+        <v>-0.041</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-0.061</v>
+        <v>-0.077</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.015</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>-0.043</v>
+        <v>-0.036</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>1</v>
@@ -2251,34 +2254,34 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>4.051</v>
+        <v>4.077</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.609</v>
+        <v>0.618</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0.91</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>0.022</v>
+        <v>0.026</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0.041</v>
+        <v>0.052</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.066</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-0.065</v>
+        <v>-0.06</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-0.029</v>
+        <v>-0.021</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>0.026</v>
+        <v>0.053</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>0.051</v>
+        <v>0.061</v>
       </c>
       <c r="L10" s="15" t="n">
         <v>1</v>
@@ -2300,37 +2303,37 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>5.018</v>
+        <v>5.004</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0.53</v>
+        <v>0.575</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>0.93</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>-0.04</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0.004</v>
+        <v>-0.012</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.051</v>
+        <v>0.079</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-0.077</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-0.01</v>
+        <v>-0.025</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>-0.037</v>
+        <v>-0.05</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.063</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>-0.131</v>
+        <v>-0.1</v>
       </c>
       <c r="M11" s="15" t="n">
         <v>1</v>
@@ -2351,40 +2354,40 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>3.428</v>
+        <v>3.44</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.916</v>
+        <v>0.924</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>0.001</v>
+        <v>-0.024</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>-0.062</v>
+        <v>-0.099</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>-0.048</v>
+        <v>-0.04</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.074</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>0.06</v>
+        <v>0.037</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>0.059</v>
+        <v>0.075</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>-0.028</v>
+        <v>-0.051</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>0.03</v>
+        <v>0.033</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>0.017</v>
+        <v>0.034</v>
       </c>
       <c r="N12" s="15" t="n">
         <v>1</v>
@@ -2404,43 +2407,43 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>4.617</v>
+        <v>4.604</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.884</v>
+        <v>0.886</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>0.84</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>-0.046</v>
+        <v>-0.055</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>-0.058</v>
+        <v>-0.081</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>-0.038</v>
+        <v>-0.051</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>0.053</v>
+        <v>0.081</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-0.027</v>
+        <v>-0.041</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>-0.082</v>
+        <v>-0.097</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>-0.06</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="L13" s="15" t="n">
-        <v>-0.033</v>
+        <v>-0.043</v>
       </c>
       <c r="M13" s="15" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.039</v>
       </c>
       <c r="N13" s="15" t="n">
-        <v>-0.014</v>
+        <v>0.001</v>
       </c>
       <c r="O13" s="15" t="n">
         <v>1</v>
@@ -2459,46 +2462,46 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>4.524</v>
+        <v>4.476</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>1.186</v>
+        <v>1.207</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>0.88</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>-0.04</v>
+        <v>-0.019</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>-0.029</v>
+        <v>-0.038</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>-0.044</v>
+        <v>-0.037</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>0.014</v>
+        <v>0.023</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>0.02</v>
+        <v>0.042</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>-0.048</v>
+        <v>-0.061</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.074</v>
       </c>
       <c r="L14" s="15" t="n">
-        <v>-0.354</v>
+        <v>-0.339</v>
       </c>
       <c r="M14" s="15" t="n">
-        <v>0.311</v>
+        <v>0.328</v>
       </c>
       <c r="N14" s="15" t="n">
         <v>-0.001</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>-0.05</v>
+        <v>-0.048</v>
       </c>
       <c r="P14" s="15" t="n">
         <v>1</v>
@@ -2516,49 +2519,49 @@
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>2.966</v>
+        <v>3.013</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>1.131</v>
+        <v>1.128</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>0.87</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>0.014</v>
+        <v>0.018</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0.007</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>-0.019</v>
+        <v>-0.024</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-0.038</v>
+        <v>-0.034</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-0.038</v>
+        <v>-0.037</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>0.039</v>
+        <v>0.022</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.065</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>0.321</v>
+        <v>0.293</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.251</v>
+        <v>-0.276</v>
       </c>
       <c r="N15" s="15" t="n">
-        <v>0.045</v>
+        <v>0.025</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.101</v>
       </c>
       <c r="P15" s="15" t="n">
-        <v>-0.444</v>
+        <v>-0.43</v>
       </c>
       <c r="Q15" s="15" t="n">
         <v>1</v>
@@ -2575,52 +2578,52 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>4.501</v>
+        <v>4.495</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>0.403</v>
+        <v>0.404</v>
       </c>
       <c r="D16" s="15" t="n">
         <v>0.9</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>-0.041</v>
+        <v>-0.022</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>-0.066</v>
+        <v>-0.077</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>0.032</v>
+        <v>0.017</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-0.059</v>
+        <v>-0.04</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>0.031</v>
+        <v>0.018</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>-0.031</v>
+        <v>-0.02</v>
       </c>
       <c r="L16" s="15" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="M16" s="15" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="N16" s="15" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="O16" s="15" t="n">
         <v>0.024</v>
       </c>
-      <c r="N16" s="15" t="n">
-        <v>-0.153</v>
-      </c>
-      <c r="O16" s="15" t="n">
-        <v>0.097</v>
-      </c>
       <c r="P16" s="15" t="n">
-        <v>0.061</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="Q16" s="15" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.094</v>
       </c>
       <c r="R16" s="15" t="n">
         <v>1</v>
@@ -2636,55 +2639,55 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>4.538</v>
+        <v>4.554</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>0.832</v>
+        <v>0.806</v>
       </c>
       <c r="D17" s="15" t="n">
         <v>0.9</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>-0.027</v>
+        <v>0.004</v>
       </c>
       <c r="F17" s="15" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>-0.031</v>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="J17" s="15" t="n">
         <v>0.018</v>
       </c>
-      <c r="G17" s="15" t="n">
-        <v>-0.028</v>
-      </c>
-      <c r="H17" s="15" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I17" s="15" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="J17" s="15" t="n">
-        <v>-0.008999999999999999</v>
-      </c>
       <c r="K17" s="15" t="n">
-        <v>-0.053</v>
+        <v>-0.063</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>-0.309</v>
+        <v>-0.223</v>
       </c>
       <c r="M17" s="15" t="n">
-        <v>0.247</v>
+        <v>0.29</v>
       </c>
       <c r="N17" s="15" t="n">
-        <v>0.034</v>
+        <v>-0.001</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>0.063</v>
+        <v>0.003</v>
       </c>
       <c r="P17" s="15" t="n">
-        <v>0.699</v>
+        <v>0.708</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>-0.643</v>
+        <v>-0.619</v>
       </c>
       <c r="R17" s="15" t="n">
-        <v>0.028</v>
+        <v>0.117</v>
       </c>
       <c r="S17" s="15" t="n">
         <v>1</v>
@@ -2699,58 +2702,58 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>4.785</v>
+        <v>4.828</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>1.261</v>
+        <v>1.315</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>0.92</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>-0.013</v>
+        <v>-0.138</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>-0.012</v>
+        <v>0.037</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>-0.065</v>
+        <v>-0.106</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-0.01</v>
+        <v>0.002</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>0.026</v>
+        <v>-0.104</v>
       </c>
       <c r="J18" s="15" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="K18" s="15" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="L18" s="15" t="n">
+        <v>-0.412</v>
+      </c>
+      <c r="M18" s="15" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="N18" s="15" t="n">
         <v>-0.017</v>
       </c>
-      <c r="K18" s="15" t="n">
-        <v>-0.038</v>
-      </c>
-      <c r="L18" s="15" t="n">
-        <v>-0.407</v>
-      </c>
-      <c r="M18" s="15" t="n">
-        <v>0.342</v>
-      </c>
-      <c r="N18" s="15" t="n">
-        <v>-0.008</v>
-      </c>
       <c r="O18" s="15" t="n">
-        <v>-0.028</v>
+        <v>-0.033</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0.339</v>
+        <v>0.402</v>
       </c>
       <c r="Q18" s="15" t="n">
-        <v>-0.375</v>
+        <v>-0.372</v>
       </c>
       <c r="R18" s="15" t="n">
-        <v>-0.014</v>
+        <v>0.105</v>
       </c>
       <c r="S18" s="15" t="n">
-        <v>0.321</v>
+        <v>0.373</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>1</v>
@@ -2764,61 +2767,61 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>2.396</v>
+        <v>2.418</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>1.127</v>
+        <v>1.145</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>0.89</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.008</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>0.062</v>
+        <v>0.111</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>0.064</v>
+        <v>0.034</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-0.052</v>
+        <v>0.03</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>0.033</v>
+        <v>-0.045</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>-0.078</v>
+        <v>-0.037</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>0.025</v>
+        <v>0.044</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>0.469</v>
+        <v>0.475</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>-0.279</v>
+        <v>-0.293</v>
       </c>
       <c r="N19" s="15" t="n">
-        <v>-0.015</v>
+        <v>-0.007</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>-0.06</v>
+        <v>-0.041</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>-0.406</v>
+        <v>-0.346</v>
       </c>
       <c r="Q19" s="15" t="n">
-        <v>0.364</v>
+        <v>0.333</v>
       </c>
       <c r="R19" s="15" t="n">
-        <v>-0.11</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="S19" s="15" t="n">
-        <v>-0.409</v>
+        <v>-0.327</v>
       </c>
       <c r="T19" s="15" t="n">
-        <v>-0.441</v>
+        <v>-0.371</v>
       </c>
       <c r="U19" s="15" t="n">
         <v>1</v>

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>30.674</v>
+        <v>30.609</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>4.641</v>
+        <v>4.651</v>
       </c>
       <c r="D3" s="15" t="inlineStr"/>
       <c r="E3" s="15" t="n">
@@ -2014,14 +2014,14 @@
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>0.552</v>
+        <v>0.546</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>0.498</v>
+        <v>0.499</v>
       </c>
       <c r="D4" s="15" t="inlineStr"/>
       <c r="E4" s="15" t="n">
-        <v>0.048</v>
+        <v>0.042</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>1</v>
@@ -2049,17 +2049,17 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>3.106</v>
+        <v>3.126</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>0.944</v>
+        <v>0.93</v>
       </c>
       <c r="D5" s="15" t="inlineStr"/>
       <c r="E5" s="15" t="n">
-        <v>0.001</v>
+        <v>0.024</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.083</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>1</v>
@@ -2086,20 +2086,20 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>2.543</v>
+        <v>2.552</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>1.13</v>
+        <v>1.132</v>
       </c>
       <c r="D6" s="15" t="inlineStr"/>
       <c r="E6" s="15" t="n">
-        <v>-0.017</v>
+        <v>-0.007</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.04</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.016</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>1</v>
@@ -2125,23 +2125,23 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>8.895</v>
+        <v>8.853</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>4.843</v>
+        <v>4.824</v>
       </c>
       <c r="D7" s="15" t="inlineStr"/>
       <c r="E7" s="15" t="n">
-        <v>0.9</v>
+        <v>0.903</v>
       </c>
       <c r="F7" s="15" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G7" s="15" t="n">
         <v>0.015</v>
       </c>
-      <c r="G7" s="15" t="n">
-        <v>0.001</v>
-      </c>
       <c r="H7" s="15" t="n">
-        <v>0.005</v>
+        <v>0.014</v>
       </c>
       <c r="I7" s="15" t="n">
         <v>1</v>
@@ -2166,26 +2166,26 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>2.314</v>
+        <v>2.269</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>1.504</v>
+        <v>1.437</v>
       </c>
       <c r="D8" s="15" t="inlineStr"/>
       <c r="E8" s="15" t="n">
-        <v>0.202</v>
+        <v>0.183</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>-0.014</v>
+        <v>-0.002</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>-0.043</v>
+        <v>-0.047</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>0.163</v>
+        <v>0.156</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>1</v>
@@ -2209,29 +2209,29 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>3.296</v>
+        <v>3.283</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>1.083</v>
+        <v>1.082</v>
       </c>
       <c r="D9" s="15" t="inlineStr"/>
       <c r="E9" s="15" t="n">
-        <v>0.004</v>
+        <v>-0.024</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.115</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>-0.041</v>
+        <v>-0.075</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-0.077</v>
+        <v>-0.057</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>0.015</v>
+        <v>-0.013</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>-0.036</v>
+        <v>-0.058</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>1</v>
@@ -2254,34 +2254,34 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>4.077</v>
+        <v>4.029</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.618</v>
+        <v>0.611</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0.91</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>0.026</v>
+        <v>0.001</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0.052</v>
+        <v>0.017</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.077</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-0.06</v>
+        <v>-0.089</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-0.021</v>
+        <v>-0.039</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>0.053</v>
+        <v>0.003</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>0.061</v>
+        <v>0.022</v>
       </c>
       <c r="L10" s="15" t="n">
         <v>1</v>
@@ -2303,37 +2303,37 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>5.004</v>
+        <v>5</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0.575</v>
+        <v>0.57</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>0.93</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.048</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>-0.012</v>
+        <v>-0.051</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.079</v>
+        <v>0.04</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.059</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-0.025</v>
+        <v>0.004</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>-0.05</v>
+        <v>-0.079</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>-0.063</v>
+        <v>-0.064</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>-0.1</v>
+        <v>-0.127</v>
       </c>
       <c r="M11" s="15" t="n">
         <v>1</v>
@@ -2354,40 +2354,40 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>3.44</v>
+        <v>3.438</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.924</v>
+        <v>0.906</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>-0.024</v>
+        <v>-0.038</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>-0.099</v>
+        <v>-0.041</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>0.074</v>
+        <v>0.054</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>0.037</v>
+        <v>0.048</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>0.075</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>-0.051</v>
+        <v>-0.045</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>0.033</v>
+        <v>0.005</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>0.034</v>
+        <v>0.053</v>
       </c>
       <c r="N12" s="15" t="n">
         <v>1</v>
@@ -2407,43 +2407,43 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>4.604</v>
+        <v>4.575</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.886</v>
+        <v>0.897</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>0.84</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>-0.055</v>
+        <v>-0.079</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>-0.081</v>
+        <v>-0.107</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>-0.051</v>
+        <v>-0.019</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>0.081</v>
+        <v>0.052</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-0.041</v>
+        <v>-0.056</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>-0.097</v>
+        <v>-0.056</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="L13" s="15" t="n">
-        <v>-0.043</v>
+        <v>-0.002</v>
       </c>
       <c r="M13" s="15" t="n">
-        <v>-0.039</v>
+        <v>-0.04</v>
       </c>
       <c r="N13" s="15" t="n">
-        <v>0.001</v>
+        <v>-0.018</v>
       </c>
       <c r="O13" s="15" t="n">
         <v>1</v>
@@ -2462,46 +2462,46 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>4.476</v>
+        <v>4.471</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>1.207</v>
+        <v>1.194</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>0.88</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>-0.019</v>
+        <v>0.003</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>-0.038</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>-0.037</v>
+        <v>-0.036</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>0.023</v>
+        <v>0.053</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>0.042</v>
+        <v>0.068</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>-0.061</v>
+        <v>-0.053</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>-0.074</v>
+        <v>-0.048</v>
       </c>
       <c r="L14" s="15" t="n">
-        <v>-0.339</v>
+        <v>-0.356</v>
       </c>
       <c r="M14" s="15" t="n">
-        <v>0.328</v>
+        <v>0.336</v>
       </c>
       <c r="N14" s="15" t="n">
-        <v>-0.001</v>
+        <v>-0.008</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>-0.048</v>
+        <v>-0.051</v>
       </c>
       <c r="P14" s="15" t="n">
         <v>1</v>
@@ -2519,49 +2519,49 @@
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>3.013</v>
+        <v>2.977</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>1.128</v>
+        <v>1.137</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>0.87</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>0.018</v>
+        <v>0.016</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0.007</v>
+        <v>0.025</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>-0.024</v>
+        <v>-0.03</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-0.034</v>
+        <v>-0.052</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-0.037</v>
+        <v>-0.039</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>0.022</v>
+        <v>0.047</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>0.065</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>0.293</v>
+        <v>0.319</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.276</v>
+        <v>-0.302</v>
       </c>
       <c r="N15" s="15" t="n">
-        <v>0.025</v>
+        <v>0.049</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.101</v>
+        <v>-0.092</v>
       </c>
       <c r="P15" s="15" t="n">
-        <v>-0.43</v>
+        <v>-0.457</v>
       </c>
       <c r="Q15" s="15" t="n">
         <v>1</v>
@@ -2578,52 +2578,52 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>4.495</v>
+        <v>4.505</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>0.404</v>
+        <v>0.403</v>
       </c>
       <c r="D16" s="15" t="n">
         <v>0.9</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>-0.022</v>
+        <v>-0.036</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>-0.077</v>
+        <v>-0.091</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>0.017</v>
+        <v>0.004</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-0.04</v>
+        <v>-0.037</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>0.018</v>
+        <v>0.015</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>-0.02</v>
+        <v>0.022</v>
       </c>
       <c r="L16" s="15" t="n">
-        <v>0.02</v>
+        <v>-0.004</v>
       </c>
       <c r="M16" s="15" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="N16" s="15" t="n">
+        <v>-0.175</v>
+      </c>
+      <c r="O16" s="15" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="P16" s="15" t="n">
         <v>0.075</v>
       </c>
-      <c r="N16" s="15" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="O16" s="15" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="P16" s="15" t="n">
-        <v>0.08400000000000001</v>
-      </c>
       <c r="Q16" s="15" t="n">
-        <v>-0.094</v>
+        <v>-0.095</v>
       </c>
       <c r="R16" s="15" t="n">
         <v>1</v>
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>4.554</v>
+        <v>4.548</v>
       </c>
       <c r="C17" s="15" t="n">
         <v>0.806</v>
@@ -2648,46 +2648,46 @@
         <v>0.9</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>0.004</v>
+        <v>0.015</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>-0.042</v>
+        <v>0.011</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>-0.031</v>
+        <v>-0.047</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>0.058</v>
+        <v>0.03</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>0.043</v>
+        <v>0.06</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>0.018</v>
+        <v>0.028</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>-0.063</v>
+        <v>-0.081</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>-0.223</v>
+        <v>-0.355</v>
       </c>
       <c r="M17" s="15" t="n">
-        <v>0.29</v>
+        <v>0.285</v>
       </c>
       <c r="N17" s="15" t="n">
-        <v>-0.001</v>
+        <v>-0.052</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>0.003</v>
+        <v>0.04</v>
       </c>
       <c r="P17" s="15" t="n">
-        <v>0.708</v>
+        <v>0.677</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>-0.619</v>
+        <v>-0.6870000000000001</v>
       </c>
       <c r="R17" s="15" t="n">
-        <v>0.117</v>
+        <v>0.083</v>
       </c>
       <c r="S17" s="15" t="n">
         <v>1</v>
@@ -2702,58 +2702,58 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>4.828</v>
+        <v>4.814</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>1.315</v>
+        <v>1.368</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>0.92</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>-0.138</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>0.037</v>
+        <v>-0.056</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>-0.106</v>
+        <v>-0.002</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>0.002</v>
+        <v>-0.019</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-0.104</v>
+        <v>-0.074</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>-0.024</v>
+        <v>0.031</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>0.024</v>
+        <v>0.006</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>-0.412</v>
+        <v>-0.419</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>0.321</v>
+        <v>0.477</v>
       </c>
       <c r="N18" s="15" t="n">
-        <v>-0.017</v>
+        <v>0.053</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>-0.033</v>
+        <v>-0.047</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0.402</v>
+        <v>0.422</v>
       </c>
       <c r="Q18" s="15" t="n">
-        <v>-0.372</v>
+        <v>-0.432</v>
       </c>
       <c r="R18" s="15" t="n">
-        <v>0.105</v>
+        <v>0.062</v>
       </c>
       <c r="S18" s="15" t="n">
-        <v>0.373</v>
+        <v>0.397</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>1</v>
@@ -2767,61 +2767,61 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>2.418</v>
+        <v>2.416</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>1.145</v>
+        <v>1.168</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>0.89</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>0.008</v>
+        <v>0.047</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>0.111</v>
+        <v>0.076</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>0.034</v>
+        <v>0.027</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>0.03</v>
+        <v>-0.001</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-0.045</v>
+        <v>0.004</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>-0.037</v>
+        <v>-0.029</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>0.044</v>
+        <v>-0.003</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>0.475</v>
+        <v>0.43</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>-0.293</v>
+        <v>-0.493</v>
       </c>
       <c r="N19" s="15" t="n">
-        <v>-0.007</v>
+        <v>-0.034</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>-0.041</v>
+        <v>-0.039</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>-0.346</v>
+        <v>-0.424</v>
       </c>
       <c r="Q19" s="15" t="n">
-        <v>0.333</v>
+        <v>0.451</v>
       </c>
       <c r="R19" s="15" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.108</v>
       </c>
       <c r="S19" s="15" t="n">
-        <v>-0.327</v>
+        <v>-0.407</v>
       </c>
       <c r="T19" s="15" t="n">
-        <v>-0.371</v>
+        <v>-0.697</v>
       </c>
       <c r="U19" s="15" t="n">
         <v>1</v>

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>30.609</v>
+        <v>30.699</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>4.651</v>
+        <v>4.675</v>
       </c>
       <c r="D3" s="15" t="inlineStr"/>
       <c r="E3" s="15" t="n">
@@ -2014,14 +2014,14 @@
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>0.546</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>0.499</v>
+        <v>0.497</v>
       </c>
       <c r="D4" s="15" t="inlineStr"/>
       <c r="E4" s="15" t="n">
-        <v>0.042</v>
+        <v>0.022</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>1</v>
@@ -2049,17 +2049,17 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>3.126</v>
+        <v>3.104</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>0.93</v>
+        <v>0.923</v>
       </c>
       <c r="D5" s="15" t="inlineStr"/>
       <c r="E5" s="15" t="n">
-        <v>0.024</v>
+        <v>0.006</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>-0.083</v>
+        <v>-0.073</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>1</v>
@@ -2086,20 +2086,20 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>2.552</v>
+        <v>2.568</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>1.132</v>
+        <v>1.131</v>
       </c>
       <c r="D6" s="15" t="inlineStr"/>
       <c r="E6" s="15" t="n">
-        <v>-0.007</v>
+        <v>0.007</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>-0.04</v>
+        <v>-0.036</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>-0.016</v>
+        <v>-0.025</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>1</v>
@@ -2125,23 +2125,23 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>8.853</v>
+        <v>8.948</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>4.824</v>
+        <v>4.88</v>
       </c>
       <c r="D7" s="15" t="inlineStr"/>
       <c r="E7" s="15" t="n">
-        <v>0.903</v>
+        <v>0.905</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0.018</v>
+        <v>-0.008</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0.015</v>
+        <v>-0.008</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>0.014</v>
+        <v>0.029</v>
       </c>
       <c r="I7" s="15" t="n">
         <v>1</v>
@@ -2166,26 +2166,26 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>2.269</v>
+        <v>2.297</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>1.437</v>
+        <v>1.468</v>
       </c>
       <c r="D8" s="15" t="inlineStr"/>
       <c r="E8" s="15" t="n">
-        <v>0.183</v>
+        <v>0.203</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>-0.002</v>
+        <v>-0.025</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>-0.047</v>
+        <v>-0.01</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>0</v>
+        <v>-0.004</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>0.156</v>
+        <v>0.173</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>1</v>
@@ -2209,29 +2209,29 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>3.283</v>
+        <v>3.249</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>1.082</v>
+        <v>1.06</v>
       </c>
       <c r="D9" s="15" t="inlineStr"/>
       <c r="E9" s="15" t="n">
-        <v>-0.024</v>
+        <v>-0.014</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.115</v>
+        <v>0.096</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>-0.075</v>
+        <v>-0.057</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-0.057</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-0.013</v>
+        <v>-0.005</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>-0.058</v>
+        <v>-0.049</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>1</v>
@@ -2254,34 +2254,34 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>4.029</v>
+        <v>4.04</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.611</v>
+        <v>0.623</v>
       </c>
       <c r="D10" s="15" t="n">
-        <v>0.91</v>
+        <v>0.86</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>0.001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0.017</v>
+        <v>-0.004</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.077</v>
+        <v>0.066</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-0.089</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-0.039</v>
+        <v>-0.029</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>0.003</v>
+        <v>0.043</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
       <c r="L10" s="15" t="n">
         <v>1</v>
@@ -2303,37 +2303,37 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>5</v>
+        <v>4.999</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0.57</v>
+        <v>0.634</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>-0.048</v>
+        <v>-0.079</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>-0.051</v>
+        <v>0.013</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.04</v>
+        <v>0.032</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-0.059</v>
+        <v>-0.046</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>0.004</v>
+        <v>-0.029</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>-0.079</v>
+        <v>-0.041</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>-0.064</v>
+        <v>-0.058</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>-0.127</v>
+        <v>-0.384</v>
       </c>
       <c r="M11" s="15" t="n">
         <v>1</v>
@@ -2354,40 +2354,40 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>3.438</v>
+        <v>3.463</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.906</v>
+        <v>0.921</v>
       </c>
       <c r="D12" s="15" t="n">
-        <v>0.86</v>
+        <v>0.79</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>-0.038</v>
+        <v>-0</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>-0.041</v>
+        <v>-0.062</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>-0.01</v>
+        <v>-0.043</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>0.054</v>
+        <v>0.08</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>0.048</v>
+        <v>0.056</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.076</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>-0.045</v>
+        <v>-0.06</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>0.005</v>
+        <v>0.055</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>0.053</v>
+        <v>-0.004</v>
       </c>
       <c r="N12" s="15" t="n">
         <v>1</v>
@@ -2407,43 +2407,43 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>4.575</v>
+        <v>4.597</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.897</v>
+        <v>0.887</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>-0.079</v>
+        <v>-0.091</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>-0.107</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>-0.019</v>
+        <v>-0.044</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>0.052</v>
+        <v>0.048</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-0.056</v>
+        <v>-0.063</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>-0.056</v>
+        <v>-0.046</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.049</v>
       </c>
       <c r="L13" s="15" t="n">
-        <v>-0.002</v>
+        <v>0.007</v>
       </c>
       <c r="M13" s="15" t="n">
-        <v>-0.04</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="N13" s="15" t="n">
-        <v>-0.018</v>
+        <v>0.02</v>
       </c>
       <c r="O13" s="15" t="n">
         <v>1</v>
@@ -2462,46 +2462,46 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>4.471</v>
+        <v>4.533</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>1.194</v>
+        <v>1.266</v>
       </c>
       <c r="D14" s="15" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>0.003</v>
+        <v>-0.038</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>-0.036</v>
+        <v>-0.033</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>0.053</v>
+        <v>0.03</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>0.068</v>
+        <v>0.012</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>-0.053</v>
+        <v>-0.016</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>-0.048</v>
+        <v>-0.059</v>
       </c>
       <c r="L14" s="15" t="n">
-        <v>-0.356</v>
+        <v>-0.424</v>
       </c>
       <c r="M14" s="15" t="n">
-        <v>0.336</v>
+        <v>0.387</v>
       </c>
       <c r="N14" s="15" t="n">
-        <v>-0.008</v>
+        <v>-0.059</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>-0.051</v>
+        <v>-0.081</v>
       </c>
       <c r="P14" s="15" t="n">
         <v>1</v>
@@ -2519,49 +2519,49 @@
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>2.977</v>
+        <v>2.971</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>1.137</v>
+        <v>1.201</v>
       </c>
       <c r="D15" s="15" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>0.016</v>
+        <v>0.05</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0.025</v>
+        <v>-0.011</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-0.052</v>
+        <v>-0.029</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-0.039</v>
+        <v>-0.006</v>
       </c>
       <c r="J15" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="15" t="n">
         <v>0.047</v>
       </c>
-      <c r="K15" s="15" t="n">
-        <v>0.08599999999999999</v>
-      </c>
       <c r="L15" s="15" t="n">
-        <v>0.319</v>
+        <v>0.301</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.302</v>
+        <v>-0.328</v>
       </c>
       <c r="N15" s="15" t="n">
-        <v>0.049</v>
+        <v>0.039</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.092</v>
+        <v>-0.026</v>
       </c>
       <c r="P15" s="15" t="n">
-        <v>-0.457</v>
+        <v>-0.456</v>
       </c>
       <c r="Q15" s="15" t="n">
         <v>1</v>
@@ -2578,52 +2578,52 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>4.505</v>
+        <v>4.42</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>0.403</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>-0.036</v>
+        <v>-0.025</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>0.004</v>
+        <v>-0.005</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>-0.091</v>
+        <v>-0.109</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-0.037</v>
+        <v>-0.058</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>0.015</v>
+        <v>-0.013</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>0.022</v>
+        <v>0.001</v>
       </c>
       <c r="L16" s="15" t="n">
-        <v>-0.004</v>
+        <v>0.006</v>
       </c>
       <c r="M16" s="15" t="n">
-        <v>0.068</v>
+        <v>-0.103</v>
       </c>
       <c r="N16" s="15" t="n">
-        <v>-0.175</v>
+        <v>-0.13</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>0.073</v>
+        <v>0.034</v>
       </c>
       <c r="P16" s="15" t="n">
-        <v>0.075</v>
+        <v>-0.005</v>
       </c>
       <c r="Q16" s="15" t="n">
-        <v>-0.095</v>
+        <v>-0.065</v>
       </c>
       <c r="R16" s="15" t="n">
         <v>1</v>
@@ -2639,55 +2639,55 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>4.548</v>
+        <v>4.524</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>0.806</v>
+        <v>0.829</v>
       </c>
       <c r="D17" s="15" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>0.015</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>0.011</v>
+        <v>0.033</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>-0.047</v>
+        <v>-0.065</v>
       </c>
       <c r="H17" s="15" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>-0.058</v>
+      </c>
+      <c r="J17" s="15" t="n">
         <v>0.03</v>
       </c>
-      <c r="I17" s="15" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="J17" s="15" t="n">
+      <c r="K17" s="15" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="L17" s="15" t="n">
+        <v>-0.229</v>
+      </c>
+      <c r="M17" s="15" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="N17" s="15" t="n">
+        <v>-0.094</v>
+      </c>
+      <c r="O17" s="15" t="n">
         <v>0.028</v>
       </c>
-      <c r="K17" s="15" t="n">
-        <v>-0.081</v>
-      </c>
-      <c r="L17" s="15" t="n">
-        <v>-0.355</v>
-      </c>
-      <c r="M17" s="15" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="N17" s="15" t="n">
-        <v>-0.052</v>
-      </c>
-      <c r="O17" s="15" t="n">
-        <v>0.04</v>
-      </c>
       <c r="P17" s="15" t="n">
-        <v>0.677</v>
+        <v>0.576</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-0.615</v>
       </c>
       <c r="R17" s="15" t="n">
-        <v>0.083</v>
+        <v>0.433</v>
       </c>
       <c r="S17" s="15" t="n">
         <v>1</v>
@@ -2702,58 +2702,58 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>4.814</v>
+        <v>4.908</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>1.368</v>
+        <v>1.324</v>
       </c>
       <c r="D18" s="15" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.093</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>-0.056</v>
+        <v>0.04</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>-0.002</v>
+        <v>-0.053</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-0.019</v>
+        <v>0.023</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-0.074</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>0.031</v>
+        <v>0.035</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>0.006</v>
+        <v>0.039</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>-0.419</v>
+        <v>-0.497</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>0.477</v>
+        <v>0.35</v>
       </c>
       <c r="N18" s="15" t="n">
-        <v>0.053</v>
+        <v>-0.031</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>-0.047</v>
+        <v>0.012</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0.422</v>
+        <v>0.365</v>
       </c>
       <c r="Q18" s="15" t="n">
-        <v>-0.432</v>
+        <v>-0.353</v>
       </c>
       <c r="R18" s="15" t="n">
-        <v>0.062</v>
+        <v>0.098</v>
       </c>
       <c r="S18" s="15" t="n">
-        <v>0.397</v>
+        <v>0.303</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>1</v>
@@ -2767,61 +2767,61 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>2.416</v>
+        <v>2.431</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>1.168</v>
+        <v>1.173</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>0.89</v>
+        <v>0.82</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>0.047</v>
+        <v>0.111</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>0.076</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>0.027</v>
+        <v>0.068</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-0.001</v>
+        <v>-0.012</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>0.004</v>
+        <v>0.058</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>-0.029</v>
+        <v>-0.025</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>-0.003</v>
+        <v>0.03</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>0.43</v>
+        <v>0.543</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>-0.493</v>
+        <v>-0.522</v>
       </c>
       <c r="N19" s="15" t="n">
-        <v>-0.034</v>
+        <v>0.048</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>-0.039</v>
+        <v>0.056</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>-0.424</v>
+        <v>-0.427</v>
       </c>
       <c r="Q19" s="15" t="n">
-        <v>0.451</v>
+        <v>0.301</v>
       </c>
       <c r="R19" s="15" t="n">
-        <v>-0.108</v>
+        <v>0.065</v>
       </c>
       <c r="S19" s="15" t="n">
-        <v>-0.407</v>
+        <v>-0.26</v>
       </c>
       <c r="T19" s="15" t="n">
-        <v>-0.697</v>
+        <v>-0.458</v>
       </c>
       <c r="U19" s="15" t="n">
         <v>1</v>

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>30.699</v>
+        <v>30.654</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>4.675</v>
+        <v>4.636</v>
       </c>
       <c r="D3" s="15" t="inlineStr"/>
       <c r="E3" s="15" t="n">
@@ -2014,14 +2014,14 @@
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.551</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>0.497</v>
+        <v>0.498</v>
       </c>
       <c r="D4" s="15" t="inlineStr"/>
       <c r="E4" s="15" t="n">
-        <v>0.022</v>
+        <v>0.041</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>1</v>
@@ -2049,17 +2049,17 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>3.104</v>
+        <v>3.112</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>0.923</v>
+        <v>0.956</v>
       </c>
       <c r="D5" s="15" t="inlineStr"/>
       <c r="E5" s="15" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>-0.073</v>
+        <v>-0.06</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>1</v>
@@ -2086,20 +2086,20 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>2.568</v>
+        <v>2.525</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>1.131</v>
+        <v>1.122</v>
       </c>
       <c r="D6" s="15" t="inlineStr"/>
       <c r="E6" s="15" t="n">
-        <v>0.007</v>
+        <v>-0.041</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>-0.036</v>
+        <v>-0.03</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>-0.025</v>
+        <v>-0.029</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>1</v>
@@ -2125,23 +2125,23 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>8.948</v>
+        <v>8.875</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>4.88</v>
+        <v>4.816</v>
       </c>
       <c r="D7" s="15" t="inlineStr"/>
       <c r="E7" s="15" t="n">
         <v>0.905</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>-0.008</v>
+        <v>0.01</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>-0.008</v>
+        <v>-0.004</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>0.029</v>
+        <v>-0.016</v>
       </c>
       <c r="I7" s="15" t="n">
         <v>1</v>
@@ -2166,26 +2166,26 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>2.297</v>
+        <v>2.307</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>1.468</v>
+        <v>1.49</v>
       </c>
       <c r="D8" s="15" t="inlineStr"/>
       <c r="E8" s="15" t="n">
-        <v>0.203</v>
+        <v>0.191</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>-0.025</v>
+        <v>-0.004</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>-0.01</v>
+        <v>-0.046</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-0.004</v>
+        <v>0.037</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>0.173</v>
+        <v>0.158</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>1</v>
@@ -2209,29 +2209,29 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>3.249</v>
+        <v>3.302</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>1.06</v>
+        <v>1.078</v>
       </c>
       <c r="D9" s="15" t="inlineStr"/>
       <c r="E9" s="15" t="n">
-        <v>-0.014</v>
+        <v>-0.034</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.096</v>
+        <v>0.103</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>-0.057</v>
+        <v>-0.062</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.119</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-0.005</v>
+        <v>-0.017</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>-0.049</v>
+        <v>-0.061</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>1</v>
@@ -2254,34 +2254,34 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>4.04</v>
+        <v>4.055</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.623</v>
+        <v>0.598</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>-0.004</v>
+        <v>0.083</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.066</v>
+        <v>0.053</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.125</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-0.029</v>
+        <v>-0.04</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>0.043</v>
+        <v>0.044</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>0.02</v>
+        <v>0.036</v>
       </c>
       <c r="L10" s="15" t="n">
         <v>1</v>
@@ -2303,37 +2303,37 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>4.999</v>
+        <v>4.998</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0.634</v>
+        <v>0.629</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>0.87</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>-0.079</v>
+        <v>-0.05</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0.013</v>
+        <v>-0.062</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.032</v>
+        <v>0.035</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-0.046</v>
+        <v>-0.003</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-0.029</v>
+        <v>0.022</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>-0.041</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>-0.058</v>
+        <v>-0.056</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>-0.384</v>
+        <v>-0.393</v>
       </c>
       <c r="M11" s="15" t="n">
         <v>1</v>
@@ -2354,40 +2354,40 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>3.463</v>
+        <v>3.445</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.921</v>
+        <v>0.905</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>0.79</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>-0</v>
+        <v>-0.041</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>-0.062</v>
+        <v>-0.055</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>-0.043</v>
+        <v>-0.054</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>0.08</v>
+        <v>0.063</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>0.056</v>
+        <v>0.011</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>0.076</v>
+        <v>0.057</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>-0.06</v>
+        <v>-0.066</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>0.055</v>
+        <v>0.008</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>-0.004</v>
+        <v>0.073</v>
       </c>
       <c r="N12" s="15" t="n">
         <v>1</v>
@@ -2407,43 +2407,43 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>4.597</v>
+        <v>4.556</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.887</v>
+        <v>0.878</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>0.78</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>-0.091</v>
+        <v>-0.092</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G13" s="15" t="n">
+        <v>-0.058</v>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>-0.074</v>
+      </c>
+      <c r="J13" s="15" t="n">
+        <v>-0.092</v>
+      </c>
+      <c r="K13" s="15" t="n">
         <v>-0.044</v>
       </c>
-      <c r="H13" s="15" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="I13" s="15" t="n">
-        <v>-0.063</v>
-      </c>
-      <c r="J13" s="15" t="n">
-        <v>-0.046</v>
-      </c>
-      <c r="K13" s="15" t="n">
-        <v>-0.049</v>
-      </c>
       <c r="L13" s="15" t="n">
-        <v>0.007</v>
+        <v>-0.022</v>
       </c>
       <c r="M13" s="15" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.037</v>
       </c>
       <c r="N13" s="15" t="n">
-        <v>0.02</v>
+        <v>-0.003</v>
       </c>
       <c r="O13" s="15" t="n">
         <v>1</v>
@@ -2462,46 +2462,46 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>4.533</v>
+        <v>4.546</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>1.266</v>
+        <v>1.248</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>0.84</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>-0.038</v>
+        <v>-0.018</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0.03</v>
+        <v>-0.026</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>-0.033</v>
+        <v>-0.023</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>0.03</v>
+        <v>0.043</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>0.012</v>
+        <v>0.041</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>-0.016</v>
+        <v>-0.006</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>-0.059</v>
+        <v>-0.08</v>
       </c>
       <c r="L14" s="15" t="n">
-        <v>-0.424</v>
+        <v>-0.393</v>
       </c>
       <c r="M14" s="15" t="n">
-        <v>0.387</v>
+        <v>0.357</v>
       </c>
       <c r="N14" s="15" t="n">
-        <v>-0.059</v>
+        <v>-0.017</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>-0.081</v>
+        <v>-0.036</v>
       </c>
       <c r="P14" s="15" t="n">
         <v>1</v>
@@ -2519,49 +2519,49 @@
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>2.971</v>
+        <v>2.961</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>1.201</v>
+        <v>1.182</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>0.05</v>
+        <v>0.036</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>-0.011</v>
+        <v>0.032</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>-0.02</v>
+        <v>-0.023</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-0.029</v>
+        <v>-0.039</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-0.006</v>
+        <v>-0.016</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>0.047</v>
+        <v>0.074</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>0.301</v>
+        <v>0.319</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.328</v>
+        <v>-0.331</v>
       </c>
       <c r="N15" s="15" t="n">
-        <v>0.039</v>
+        <v>-0.008</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.026</v>
+        <v>-0.08</v>
       </c>
       <c r="P15" s="15" t="n">
-        <v>-0.456</v>
+        <v>-0.454</v>
       </c>
       <c r="Q15" s="15" t="n">
         <v>1</v>
@@ -2578,52 +2578,52 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>4.42</v>
+        <v>4.402</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.639</v>
       </c>
       <c r="D16" s="15" t="n">
         <v>0.83</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>-0.025</v>
+        <v>-0.013</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>-0.005</v>
+        <v>-0.026</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>-0.109</v>
+        <v>-0.101</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>0.005</v>
+        <v>-0.013</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-0.058</v>
+        <v>-0.06</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>-0.013</v>
+        <v>-0.052</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>0.001</v>
+        <v>-0.008</v>
       </c>
       <c r="L16" s="15" t="n">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="M16" s="15" t="n">
-        <v>-0.103</v>
+        <v>-0.028</v>
       </c>
       <c r="N16" s="15" t="n">
-        <v>-0.13</v>
+        <v>-0.125</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>0.034</v>
+        <v>-0.045</v>
       </c>
       <c r="P16" s="15" t="n">
-        <v>-0.005</v>
+        <v>0.041</v>
       </c>
       <c r="Q16" s="15" t="n">
-        <v>-0.065</v>
+        <v>-0.068</v>
       </c>
       <c r="R16" s="15" t="n">
         <v>1</v>
@@ -2639,55 +2639,55 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>4.524</v>
+        <v>4.518</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>0.829</v>
+        <v>0.828</v>
       </c>
       <c r="D17" s="15" t="n">
         <v>0.85</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.029</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>0.033</v>
+        <v>-0.06</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>-0.065</v>
+        <v>-0.019</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>0.039</v>
+        <v>0.044</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-0.058</v>
+        <v>-0.016</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>0.03</v>
+        <v>-0.042</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>-0.06</v>
+        <v>-0.108</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>-0.229</v>
+        <v>-0.227</v>
       </c>
       <c r="M17" s="15" t="n">
-        <v>0.209</v>
+        <v>0.265</v>
       </c>
       <c r="N17" s="15" t="n">
-        <v>-0.094</v>
+        <v>-0.025</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>0.028</v>
+        <v>0.013</v>
       </c>
       <c r="P17" s="15" t="n">
-        <v>0.576</v>
+        <v>0.602</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>-0.615</v>
+        <v>-0.663</v>
       </c>
       <c r="R17" s="15" t="n">
-        <v>0.433</v>
+        <v>0.394</v>
       </c>
       <c r="S17" s="15" t="n">
         <v>1</v>
@@ -2702,58 +2702,58 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>4.908</v>
+        <v>4.823</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>1.324</v>
+        <v>1.367</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>-0.093</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>0.04</v>
+        <v>-0.091</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>-0.053</v>
+        <v>-0.005</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>0.023</v>
+        <v>-0.042</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.016</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>0.035</v>
+        <v>0.021</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>0.039</v>
+        <v>0.015</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>-0.497</v>
+        <v>-0.396</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>0.35</v>
+        <v>0.477</v>
       </c>
       <c r="N18" s="15" t="n">
-        <v>-0.031</v>
+        <v>-0.04</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>0.012</v>
+        <v>-0.057</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0.365</v>
+        <v>0.423</v>
       </c>
       <c r="Q18" s="15" t="n">
-        <v>-0.353</v>
+        <v>-0.382</v>
       </c>
       <c r="R18" s="15" t="n">
-        <v>0.098</v>
+        <v>0.095</v>
       </c>
       <c r="S18" s="15" t="n">
-        <v>0.303</v>
+        <v>0.34</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>1</v>
@@ -2767,61 +2767,61 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>2.431</v>
+        <v>2.409</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>1.173</v>
+        <v>1.061</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>0.82</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>0.111</v>
+        <v>0.018</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.035</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>0.068</v>
+        <v>0.059</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-0.012</v>
+        <v>-0.015</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>0.058</v>
+        <v>-0.01</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>-0.025</v>
+        <v>-0.041</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>0.03</v>
+        <v>-0.049</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>0.543</v>
+        <v>0.393</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>-0.522</v>
+        <v>-0.461</v>
       </c>
       <c r="N19" s="15" t="n">
-        <v>0.048</v>
+        <v>-0.049</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>0.056</v>
+        <v>-0.043</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>-0.427</v>
+        <v>-0.347</v>
       </c>
       <c r="Q19" s="15" t="n">
-        <v>0.301</v>
+        <v>0.372</v>
       </c>
       <c r="R19" s="15" t="n">
-        <v>0.065</v>
+        <v>-0.097</v>
       </c>
       <c r="S19" s="15" t="n">
-        <v>-0.26</v>
+        <v>-0.324</v>
       </c>
       <c r="T19" s="15" t="n">
-        <v>-0.458</v>
+        <v>-0.572</v>
       </c>
       <c r="U19" s="15" t="n">
         <v>1</v>

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>30.654</v>
+        <v>30.834</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>4.636</v>
+        <v>4.634</v>
       </c>
       <c r="D3" s="15" t="inlineStr"/>
       <c r="E3" s="15" t="n">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="D4" s="15" t="inlineStr"/>
       <c r="E4" s="15" t="n">
-        <v>0.041</v>
+        <v>0.027</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>1</v>
@@ -2049,17 +2049,17 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>3.112</v>
+        <v>3.098</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>0.956</v>
+        <v>0.931</v>
       </c>
       <c r="D5" s="15" t="inlineStr"/>
       <c r="E5" s="15" t="n">
-        <v>0.002</v>
+        <v>0.028</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>-0.06</v>
+        <v>-0.063</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>1</v>
@@ -2086,20 +2086,20 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>2.525</v>
+        <v>2.552</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>1.122</v>
+        <v>1.137</v>
       </c>
       <c r="D6" s="15" t="inlineStr"/>
       <c r="E6" s="15" t="n">
         <v>-0.041</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>-0.029</v>
+        <v>0.007</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>1</v>
@@ -2125,23 +2125,23 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>8.875</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>4.816</v>
+        <v>4.848</v>
       </c>
       <c r="D7" s="15" t="inlineStr"/>
       <c r="E7" s="15" t="n">
-        <v>0.905</v>
+        <v>0.907</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>-0.004</v>
+        <v>0.019</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-0.016</v>
+        <v>-0.005</v>
       </c>
       <c r="I7" s="15" t="n">
         <v>1</v>
@@ -2166,26 +2166,26 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>2.307</v>
+        <v>2.331</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>1.49</v>
+        <v>1.474</v>
       </c>
       <c r="D8" s="15" t="inlineStr"/>
       <c r="E8" s="15" t="n">
-        <v>0.191</v>
+        <v>0.187</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>-0.004</v>
+        <v>-0.013</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>-0.046</v>
+        <v>-0.032</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>0.037</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>0.158</v>
+        <v>0.164</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>1</v>
@@ -2209,29 +2209,29 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>3.302</v>
+        <v>3.271</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>1.078</v>
+        <v>1.061</v>
       </c>
       <c r="D9" s="15" t="inlineStr"/>
       <c r="E9" s="15" t="n">
-        <v>-0.034</v>
+        <v>-0.024</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.103</v>
+        <v>0.031</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>-0.062</v>
+        <v>-0.046</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-0.119</v>
+        <v>-0.099</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-0.017</v>
+        <v>-0.005</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>-0.061</v>
+        <v>-0.068</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>1</v>
@@ -2254,34 +2254,34 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>4.055</v>
+        <v>4.031</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.598</v>
+        <v>0.584</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>0.01</v>
+        <v>0.036</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0.083</v>
+        <v>0.02</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.053</v>
+        <v>0.047</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-0.125</v>
+        <v>-0.09</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-0.04</v>
+        <v>-0.003</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>0.044</v>
+        <v>0.027</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>0.036</v>
+        <v>0.03</v>
       </c>
       <c r="L10" s="15" t="n">
         <v>1</v>
@@ -2303,37 +2303,37 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>4.998</v>
+        <v>4.913</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0.629</v>
+        <v>0.635</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>0.87</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>-0.05</v>
+        <v>-0.058</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>-0.062</v>
+        <v>0.013</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.035</v>
+        <v>0.064</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-0.003</v>
+        <v>-0.042</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>0.022</v>
+        <v>-0.039</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.047</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>-0.056</v>
+        <v>-0.045</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>-0.393</v>
+        <v>-0.341</v>
       </c>
       <c r="M11" s="15" t="n">
         <v>1</v>
@@ -2354,40 +2354,40 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>3.445</v>
+        <v>3.433</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.905</v>
+        <v>0.889</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>0.79</v>
       </c>
       <c r="E12" s="15" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="F12" s="15" t="n">
         <v>-0.041</v>
       </c>
-      <c r="F12" s="15" t="n">
-        <v>-0.055</v>
-      </c>
       <c r="G12" s="15" t="n">
-        <v>-0.054</v>
+        <v>-0.063</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>0.063</v>
+        <v>0.082</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>0.011</v>
+        <v>0.023</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>0.057</v>
+        <v>0.056</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>-0.066</v>
+        <v>0.015</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>0.008</v>
+        <v>-0.01</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>0.073</v>
+        <v>0.01</v>
       </c>
       <c r="N12" s="15" t="n">
         <v>1</v>
@@ -2407,43 +2407,43 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>4.556</v>
+        <v>4.585</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.878</v>
+        <v>0.887</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>0.78</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>-0.092</v>
+        <v>-0.059</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.101</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>-0.058</v>
+        <v>-0.061</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>0.053</v>
+        <v>0.066</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-0.074</v>
+        <v>-0.039</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>-0.092</v>
+        <v>-0.056</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>-0.044</v>
+        <v>-0.068</v>
       </c>
       <c r="L13" s="15" t="n">
-        <v>-0.022</v>
+        <v>-0.035</v>
       </c>
       <c r="M13" s="15" t="n">
-        <v>-0.037</v>
+        <v>-0.078</v>
       </c>
       <c r="N13" s="15" t="n">
-        <v>-0.003</v>
+        <v>-0.007</v>
       </c>
       <c r="O13" s="15" t="n">
         <v>1</v>
@@ -2462,46 +2462,46 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>4.546</v>
+        <v>4.512</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>1.248</v>
+        <v>1.214</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>0.84</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>-0.018</v>
+        <v>-0.013</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>-0.026</v>
+        <v>-0.04</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>-0.023</v>
+        <v>0.023</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>0.043</v>
+        <v>0.055</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>0.041</v>
+        <v>0.057</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>-0.006</v>
+        <v>-0.022</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>-0.08</v>
+        <v>-0.058</v>
       </c>
       <c r="L14" s="15" t="n">
-        <v>-0.393</v>
+        <v>-0.346</v>
       </c>
       <c r="M14" s="15" t="n">
-        <v>0.357</v>
+        <v>0.372</v>
       </c>
       <c r="N14" s="15" t="n">
-        <v>-0.017</v>
+        <v>-0.004</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>-0.036</v>
+        <v>-0.021</v>
       </c>
       <c r="P14" s="15" t="n">
         <v>1</v>
@@ -2519,49 +2519,49 @@
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>2.961</v>
+        <v>3.064</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>1.182</v>
+        <v>1.179</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>0.036</v>
+        <v>0.001</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0.032</v>
+        <v>0.011</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>-0.023</v>
+        <v>-0.029</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-0.039</v>
+        <v>-0.052</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-0.016</v>
+        <v>-0.041</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>0.008</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>0.074</v>
+        <v>0.024</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>0.319</v>
+        <v>0.297</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.331</v>
+        <v>-0.32</v>
       </c>
       <c r="N15" s="15" t="n">
-        <v>-0.008</v>
+        <v>0.017</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.08</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="P15" s="15" t="n">
-        <v>-0.454</v>
+        <v>-0.448</v>
       </c>
       <c r="Q15" s="15" t="n">
         <v>1</v>
@@ -2578,52 +2578,52 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>4.402</v>
+        <v>4.379</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>0.639</v>
+        <v>0.649</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>-0.013</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>-0.026</v>
+        <v>0.034</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>-0.101</v>
+        <v>-0.018</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-0.013</v>
+        <v>0.048</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-0.06</v>
+        <v>-0.011</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>-0.052</v>
+        <v>-0.02</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>-0.008</v>
+        <v>-0.03</v>
       </c>
       <c r="L16" s="15" t="n">
-        <v>0.01</v>
+        <v>0.106</v>
       </c>
       <c r="M16" s="15" t="n">
-        <v>-0.028</v>
+        <v>-0.048</v>
       </c>
       <c r="N16" s="15" t="n">
-        <v>-0.125</v>
+        <v>-0.153</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>-0.045</v>
+        <v>-0.074</v>
       </c>
       <c r="P16" s="15" t="n">
-        <v>0.041</v>
+        <v>-0.005</v>
       </c>
       <c r="Q16" s="15" t="n">
-        <v>-0.068</v>
+        <v>0.067</v>
       </c>
       <c r="R16" s="15" t="n">
         <v>1</v>
@@ -2639,55 +2639,55 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>4.518</v>
+        <v>4.525</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>0.828</v>
+        <v>0.742</v>
       </c>
       <c r="D17" s="15" t="n">
         <v>0.85</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>-0.029</v>
+        <v>-0.028</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>-0.06</v>
+        <v>0.028</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>-0.019</v>
+        <v>0.028</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>0.044</v>
+        <v>0.11</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-0.016</v>
+        <v>0.006</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>-0.042</v>
+        <v>-0.006</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>-0.108</v>
+        <v>-0.051</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>-0.227</v>
+        <v>-0.214</v>
       </c>
       <c r="M17" s="15" t="n">
-        <v>0.265</v>
+        <v>0.245</v>
       </c>
       <c r="N17" s="15" t="n">
-        <v>-0.025</v>
+        <v>-0.105</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>0.013</v>
+        <v>-0.011</v>
       </c>
       <c r="P17" s="15" t="n">
-        <v>0.602</v>
+        <v>0.603</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>-0.663</v>
+        <v>-0.634</v>
       </c>
       <c r="R17" s="15" t="n">
-        <v>0.394</v>
+        <v>0.318</v>
       </c>
       <c r="S17" s="15" t="n">
         <v>1</v>
@@ -2702,58 +2702,58 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>4.823</v>
+        <v>4.831</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>1.367</v>
+        <v>1.212</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.104</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>-0.091</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-0.042</v>
+        <v>0.05</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-0.016</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>0.021</v>
+        <v>0.046</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>0.015</v>
+        <v>0.035</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>-0.396</v>
+        <v>-0.409</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>0.477</v>
+        <v>0.434</v>
       </c>
       <c r="N18" s="15" t="n">
-        <v>-0.04</v>
+        <v>0.079</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>-0.057</v>
+        <v>0.004</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0.423</v>
+        <v>0.366</v>
       </c>
       <c r="Q18" s="15" t="n">
-        <v>-0.382</v>
+        <v>-0.35</v>
       </c>
       <c r="R18" s="15" t="n">
-        <v>0.095</v>
+        <v>-0.164</v>
       </c>
       <c r="S18" s="15" t="n">
-        <v>0.34</v>
+        <v>0.196</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>1</v>
@@ -2767,61 +2767,61 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>2.409</v>
+        <v>2.527</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>1.061</v>
+        <v>1.09</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>0.82</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>0.018</v>
+        <v>0.033</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>0.035</v>
+        <v>0.011</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>0.059</v>
+        <v>-0</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-0.015</v>
+        <v>0.031</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-0.01</v>
+        <v>0.019</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>-0.041</v>
+        <v>-0.076</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>-0.049</v>
+        <v>-0.004</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>0.393</v>
+        <v>0.329</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>-0.461</v>
+        <v>-0.493</v>
       </c>
       <c r="N19" s="15" t="n">
-        <v>-0.049</v>
+        <v>-0.005</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>-0.043</v>
+        <v>0.039</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>-0.347</v>
+        <v>-0.375</v>
       </c>
       <c r="Q19" s="15" t="n">
-        <v>0.372</v>
+        <v>0.368</v>
       </c>
       <c r="R19" s="15" t="n">
-        <v>-0.097</v>
+        <v>0.143</v>
       </c>
       <c r="S19" s="15" t="n">
-        <v>-0.324</v>
+        <v>-0.217</v>
       </c>
       <c r="T19" s="15" t="n">
-        <v>-0.572</v>
+        <v>-0.507</v>
       </c>
       <c r="U19" s="15" t="n">
         <v>1</v>

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>30.834</v>
+        <v>30.756</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>4.634</v>
+        <v>4.688</v>
       </c>
       <c r="D3" s="15" t="inlineStr"/>
       <c r="E3" s="15" t="n">
@@ -2014,14 +2014,14 @@
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>0.551</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>0.498</v>
+        <v>0.497</v>
       </c>
       <c r="D4" s="15" t="inlineStr"/>
       <c r="E4" s="15" t="n">
-        <v>0.027</v>
+        <v>0.028</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>1</v>
@@ -2049,17 +2049,17 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>3.098</v>
+        <v>3.068</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>0.931</v>
+        <v>0.927</v>
       </c>
       <c r="D5" s="15" t="inlineStr"/>
       <c r="E5" s="15" t="n">
-        <v>0.028</v>
+        <v>-0.003</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>-0.063</v>
+        <v>-0.064</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>1</v>
@@ -2086,20 +2086,20 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>2.552</v>
+        <v>2.545</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>1.137</v>
+        <v>1.131</v>
       </c>
       <c r="D6" s="15" t="inlineStr"/>
       <c r="E6" s="15" t="n">
-        <v>-0.041</v>
+        <v>0.024</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0.007</v>
+        <v>-0.047</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>1</v>
@@ -2125,23 +2125,23 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>8.970000000000001</v>
+        <v>9.007999999999999</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>4.848</v>
+        <v>4.909</v>
       </c>
       <c r="D7" s="15" t="inlineStr"/>
       <c r="E7" s="15" t="n">
-        <v>0.907</v>
+        <v>0.905</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0.019</v>
+        <v>0.004</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-0.005</v>
+        <v>0.047</v>
       </c>
       <c r="I7" s="15" t="n">
         <v>1</v>
@@ -2166,26 +2166,26 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>2.331</v>
+        <v>2.328</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>1.474</v>
+        <v>1.481</v>
       </c>
       <c r="D8" s="15" t="inlineStr"/>
       <c r="E8" s="15" t="n">
         <v>0.187</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>-0.013</v>
+        <v>0.01</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>-0.032</v>
+        <v>-0.025</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>0.037</v>
+        <v>0.034</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>0.164</v>
+        <v>0.145</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>1</v>
@@ -2209,29 +2209,29 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>3.271</v>
+        <v>3.297</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>1.061</v>
+        <v>1.07</v>
       </c>
       <c r="D9" s="15" t="inlineStr"/>
       <c r="E9" s="15" t="n">
-        <v>-0.024</v>
+        <v>-0.034</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.031</v>
+        <v>0.122</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>-0.046</v>
+        <v>-0.048</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-0.099</v>
+        <v>-0.081</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-0.005</v>
+        <v>-0.037</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>-0.068</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>1</v>
@@ -2254,34 +2254,34 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>4.031</v>
+        <v>4.054</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.584</v>
+        <v>0.609</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>0.036</v>
+        <v>0.041</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0.02</v>
+        <v>0.014</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.047</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-0.09</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="I10" s="15" t="n">
         <v>-0.003</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>0.027</v>
+        <v>0.037</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>0.03</v>
+        <v>0.055</v>
       </c>
       <c r="L10" s="15" t="n">
         <v>1</v>
@@ -2303,37 +2303,37 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>4.913</v>
+        <v>4.869</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0.635</v>
+        <v>0.653</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>0.87</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>-0.058</v>
+        <v>-0.055</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.064</v>
+        <v>0.038</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-0.042</v>
+        <v>-0.025</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-0.039</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>-0.047</v>
+        <v>-0.059</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>-0.045</v>
+        <v>-0.052</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>-0.341</v>
+        <v>-0.414</v>
       </c>
       <c r="M11" s="15" t="n">
         <v>1</v>
@@ -2354,40 +2354,40 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>3.433</v>
+        <v>3.45</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.889</v>
+        <v>0.893</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>0.79</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>-0.025</v>
+        <v>-0.027</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>-0.041</v>
+        <v>-0.063</v>
       </c>
       <c r="G12" s="15" t="n">
+        <v>-0.058</v>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="J12" s="15" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="K12" s="15" t="n">
         <v>-0.063</v>
       </c>
-      <c r="H12" s="15" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="I12" s="15" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="J12" s="15" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="K12" s="15" t="n">
-        <v>0.015</v>
-      </c>
       <c r="L12" s="15" t="n">
-        <v>-0.01</v>
+        <v>-0.001</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>0.01</v>
+        <v>0.031</v>
       </c>
       <c r="N12" s="15" t="n">
         <v>1</v>
@@ -2407,43 +2407,43 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>4.585</v>
+        <v>4.622</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.887</v>
+        <v>0.881</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>0.78</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>-0.059</v>
+        <v>-0.047</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>-0.101</v>
+        <v>-0.113</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>-0.061</v>
+        <v>0.001</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>0.066</v>
+        <v>0.046</v>
       </c>
       <c r="I13" s="15" t="n">
+        <v>-0.026</v>
+      </c>
+      <c r="J13" s="15" t="n">
+        <v>-0.08599999999999999</v>
+      </c>
+      <c r="K13" s="15" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="L13" s="15" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="M13" s="15" t="n">
         <v>-0.039</v>
       </c>
-      <c r="J13" s="15" t="n">
-        <v>-0.056</v>
-      </c>
-      <c r="K13" s="15" t="n">
-        <v>-0.068</v>
-      </c>
-      <c r="L13" s="15" t="n">
-        <v>-0.035</v>
-      </c>
-      <c r="M13" s="15" t="n">
-        <v>-0.078</v>
-      </c>
       <c r="N13" s="15" t="n">
-        <v>-0.007</v>
+        <v>0.015</v>
       </c>
       <c r="O13" s="15" t="n">
         <v>1</v>
@@ -2462,46 +2462,46 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>4.512</v>
+        <v>4.45</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>1.214</v>
+        <v>1.246</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>0.84</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>-0.013</v>
+        <v>-0.006</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>-0.04</v>
+        <v>-0.044</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0.023</v>
+        <v>-0.016</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>0.055</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>0.057</v>
+        <v>0.054</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>-0.022</v>
+        <v>-0.012</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>-0.058</v>
+        <v>-0.065</v>
       </c>
       <c r="L14" s="15" t="n">
-        <v>-0.346</v>
+        <v>-0.376</v>
       </c>
       <c r="M14" s="15" t="n">
-        <v>0.372</v>
+        <v>0.382</v>
       </c>
       <c r="N14" s="15" t="n">
-        <v>-0.004</v>
+        <v>0.004</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>-0.021</v>
+        <v>-0.029</v>
       </c>
       <c r="P14" s="15" t="n">
         <v>1</v>
@@ -2519,49 +2519,49 @@
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>3.064</v>
+        <v>3.084</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>1.179</v>
+        <v>1.215</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>0.001</v>
+        <v>0.026</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0.011</v>
+        <v>0.031</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>-0.029</v>
+        <v>-0.011</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-0.052</v>
+        <v>-0.081</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-0.041</v>
+        <v>-0.032</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.02</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>0.024</v>
+        <v>0.026</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>0.297</v>
+        <v>0.334</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.32</v>
+        <v>-0.348</v>
       </c>
       <c r="N15" s="15" t="n">
-        <v>0.017</v>
+        <v>0.022</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.062</v>
       </c>
       <c r="P15" s="15" t="n">
-        <v>-0.448</v>
+        <v>-0.438</v>
       </c>
       <c r="Q15" s="15" t="n">
         <v>1</v>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>4.379</v>
+        <v>4.382</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>0.649</v>
+        <v>0.655</v>
       </c>
       <c r="D16" s="15" t="n">
         <v>0.79</v>
@@ -2590,40 +2590,40 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>0.034</v>
+        <v>0.036</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>-0.018</v>
+        <v>-0.041</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>0.048</v>
+        <v>0.054</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-0.011</v>
+        <v>-0.013</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>-0.02</v>
+        <v>-0.024</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>-0.03</v>
+        <v>-0.021</v>
       </c>
       <c r="L16" s="15" t="n">
-        <v>0.106</v>
+        <v>0.119</v>
       </c>
       <c r="M16" s="15" t="n">
-        <v>-0.048</v>
+        <v>-0.062</v>
       </c>
       <c r="N16" s="15" t="n">
-        <v>-0.153</v>
+        <v>-0.115</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>-0.074</v>
+        <v>-0.057</v>
       </c>
       <c r="P16" s="15" t="n">
-        <v>-0.005</v>
+        <v>-0</v>
       </c>
       <c r="Q16" s="15" t="n">
-        <v>0.067</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="R16" s="15" t="n">
         <v>1</v>
@@ -2639,55 +2639,55 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>4.525</v>
+        <v>4.509</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>0.742</v>
+        <v>0.744</v>
       </c>
       <c r="D17" s="15" t="n">
         <v>0.85</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>-0.028</v>
+        <v>-0.024</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>0.028</v>
+        <v>0.008</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>0.028</v>
+        <v>0.038</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>0.11</v>
+        <v>0.062</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>0.006</v>
+        <v>-0.001</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>-0.006</v>
+        <v>0.005</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>-0.051</v>
+        <v>-0.031</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>-0.214</v>
+        <v>-0.26</v>
       </c>
       <c r="M17" s="15" t="n">
-        <v>0.245</v>
+        <v>0.272</v>
       </c>
       <c r="N17" s="15" t="n">
-        <v>-0.105</v>
+        <v>-0.095</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>-0.011</v>
+        <v>-0.032</v>
       </c>
       <c r="P17" s="15" t="n">
         <v>0.603</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>-0.634</v>
+        <v>-0.578</v>
       </c>
       <c r="R17" s="15" t="n">
-        <v>0.318</v>
+        <v>0.313</v>
       </c>
       <c r="S17" s="15" t="n">
         <v>1</v>
@@ -2702,58 +2702,58 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>4.831</v>
+        <v>4.718</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>1.212</v>
+        <v>1.233</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>-0.104</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>0.005</v>
+        <v>-0.027</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>0.05</v>
+        <v>0.066</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.04</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>0.035</v>
+        <v>0.029</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>-0.409</v>
+        <v>-0.46</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>0.434</v>
+        <v>0.415</v>
       </c>
       <c r="N18" s="15" t="n">
-        <v>0.079</v>
+        <v>-0.044</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>0.004</v>
+        <v>-0.026</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0.366</v>
+        <v>0.345</v>
       </c>
       <c r="Q18" s="15" t="n">
-        <v>-0.35</v>
+        <v>-0.294</v>
       </c>
       <c r="R18" s="15" t="n">
-        <v>-0.164</v>
+        <v>-0.094</v>
       </c>
       <c r="S18" s="15" t="n">
-        <v>0.196</v>
+        <v>0.249</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>1</v>
@@ -2767,61 +2767,61 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>2.527</v>
+        <v>2.632</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>1.09</v>
+        <v>1.122</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>0.82</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>0.033</v>
+        <v>0.052</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>-0</v>
+        <v>0.135</v>
       </c>
       <c r="H19" s="15" t="n">
+        <v>-0.051</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="J19" s="15" t="n">
         <v>0.031</v>
       </c>
-      <c r="I19" s="15" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="J19" s="15" t="n">
-        <v>-0.076</v>
-      </c>
       <c r="K19" s="15" t="n">
-        <v>-0.004</v>
+        <v>0.015</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>0.329</v>
+        <v>0.505</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>-0.493</v>
+        <v>-0.19</v>
       </c>
       <c r="N19" s="15" t="n">
-        <v>-0.005</v>
+        <v>-0.016</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>0.039</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>-0.375</v>
+        <v>-0.33</v>
       </c>
       <c r="Q19" s="15" t="n">
-        <v>0.368</v>
+        <v>0.309</v>
       </c>
       <c r="R19" s="15" t="n">
-        <v>0.143</v>
+        <v>0.131</v>
       </c>
       <c r="S19" s="15" t="n">
-        <v>-0.217</v>
+        <v>-0.18</v>
       </c>
       <c r="T19" s="15" t="n">
-        <v>-0.507</v>
+        <v>-0.322</v>
       </c>
       <c r="U19" s="15" t="n">
         <v>1</v>

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>30.756</v>
+        <v>30.74</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>4.688</v>
+        <v>4.596</v>
       </c>
       <c r="D3" s="15" t="inlineStr"/>
       <c r="E3" s="15" t="n">
@@ -2014,14 +2014,14 @@
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.551</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>0.497</v>
+        <v>0.498</v>
       </c>
       <c r="D4" s="15" t="inlineStr"/>
       <c r="E4" s="15" t="n">
-        <v>0.028</v>
+        <v>0.04</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>1</v>
@@ -2049,17 +2049,17 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>3.068</v>
+        <v>3.077</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>0.927</v>
+        <v>0.929</v>
       </c>
       <c r="D5" s="15" t="inlineStr"/>
       <c r="E5" s="15" t="n">
-        <v>-0.003</v>
+        <v>0.004</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>-0.064</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>1</v>
@@ -2086,20 +2086,20 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>2.545</v>
+        <v>2.548</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>1.131</v>
+        <v>1.125</v>
       </c>
       <c r="D6" s="15" t="inlineStr"/>
       <c r="E6" s="15" t="n">
-        <v>0.024</v>
+        <v>-0.012</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>-0.06</v>
+        <v>-0.053</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>-0.047</v>
+        <v>-0.006</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>1</v>
@@ -2125,23 +2125,23 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>9.007999999999999</v>
+        <v>8.912000000000001</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>4.909</v>
+        <v>4.85</v>
       </c>
       <c r="D7" s="15" t="inlineStr"/>
       <c r="E7" s="15" t="n">
-        <v>0.905</v>
+        <v>0.904</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0.004</v>
+        <v>0.01</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0.004</v>
+        <v>-0.015</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>0.047</v>
+        <v>0.015</v>
       </c>
       <c r="I7" s="15" t="n">
         <v>1</v>
@@ -2166,26 +2166,26 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>2.328</v>
+        <v>2.305</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>1.481</v>
+        <v>1.458</v>
       </c>
       <c r="D8" s="15" t="inlineStr"/>
       <c r="E8" s="15" t="n">
-        <v>0.187</v>
+        <v>0.184</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>-0.025</v>
+        <v>0.011</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>0.034</v>
+        <v>0.017</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>0.145</v>
+        <v>0.167</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>1</v>
@@ -2209,29 +2209,29 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>3.297</v>
+        <v>3.307</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>1.07</v>
+        <v>1.081</v>
       </c>
       <c r="D9" s="15" t="inlineStr"/>
       <c r="E9" s="15" t="n">
-        <v>-0.034</v>
+        <v>-0.038</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.122</v>
+        <v>0.063</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>-0.048</v>
+        <v>-0.042</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-0.081</v>
+        <v>-0.077</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-0.037</v>
+        <v>-0.025</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.027</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>1</v>
@@ -2254,34 +2254,34 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>4.054</v>
+        <v>4.062</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.609</v>
+        <v>0.623</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>0.041</v>
+        <v>0.004</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0.014</v>
+        <v>0.017</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.082</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.065</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-0.003</v>
+        <v>-0.028</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>0.037</v>
+        <v>0.056</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>0.055</v>
+        <v>0.029</v>
       </c>
       <c r="L10" s="15" t="n">
         <v>1</v>
@@ -2303,37 +2303,37 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>4.869</v>
+        <v>4.916</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0.653</v>
+        <v>0.638</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>0.87</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>-0.055</v>
+        <v>-0.04</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0.014</v>
+        <v>0.001</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.038</v>
+        <v>0.043</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-0.025</v>
+        <v>-0.024</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.005</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>-0.059</v>
+        <v>-0.063</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>-0.052</v>
+        <v>-0.037</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>-0.414</v>
+        <v>-0.371</v>
       </c>
       <c r="M11" s="15" t="n">
         <v>1</v>
@@ -2354,40 +2354,40 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>3.45</v>
+        <v>3.456</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.893</v>
+        <v>0.918</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>0.79</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>-0.027</v>
+        <v>-0.002</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>-0.063</v>
+        <v>-0.08</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>-0.058</v>
+        <v>-0.049</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>0.065</v>
+        <v>0.101</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>0.042</v>
+        <v>0.067</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>-0.063</v>
+        <v>-0.04</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>-0.001</v>
+        <v>0.023</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>0.031</v>
+        <v>0.041</v>
       </c>
       <c r="N12" s="15" t="n">
         <v>1</v>
@@ -2407,43 +2407,43 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>4.622</v>
+        <v>4.57</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.881</v>
+        <v>0.901</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>-0.047</v>
+        <v>-0.078</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>-0.113</v>
+        <v>-0.065</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0.001</v>
+        <v>-0.052</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>0.046</v>
+        <v>0.044</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-0.026</v>
+        <v>-0.051</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>-0.1</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="L13" s="15" t="n">
-        <v>-0.03</v>
+        <v>-0.001</v>
       </c>
       <c r="M13" s="15" t="n">
-        <v>-0.039</v>
+        <v>-0.091</v>
       </c>
       <c r="N13" s="15" t="n">
-        <v>0.015</v>
+        <v>-0.008</v>
       </c>
       <c r="O13" s="15" t="n">
         <v>1</v>
@@ -2462,46 +2462,46 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>4.45</v>
+        <v>4.51</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>1.246</v>
+        <v>1.234</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>0.84</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>-0.006</v>
+        <v>0.002</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>-0.044</v>
+        <v>-0.03</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>-0.016</v>
+        <v>0.02</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>0.054</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>-0.012</v>
+        <v>-0.067</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>-0.065</v>
+        <v>-0.045</v>
       </c>
       <c r="L14" s="15" t="n">
         <v>-0.376</v>
       </c>
       <c r="M14" s="15" t="n">
-        <v>0.382</v>
+        <v>0.355</v>
       </c>
       <c r="N14" s="15" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>-0.029</v>
+        <v>-0.025</v>
       </c>
       <c r="P14" s="15" t="n">
         <v>1</v>
@@ -2519,49 +2519,49 @@
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>3.084</v>
+        <v>3.046</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>1.215</v>
+        <v>1.217</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>0.026</v>
+        <v>-0.004</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0.031</v>
+        <v>0.019</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>-0.011</v>
+        <v>-0.015</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-0.081</v>
+        <v>-0.079</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-0.032</v>
+        <v>-0.056</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>-0.02</v>
+        <v>-0.005</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>0.026</v>
+        <v>0.046</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>0.334</v>
+        <v>0.329</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.348</v>
+        <v>-0.332</v>
       </c>
       <c r="N15" s="15" t="n">
-        <v>0.022</v>
+        <v>0.041</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.062</v>
+        <v>-0.066</v>
       </c>
       <c r="P15" s="15" t="n">
-        <v>-0.438</v>
+        <v>-0.431</v>
       </c>
       <c r="Q15" s="15" t="n">
         <v>1</v>
@@ -2578,52 +2578,52 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>4.382</v>
+        <v>4.372</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>0.655</v>
+        <v>0.647</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>0.036</v>
+        <v>0.007</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>-0.041</v>
+        <v>-0.025</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>0.054</v>
+        <v>0.014</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-0.013</v>
+        <v>-0.026</v>
       </c>
       <c r="J16" s="15" t="n">
         <v>-0.024</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>-0.021</v>
+        <v>-0.032</v>
       </c>
       <c r="L16" s="15" t="n">
-        <v>0.119</v>
+        <v>0.091</v>
       </c>
       <c r="M16" s="15" t="n">
-        <v>-0.062</v>
+        <v>-0.039</v>
       </c>
       <c r="N16" s="15" t="n">
-        <v>-0.115</v>
+        <v>-0.117</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>-0.057</v>
+        <v>-0.075</v>
       </c>
       <c r="P16" s="15" t="n">
         <v>-0</v>
       </c>
       <c r="Q16" s="15" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.061</v>
       </c>
       <c r="R16" s="15" t="n">
         <v>1</v>
@@ -2639,55 +2639,55 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>4.509</v>
+        <v>4.521</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>0.744</v>
+        <v>0.741</v>
       </c>
       <c r="D17" s="15" t="n">
         <v>0.85</v>
       </c>
       <c r="E17" s="15" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="J17" s="15" t="n">
         <v>-0.024</v>
       </c>
-      <c r="F17" s="15" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="G17" s="15" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="H17" s="15" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="I17" s="15" t="n">
-        <v>-0.001</v>
-      </c>
-      <c r="J17" s="15" t="n">
-        <v>0.005</v>
-      </c>
       <c r="K17" s="15" t="n">
-        <v>-0.031</v>
+        <v>-0.082</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>-0.26</v>
+        <v>-0.21</v>
       </c>
       <c r="M17" s="15" t="n">
-        <v>0.272</v>
+        <v>0.273</v>
       </c>
       <c r="N17" s="15" t="n">
-        <v>-0.095</v>
+        <v>-0.064</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>-0.032</v>
+        <v>-0.005</v>
       </c>
       <c r="P17" s="15" t="n">
-        <v>0.603</v>
+        <v>0.57</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>-0.578</v>
+        <v>-0.592</v>
       </c>
       <c r="R17" s="15" t="n">
-        <v>0.313</v>
+        <v>0.375</v>
       </c>
       <c r="S17" s="15" t="n">
         <v>1</v>
@@ -2702,58 +2702,58 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>4.718</v>
+        <v>4.809</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>1.233</v>
+        <v>1.186</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>-0.02</v>
+        <v>-0.091</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>-0.027</v>
+        <v>-0.025</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>0.066</v>
+        <v>-0.025</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-0.04</v>
+        <v>0.048</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>0.045</v>
+        <v>-0.095</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>0.029</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>-0.46</v>
+        <v>-0.442</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>0.415</v>
+        <v>0.493</v>
       </c>
       <c r="N18" s="15" t="n">
-        <v>-0.044</v>
+        <v>-0.073</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>-0.026</v>
+        <v>-0.028</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0.345</v>
+        <v>0.414</v>
       </c>
       <c r="Q18" s="15" t="n">
-        <v>-0.294</v>
+        <v>-0.36</v>
       </c>
       <c r="R18" s="15" t="n">
-        <v>-0.094</v>
+        <v>0.012</v>
       </c>
       <c r="S18" s="15" t="n">
-        <v>0.249</v>
+        <v>0.262</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>1</v>
@@ -2767,61 +2767,61 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>2.632</v>
+        <v>2.507</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>1.122</v>
+        <v>1.027</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>0.82</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>0.052</v>
+        <v>0.042</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>0.007</v>
+        <v>0.014</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>0.135</v>
+        <v>0.032</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-0.051</v>
+        <v>0.01</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>0.012</v>
+        <v>0.017</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>0.031</v>
+        <v>0.017</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>0.015</v>
+        <v>0.032</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>0.505</v>
+        <v>0.319</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>-0.19</v>
+        <v>-0.464</v>
       </c>
       <c r="N19" s="15" t="n">
-        <v>-0.016</v>
+        <v>0.038</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.045</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>-0.33</v>
+        <v>-0.309</v>
       </c>
       <c r="Q19" s="15" t="n">
-        <v>0.309</v>
+        <v>0.361</v>
       </c>
       <c r="R19" s="15" t="n">
-        <v>0.131</v>
+        <v>0.024</v>
       </c>
       <c r="S19" s="15" t="n">
-        <v>-0.18</v>
+        <v>-0.276</v>
       </c>
       <c r="T19" s="15" t="n">
-        <v>-0.322</v>
+        <v>-0.493</v>
       </c>
       <c r="U19" s="15" t="n">
         <v>1</v>

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>30.74</v>
+        <v>30.636</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>4.596</v>
+        <v>4.537</v>
       </c>
       <c r="D3" s="15" t="inlineStr"/>
       <c r="E3" s="15" t="n">
@@ -2014,14 +2014,14 @@
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>0.551</v>
+        <v>0.543</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>0.498</v>
+        <v>0.499</v>
       </c>
       <c r="D4" s="15" t="inlineStr"/>
       <c r="E4" s="15" t="n">
-        <v>0.04</v>
+        <v>0.031</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>1</v>
@@ -2049,17 +2049,17 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>3.077</v>
+        <v>3.084</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>0.929</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="D5" s="15" t="inlineStr"/>
       <c r="E5" s="15" t="n">
-        <v>0.004</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.092</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>1</v>
@@ -2086,20 +2086,20 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>2.548</v>
+        <v>2.546</v>
       </c>
       <c r="C6" s="15" t="n">
         <v>1.125</v>
       </c>
       <c r="D6" s="15" t="inlineStr"/>
       <c r="E6" s="15" t="n">
-        <v>-0.012</v>
+        <v>-0.004</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>-0.053</v>
+        <v>-0.019</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>-0.006</v>
+        <v>0.007</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>1</v>
@@ -2125,23 +2125,23 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>8.912000000000001</v>
+        <v>8.862</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>4.85</v>
+        <v>4.827</v>
       </c>
       <c r="D7" s="15" t="inlineStr"/>
       <c r="E7" s="15" t="n">
-        <v>0.904</v>
+        <v>0.905</v>
       </c>
       <c r="F7" s="15" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="H7" s="15" t="n">
         <v>0.01</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>-0.015</v>
-      </c>
-      <c r="H7" s="15" t="n">
-        <v>0.015</v>
       </c>
       <c r="I7" s="15" t="n">
         <v>1</v>
@@ -2166,26 +2166,26 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>2.305</v>
+        <v>2.307</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>1.458</v>
+        <v>1.45</v>
       </c>
       <c r="D8" s="15" t="inlineStr"/>
       <c r="E8" s="15" t="n">
-        <v>0.184</v>
+        <v>0.2</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>0.017</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>0.167</v>
+        <v>0.169</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>1</v>
@@ -2209,29 +2209,29 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>3.307</v>
+        <v>3.289</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>1.081</v>
+        <v>1.088</v>
       </c>
       <c r="D9" s="15" t="inlineStr"/>
       <c r="E9" s="15" t="n">
-        <v>-0.038</v>
+        <v>-0.022</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.063</v>
+        <v>0.061</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>-0.042</v>
+        <v>-0.051</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-0.077</v>
+        <v>-0.061</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-0.025</v>
+        <v>-0.014</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>-0.027</v>
+        <v>-0.046</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>1</v>
@@ -2254,34 +2254,34 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>4.062</v>
+        <v>4.04</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.623</v>
+        <v>0.601</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0.017</v>
+        <v>0.007</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.082</v>
+        <v>0.064</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-0.065</v>
+        <v>-0.093</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-0.028</v>
+        <v>-0.04</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>0.056</v>
+        <v>0.018</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>0.029</v>
+        <v>0.033</v>
       </c>
       <c r="L10" s="15" t="n">
         <v>1</v>
@@ -2303,37 +2303,37 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>4.916</v>
+        <v>4.931</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0.638</v>
+        <v>0.625</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>0.87</v>
       </c>
       <c r="E11" s="15" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>-0.052</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="J11" s="15" t="n">
         <v>-0.04</v>
       </c>
-      <c r="F11" s="15" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="H11" s="15" t="n">
-        <v>-0.024</v>
-      </c>
-      <c r="I11" s="15" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="J11" s="15" t="n">
-        <v>-0.063</v>
-      </c>
       <c r="K11" s="15" t="n">
-        <v>-0.037</v>
+        <v>-0.061</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>-0.371</v>
+        <v>-0.406</v>
       </c>
       <c r="M11" s="15" t="n">
         <v>1</v>
@@ -2354,40 +2354,40 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>3.456</v>
+        <v>3.449</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.918</v>
+        <v>0.915</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>0.79</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>-0.002</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>-0.08</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>-0.049</v>
+        <v>-0.056</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>0.101</v>
+        <v>0.073</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>0.067</v>
+        <v>0.078</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>0.09</v>
+        <v>0.038</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>-0.04</v>
+        <v>-0.036</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>0.023</v>
+        <v>-0.004</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>0.041</v>
+        <v>0.065</v>
       </c>
       <c r="N12" s="15" t="n">
         <v>1</v>
@@ -2407,43 +2407,43 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>4.57</v>
+        <v>4.592</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.901</v>
+        <v>0.871</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>0.74</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>-0.078</v>
+        <v>-0.075</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>-0.065</v>
+        <v>-0.082</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>-0.052</v>
+        <v>-0.059</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>0.044</v>
+        <v>0.067</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-0.051</v>
+        <v>-0.034</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.045</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.1</v>
       </c>
       <c r="L13" s="15" t="n">
-        <v>-0.001</v>
+        <v>-0.025</v>
       </c>
       <c r="M13" s="15" t="n">
-        <v>-0.091</v>
+        <v>-0.094</v>
       </c>
       <c r="N13" s="15" t="n">
-        <v>-0.008</v>
+        <v>0.005</v>
       </c>
       <c r="O13" s="15" t="n">
         <v>1</v>
@@ -2462,46 +2462,46 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>4.51</v>
+        <v>4.526</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>1.234</v>
+        <v>1.254</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>0.84</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>0.002</v>
+        <v>-0.005</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>-0.03</v>
+        <v>-0.032</v>
       </c>
       <c r="G14" s="15" t="n">
         <v>0.02</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.057</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>-0.067</v>
+        <v>-0.034</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>-0.045</v>
+        <v>-0.055</v>
       </c>
       <c r="L14" s="15" t="n">
-        <v>-0.376</v>
+        <v>-0.349</v>
       </c>
       <c r="M14" s="15" t="n">
-        <v>0.355</v>
+        <v>0.345</v>
       </c>
       <c r="N14" s="15" t="n">
-        <v>0.002</v>
+        <v>0.016</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>-0.025</v>
+        <v>-0.042</v>
       </c>
       <c r="P14" s="15" t="n">
         <v>1</v>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>3.046</v>
+        <v>3.035</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>1.217</v>
+        <v>1.206</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>0.8100000000000001</v>
@@ -2531,37 +2531,37 @@
         <v>-0.004</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0.019</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>-0.015</v>
+        <v>-0.042</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-0.079</v>
+        <v>-0.083</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-0.056</v>
+        <v>-0.06</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>-0.005</v>
+        <v>-0.02</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>0.046</v>
+        <v>0.06</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>0.329</v>
+        <v>0.335</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.332</v>
+        <v>-0.345</v>
       </c>
       <c r="N15" s="15" t="n">
-        <v>0.041</v>
+        <v>0.01</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.066</v>
+        <v>-0.061</v>
       </c>
       <c r="P15" s="15" t="n">
-        <v>-0.431</v>
+        <v>-0.45</v>
       </c>
       <c r="Q15" s="15" t="n">
         <v>1</v>
@@ -2578,52 +2578,52 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>4.372</v>
+        <v>4.373</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>0.647</v>
+        <v>0.654</v>
       </c>
       <c r="D16" s="15" t="n">
         <v>0.75</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>-0</v>
+        <v>-0.02</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>0.007</v>
+        <v>0.045</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>-0.025</v>
+        <v>-0.027</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>0.014</v>
+        <v>0.027</v>
       </c>
       <c r="I16" s="15" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="J16" s="15" t="n">
+        <v>-0.037</v>
+      </c>
+      <c r="K16" s="15" t="n">
         <v>-0.026</v>
       </c>
-      <c r="J16" s="15" t="n">
-        <v>-0.024</v>
-      </c>
-      <c r="K16" s="15" t="n">
-        <v>-0.032</v>
-      </c>
       <c r="L16" s="15" t="n">
-        <v>0.091</v>
+        <v>0.097</v>
       </c>
       <c r="M16" s="15" t="n">
-        <v>-0.039</v>
+        <v>-0.049</v>
       </c>
       <c r="N16" s="15" t="n">
-        <v>-0.117</v>
+        <v>-0.103</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>-0.075</v>
+        <v>-0.076</v>
       </c>
       <c r="P16" s="15" t="n">
-        <v>-0</v>
+        <v>-0.013</v>
       </c>
       <c r="Q16" s="15" t="n">
-        <v>0.061</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R16" s="15" t="n">
         <v>1</v>
@@ -2639,55 +2639,55 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>4.521</v>
+        <v>4.516</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>0.741</v>
+        <v>0.783</v>
       </c>
       <c r="D17" s="15" t="n">
         <v>0.85</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>0.041</v>
+        <v>-0.001</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>0.01</v>
+        <v>-0.015</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>0.036</v>
+        <v>0.053</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>0.089</v>
+        <v>0.035</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>-0.024</v>
+        <v>0.048</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>-0.082</v>
+        <v>-0.083</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>-0.21</v>
+        <v>-0.275</v>
       </c>
       <c r="M17" s="15" t="n">
-        <v>0.273</v>
+        <v>0.293</v>
       </c>
       <c r="N17" s="15" t="n">
-        <v>-0.064</v>
+        <v>-0.03</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>-0.005</v>
+        <v>-0.046</v>
       </c>
       <c r="P17" s="15" t="n">
-        <v>0.57</v>
+        <v>0.681</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>-0.592</v>
+        <v>-0.59</v>
       </c>
       <c r="R17" s="15" t="n">
-        <v>0.375</v>
+        <v>0.292</v>
       </c>
       <c r="S17" s="15" t="n">
         <v>1</v>
@@ -2702,58 +2702,58 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>4.809</v>
+        <v>4.69</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>1.186</v>
+        <v>1.286</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>-0</v>
+        <v>-0.063</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>-0.091</v>
+        <v>-0.033</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>-0.025</v>
+        <v>0.029</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-0.025</v>
+        <v>0.099</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>0.048</v>
+        <v>-0.014</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>-0.095</v>
+        <v>-0.037</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.077</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>-0.442</v>
+        <v>-0.449</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>0.493</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="N18" s="15" t="n">
-        <v>-0.073</v>
+        <v>-0.068</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>-0.028</v>
+        <v>-0.024</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0.414</v>
+        <v>0.427</v>
       </c>
       <c r="Q18" s="15" t="n">
-        <v>-0.36</v>
+        <v>-0.333</v>
       </c>
       <c r="R18" s="15" t="n">
-        <v>0.012</v>
+        <v>-0.032</v>
       </c>
       <c r="S18" s="15" t="n">
-        <v>0.262</v>
+        <v>0.359</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>1</v>
@@ -2767,61 +2767,61 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>2.507</v>
+        <v>2.559</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>1.027</v>
+        <v>1.071</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>0.82</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>0.042</v>
+        <v>0.015</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>0.014</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>0.032</v>
+        <v>-0.045</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>0.01</v>
+        <v>-0.092</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>0.017</v>
+        <v>-0.031</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>0.017</v>
+        <v>-0.006</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>0.032</v>
+        <v>0.015</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>0.319</v>
+        <v>0.416</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>-0.464</v>
+        <v>-0.379</v>
       </c>
       <c r="N19" s="15" t="n">
-        <v>0.038</v>
+        <v>0.023</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>-0.045</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>-0.309</v>
+        <v>-0.332</v>
       </c>
       <c r="Q19" s="15" t="n">
-        <v>0.361</v>
+        <v>0.334</v>
       </c>
       <c r="R19" s="15" t="n">
-        <v>0.024</v>
+        <v>-0.064</v>
       </c>
       <c r="S19" s="15" t="n">
-        <v>-0.276</v>
+        <v>-0.325</v>
       </c>
       <c r="T19" s="15" t="n">
-        <v>-0.493</v>
+        <v>-0.444</v>
       </c>
       <c r="U19" s="15" t="n">
         <v>1</v>

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>30.636</v>
+        <v>30.623</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>4.537</v>
+        <v>4.613</v>
       </c>
       <c r="D3" s="15" t="inlineStr"/>
       <c r="E3" s="15" t="n">
@@ -2014,14 +2014,14 @@
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>0.543</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>0.499</v>
+        <v>0.497</v>
       </c>
       <c r="D4" s="15" t="inlineStr"/>
       <c r="E4" s="15" t="n">
-        <v>0.031</v>
+        <v>0.015</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>1</v>
@@ -2049,17 +2049,17 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>3.084</v>
+        <v>3.081</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="D5" s="15" t="inlineStr"/>
       <c r="E5" s="15" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.014</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>-0.092</v>
+        <v>-0.073</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>1</v>
@@ -2086,20 +2086,20 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>2.546</v>
+        <v>2.528</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>1.125</v>
+        <v>1.127</v>
       </c>
       <c r="D6" s="15" t="inlineStr"/>
       <c r="E6" s="15" t="n">
-        <v>-0.004</v>
+        <v>-0.028</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>-0.019</v>
+        <v>-0.03</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0.007</v>
+        <v>-0.007</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>1</v>
@@ -2125,23 +2125,23 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>8.862</v>
+        <v>8.787000000000001</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>4.827</v>
+        <v>4.772</v>
       </c>
       <c r="D7" s="15" t="inlineStr"/>
       <c r="E7" s="15" t="n">
-        <v>0.905</v>
+        <v>0.903</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0.006</v>
+        <v>-0.004</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>-0.004</v>
+        <v>-0.018</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>0.01</v>
+        <v>-0.015</v>
       </c>
       <c r="I7" s="15" t="n">
         <v>1</v>
@@ -2166,26 +2166,26 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>2.307</v>
+        <v>2.314</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>1.45</v>
+        <v>1.466</v>
       </c>
       <c r="D8" s="15" t="inlineStr"/>
       <c r="E8" s="15" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0.002</v>
+        <v>-0.046</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>-0.034</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>0.017</v>
+        <v>0.038</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>0.169</v>
+        <v>0.182</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>1</v>
@@ -2209,29 +2209,29 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>3.289</v>
+        <v>3.299</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>1.088</v>
+        <v>1.085</v>
       </c>
       <c r="D9" s="15" t="inlineStr"/>
       <c r="E9" s="15" t="n">
-        <v>-0.022</v>
+        <v>0.003</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.061</v>
+        <v>0.082</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>-0.051</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-0.061</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-0.014</v>
+        <v>0.028</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>-0.046</v>
+        <v>-0.054</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>1</v>
@@ -2254,34 +2254,34 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>4.04</v>
+        <v>4.088</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.601</v>
+        <v>0.612</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>0.003</v>
+        <v>0.036</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0.007</v>
+        <v>-0.006</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.064</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-0.093</v>
+        <v>-0.092</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-0.04</v>
+        <v>0.001</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>0.018</v>
+        <v>0.044</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>0.033</v>
+        <v>0.012</v>
       </c>
       <c r="L10" s="15" t="n">
         <v>1</v>
@@ -2303,37 +2303,37 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>4.931</v>
+        <v>4.891</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0.625</v>
+        <v>0.644</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>0.87</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>-0.046</v>
+        <v>-0.061</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0.014</v>
+        <v>0.004</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.078</v>
+        <v>0.023</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-0.052</v>
+        <v>-0.039</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-0.004</v>
+        <v>-0.022</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>-0.04</v>
+        <v>-0.039</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>-0.061</v>
+        <v>-0.043</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>-0.406</v>
+        <v>-0.411</v>
       </c>
       <c r="M11" s="15" t="n">
         <v>1</v>
@@ -2354,40 +2354,40 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>3.449</v>
+        <v>3.48</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.915</v>
+        <v>0.891</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>0.79</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.036</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.043</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>-0.056</v>
+        <v>-0.028</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>0.073</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>0.078</v>
+        <v>0.026</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>0.038</v>
+        <v>0.107</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>-0.036</v>
+        <v>-0.046</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>-0.004</v>
+        <v>0.006</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>0.065</v>
+        <v>0.061</v>
       </c>
       <c r="N12" s="15" t="n">
         <v>1</v>
@@ -2407,43 +2407,43 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>4.592</v>
+        <v>4.569</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.871</v>
+        <v>0.883</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>0.74</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>-0.075</v>
+        <v>-0.099</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>-0.082</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>-0.059</v>
+        <v>-0.027</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>0.067</v>
+        <v>0.065</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-0.034</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>-0.045</v>
+        <v>-0.102</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>-0.1</v>
+        <v>-0.066</v>
       </c>
       <c r="L13" s="15" t="n">
-        <v>-0.025</v>
+        <v>0.016</v>
       </c>
       <c r="M13" s="15" t="n">
         <v>-0.094</v>
       </c>
       <c r="N13" s="15" t="n">
-        <v>0.005</v>
+        <v>-0.043</v>
       </c>
       <c r="O13" s="15" t="n">
         <v>1</v>
@@ -2462,46 +2462,46 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>4.526</v>
+        <v>4.444</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>1.254</v>
+        <v>1.232</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>0.84</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>-0.005</v>
+        <v>-0.034</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>-0.032</v>
+        <v>-0.038</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0.02</v>
+        <v>-0.031</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>0.05</v>
+        <v>0.067</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>0.057</v>
+        <v>0.027</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>-0.034</v>
+        <v>-0.029</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>-0.055</v>
+        <v>-0.057</v>
       </c>
       <c r="L14" s="15" t="n">
-        <v>-0.349</v>
+        <v>-0.381</v>
       </c>
       <c r="M14" s="15" t="n">
-        <v>0.345</v>
+        <v>0.38</v>
       </c>
       <c r="N14" s="15" t="n">
-        <v>0.016</v>
+        <v>-0.011</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>-0.042</v>
+        <v>-0.021</v>
       </c>
       <c r="P14" s="15" t="n">
         <v>1</v>
@@ -2519,49 +2519,49 @@
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>3.035</v>
+        <v>3.068</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>1.206</v>
+        <v>1.173</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>-0.004</v>
+        <v>-0.022</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.017</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>-0.042</v>
+        <v>0.01</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-0.083</v>
+        <v>-0.092</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-0.06</v>
+        <v>-0.061</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>-0.02</v>
+        <v>0.007</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>0.06</v>
+        <v>0.051</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>0.335</v>
+        <v>0.357</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.345</v>
+        <v>-0.36</v>
       </c>
       <c r="N15" s="15" t="n">
-        <v>0.01</v>
+        <v>0.032</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.061</v>
+        <v>-0.058</v>
       </c>
       <c r="P15" s="15" t="n">
-        <v>-0.45</v>
+        <v>-0.466</v>
       </c>
       <c r="Q15" s="15" t="n">
         <v>1</v>
@@ -2578,52 +2578,52 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>4.373</v>
+        <v>4.392</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>0.654</v>
+        <v>0.639</v>
       </c>
       <c r="D16" s="15" t="n">
         <v>0.75</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>-0.02</v>
+        <v>-0.016</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0.045</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>-0.027</v>
+        <v>-0.046</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>0.027</v>
+        <v>0.053</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-0.04</v>
+        <v>-0.037</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>-0.037</v>
+        <v>-0.002</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>-0.026</v>
+        <v>-0.017</v>
       </c>
       <c r="L16" s="15" t="n">
-        <v>0.097</v>
+        <v>0.106</v>
       </c>
       <c r="M16" s="15" t="n">
-        <v>-0.049</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N16" s="15" t="n">
-        <v>-0.103</v>
+        <v>-0.118</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>-0.076</v>
+        <v>-0.068</v>
       </c>
       <c r="P16" s="15" t="n">
-        <v>-0.013</v>
+        <v>-0.03</v>
       </c>
       <c r="Q16" s="15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.045</v>
       </c>
       <c r="R16" s="15" t="n">
         <v>1</v>
@@ -2639,55 +2639,55 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>4.516</v>
+        <v>4.52</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>0.783</v>
+        <v>0.779</v>
       </c>
       <c r="D17" s="15" t="n">
         <v>0.85</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>-0.015</v>
+        <v>-0.026</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>0</v>
+        <v>-0.045</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>0.053</v>
+        <v>0.127</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>0.035</v>
+        <v>0.024</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>0.048</v>
+        <v>0.007</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>-0.083</v>
+        <v>-0.09</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>-0.275</v>
+        <v>-0.277</v>
       </c>
       <c r="M17" s="15" t="n">
-        <v>0.293</v>
+        <v>0.312</v>
       </c>
       <c r="N17" s="15" t="n">
-        <v>-0.03</v>
+        <v>-0.058</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>-0.046</v>
+        <v>-0.017</v>
       </c>
       <c r="P17" s="15" t="n">
-        <v>0.681</v>
+        <v>0.614</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>-0.59</v>
+        <v>-0.608</v>
       </c>
       <c r="R17" s="15" t="n">
-        <v>0.292</v>
+        <v>0.356</v>
       </c>
       <c r="S17" s="15" t="n">
         <v>1</v>
@@ -2702,58 +2702,58 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>4.69</v>
+        <v>4.793</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>1.286</v>
+        <v>1.214</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>-0.063</v>
+        <v>-0.016</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>-0.033</v>
+        <v>-0.011</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>0.099</v>
+        <v>0.064</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-0.014</v>
+        <v>0.004</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>-0.037</v>
+        <v>-0.025</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>-0.077</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>-0.449</v>
+        <v>-0.492</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="N18" s="15" t="n">
-        <v>-0.068</v>
+        <v>0.097</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>-0.024</v>
+        <v>-0.015</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0.427</v>
+        <v>0.35</v>
       </c>
       <c r="Q18" s="15" t="n">
-        <v>-0.333</v>
+        <v>-0.404</v>
       </c>
       <c r="R18" s="15" t="n">
-        <v>-0.032</v>
+        <v>-0.108</v>
       </c>
       <c r="S18" s="15" t="n">
-        <v>0.359</v>
+        <v>0.27</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>1</v>
@@ -2767,61 +2767,61 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>2.559</v>
+        <v>2.493</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>1.071</v>
+        <v>0.96</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>0.015</v>
+        <v>-0.006</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.048</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>-0.045</v>
+        <v>-0.003</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-0.092</v>
+        <v>-0.059</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-0.031</v>
+        <v>-0.029</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>-0.006</v>
+        <v>-0.064</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>0.015</v>
+        <v>0.024</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>0.416</v>
+        <v>0.304</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>-0.379</v>
+        <v>-0.352</v>
       </c>
       <c r="N19" s="15" t="n">
-        <v>0.023</v>
+        <v>-0.033</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.036</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>-0.332</v>
+        <v>-0.319</v>
       </c>
       <c r="Q19" s="15" t="n">
         <v>0.334</v>
       </c>
       <c r="R19" s="15" t="n">
-        <v>-0.064</v>
+        <v>0.165</v>
       </c>
       <c r="S19" s="15" t="n">
-        <v>-0.325</v>
+        <v>-0.19</v>
       </c>
       <c r="T19" s="15" t="n">
-        <v>-0.444</v>
+        <v>-0.425</v>
       </c>
       <c r="U19" s="15" t="n">
         <v>1</v>

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>30.623</v>
+        <v>30.638</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>4.613</v>
+        <v>4.607</v>
       </c>
       <c r="D3" s="15" t="inlineStr"/>
       <c r="E3" s="15" t="n">
@@ -2014,14 +2014,14 @@
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="C4" s="15" t="n">
         <v>0.497</v>
       </c>
       <c r="D4" s="15" t="inlineStr"/>
       <c r="E4" s="15" t="n">
-        <v>0.015</v>
+        <v>0.04</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>1</v>
@@ -2049,17 +2049,17 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>3.081</v>
+        <v>3.095</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="D5" s="15" t="inlineStr"/>
       <c r="E5" s="15" t="n">
-        <v>-0.014</v>
+        <v>0.019</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>-0.073</v>
+        <v>-0.066</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>1</v>
@@ -2086,20 +2086,20 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>2.528</v>
+        <v>2.609</v>
       </c>
       <c r="C6" s="15" t="n">
         <v>1.127</v>
       </c>
       <c r="D6" s="15" t="inlineStr"/>
       <c r="E6" s="15" t="n">
-        <v>-0.028</v>
+        <v>0.016</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>-0.03</v>
+        <v>-0.051</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>-0.007</v>
+        <v>-0.004</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>1</v>
@@ -2125,23 +2125,23 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>8.787000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>4.772</v>
+        <v>4.787</v>
       </c>
       <c r="D7" s="15" t="inlineStr"/>
       <c r="E7" s="15" t="n">
-        <v>0.903</v>
+        <v>0.902</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>-0.004</v>
+        <v>0.018</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>-0.018</v>
+        <v>0.01</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-0.015</v>
+        <v>0.037</v>
       </c>
       <c r="I7" s="15" t="n">
         <v>1</v>
@@ -2166,26 +2166,26 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>2.314</v>
+        <v>2.349</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>1.466</v>
+        <v>1.511</v>
       </c>
       <c r="D8" s="15" t="inlineStr"/>
       <c r="E8" s="15" t="n">
-        <v>0.22</v>
+        <v>0.199</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>-0.046</v>
+        <v>-0.024</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>-0.034</v>
+        <v>0.004</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>0.038</v>
+        <v>-0.006</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>0.182</v>
+        <v>0.163</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>1</v>
@@ -2209,29 +2209,29 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>3.299</v>
+        <v>3.249</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>1.085</v>
+        <v>1.076</v>
       </c>
       <c r="D9" s="15" t="inlineStr"/>
       <c r="E9" s="15" t="n">
-        <v>0.003</v>
+        <v>-0.001</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.082</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.074</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>0.028</v>
+        <v>0.008</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>-0.054</v>
+        <v>-0.046</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>1</v>
@@ -2254,34 +2254,34 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>4.088</v>
+        <v>4.009</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.612</v>
+        <v>0.572</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>0.036</v>
+        <v>0.014</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>-0.006</v>
+        <v>0.023</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.089</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-0.092</v>
+        <v>-0.045</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>0.001</v>
+        <v>-0.03</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>0.044</v>
+        <v>0.058</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>0.012</v>
+        <v>-0.002</v>
       </c>
       <c r="L10" s="15" t="n">
         <v>1</v>
@@ -2303,37 +2303,37 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>4.891</v>
+        <v>4.92</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0.644</v>
+        <v>0.637</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>0.87</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>-0.061</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.023</v>
+        <v>0.046</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-0.039</v>
+        <v>-0.046</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-0.022</v>
+        <v>-0.019</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>-0.039</v>
+        <v>-0.059</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>-0.043</v>
+        <v>-0.055</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>-0.411</v>
+        <v>-0.369</v>
       </c>
       <c r="M11" s="15" t="n">
         <v>1</v>
@@ -2354,40 +2354,40 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>3.48</v>
+        <v>3.466</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.891</v>
+        <v>0.894</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>0.79</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>-0.036</v>
+        <v>-0.032</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>-0.043</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>-0.028</v>
+        <v>-0.024</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.064</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>0.026</v>
+        <v>0.034</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>0.107</v>
+        <v>0.043</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>-0.046</v>
+        <v>-0.022</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>0.006</v>
+        <v>0.037</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>0.061</v>
+        <v>0.038</v>
       </c>
       <c r="N12" s="15" t="n">
         <v>1</v>
@@ -2407,43 +2407,43 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>4.569</v>
+        <v>4.583</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.883</v>
+        <v>0.893</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>0.74</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>-0.099</v>
+        <v>-0.095</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>-0.027</v>
+        <v>-0.049</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>0.065</v>
+        <v>0.093</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.079</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>-0.102</v>
+        <v>-0.079</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>-0.066</v>
+        <v>-0.098</v>
       </c>
       <c r="L13" s="15" t="n">
-        <v>0.016</v>
+        <v>-0.029</v>
       </c>
       <c r="M13" s="15" t="n">
-        <v>-0.094</v>
+        <v>-0.076</v>
       </c>
       <c r="N13" s="15" t="n">
-        <v>-0.043</v>
+        <v>-0.008</v>
       </c>
       <c r="O13" s="15" t="n">
         <v>1</v>
@@ -2462,46 +2462,46 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>4.444</v>
+        <v>4.527</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>1.232</v>
+        <v>1.239</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>0.84</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>-0.034</v>
+        <v>-0.026</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>-0.038</v>
+        <v>-0.053</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>-0.031</v>
+        <v>-0.015</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>0.067</v>
+        <v>0.04</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>0.027</v>
+        <v>0.04</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>-0.029</v>
+        <v>-0.045</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>-0.057</v>
+        <v>-0.068</v>
       </c>
       <c r="L14" s="15" t="n">
-        <v>-0.381</v>
+        <v>-0.359</v>
       </c>
       <c r="M14" s="15" t="n">
-        <v>0.38</v>
+        <v>0.371</v>
       </c>
       <c r="N14" s="15" t="n">
-        <v>-0.011</v>
+        <v>0.004</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>-0.021</v>
+        <v>-0.024</v>
       </c>
       <c r="P14" s="15" t="n">
         <v>1</v>
@@ -2519,49 +2519,49 @@
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>3.068</v>
+        <v>3.024</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>1.173</v>
+        <v>1.157</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>-0.022</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0.017</v>
+        <v>0.043</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0.01</v>
+        <v>-0.004</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-0.092</v>
+        <v>-0.033</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-0.061</v>
+        <v>-0.039</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>0.007</v>
+        <v>-0.012</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>0.051</v>
+        <v>0.033</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>0.357</v>
+        <v>0.306</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.36</v>
+        <v>-0.352</v>
       </c>
       <c r="N15" s="15" t="n">
-        <v>0.032</v>
+        <v>0.033</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.058</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="P15" s="15" t="n">
-        <v>-0.466</v>
+        <v>-0.46</v>
       </c>
       <c r="Q15" s="15" t="n">
         <v>1</v>
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>4.392</v>
+        <v>4.389</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>0.639</v>
+        <v>0.621</v>
       </c>
       <c r="D16" s="15" t="n">
         <v>0.75</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>-0.016</v>
+        <v>0.044</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>0.045</v>
+        <v>0.019</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>-0.046</v>
+        <v>-0.042</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>0.053</v>
+        <v>0.058</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-0.037</v>
+        <v>0.043</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>-0.002</v>
+        <v>-0.021</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>-0.017</v>
+        <v>0.013</v>
       </c>
       <c r="L16" s="15" t="n">
-        <v>0.106</v>
+        <v>0.104</v>
       </c>
       <c r="M16" s="15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.024</v>
       </c>
       <c r="N16" s="15" t="n">
-        <v>-0.118</v>
+        <v>-0.102</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>-0.068</v>
+        <v>-0.028</v>
       </c>
       <c r="P16" s="15" t="n">
-        <v>-0.03</v>
+        <v>-0.004</v>
       </c>
       <c r="Q16" s="15" t="n">
         <v>0.045</v>
@@ -2639,55 +2639,55 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>4.52</v>
+        <v>4.51</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>0.779</v>
+        <v>0.805</v>
       </c>
       <c r="D17" s="15" t="n">
         <v>0.85</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>0</v>
+        <v>-0.021</v>
       </c>
       <c r="F17" s="15" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J17" s="15" t="n">
         <v>-0.026</v>
       </c>
-      <c r="G17" s="15" t="n">
-        <v>-0.045</v>
-      </c>
-      <c r="H17" s="15" t="n">
-        <v>0.127</v>
-      </c>
-      <c r="I17" s="15" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="J17" s="15" t="n">
-        <v>0.007</v>
-      </c>
       <c r="K17" s="15" t="n">
-        <v>-0.09</v>
+        <v>-0.043</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>-0.277</v>
+        <v>-0.237</v>
       </c>
       <c r="M17" s="15" t="n">
-        <v>0.312</v>
+        <v>0.311</v>
       </c>
       <c r="N17" s="15" t="n">
-        <v>-0.058</v>
+        <v>-0.041</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>-0.017</v>
+        <v>-0.001</v>
       </c>
       <c r="P17" s="15" t="n">
-        <v>0.614</v>
+        <v>0.571</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>-0.608</v>
+        <v>-0.595</v>
       </c>
       <c r="R17" s="15" t="n">
-        <v>0.356</v>
+        <v>0.43</v>
       </c>
       <c r="S17" s="15" t="n">
         <v>1</v>
@@ -2702,58 +2702,58 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>4.793</v>
+        <v>4.698</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>1.214</v>
+        <v>1.193</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>-0.016</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>-0.011</v>
+        <v>-0.025</v>
       </c>
       <c r="G18" s="15" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>0.064</v>
+        <v>-0.026</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>0.004</v>
+        <v>-0.046</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>-0.025</v>
+        <v>-0.023</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>-0.492</v>
+        <v>-0.3</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.535</v>
       </c>
       <c r="N18" s="15" t="n">
-        <v>0.097</v>
+        <v>-0.092</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>-0.015</v>
+        <v>-0.091</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0.35</v>
+        <v>0.376</v>
       </c>
       <c r="Q18" s="15" t="n">
-        <v>-0.404</v>
+        <v>-0.345</v>
       </c>
       <c r="R18" s="15" t="n">
-        <v>-0.108</v>
+        <v>0.021</v>
       </c>
       <c r="S18" s="15" t="n">
-        <v>0.27</v>
+        <v>0.266</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>1</v>
@@ -2767,61 +2767,61 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>2.493</v>
+        <v>2.672</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>0.96</v>
+        <v>1.045</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>0.78</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>-0.006</v>
+        <v>0.03</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>0.048</v>
+        <v>0.054</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>-0.003</v>
+        <v>0.015</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-0.059</v>
+        <v>-0.019</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-0.029</v>
+        <v>-0.008</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>-0.064</v>
+        <v>0.042</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>0.024</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>0.304</v>
+        <v>0.54</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>-0.352</v>
+        <v>-0.4</v>
       </c>
       <c r="N19" s="15" t="n">
-        <v>-0.033</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>0.036</v>
+        <v>-0.052</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>-0.319</v>
+        <v>-0.365</v>
       </c>
       <c r="Q19" s="15" t="n">
-        <v>0.334</v>
+        <v>0.316</v>
       </c>
       <c r="R19" s="15" t="n">
-        <v>0.165</v>
+        <v>0.089</v>
       </c>
       <c r="S19" s="15" t="n">
-        <v>-0.19</v>
+        <v>-0.251</v>
       </c>
       <c r="T19" s="15" t="n">
-        <v>-0.425</v>
+        <v>-0.419</v>
       </c>
       <c r="U19" s="15" t="n">
         <v>1</v>

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>30.638</v>
+        <v>30.832</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>4.607</v>
+        <v>4.55</v>
       </c>
       <c r="D3" s="15" t="inlineStr"/>
       <c r="E3" s="15" t="n">
@@ -2014,14 +2014,14 @@
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.529</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>0.497</v>
+        <v>0.5</v>
       </c>
       <c r="D4" s="15" t="inlineStr"/>
       <c r="E4" s="15" t="n">
-        <v>0.04</v>
+        <v>0.044</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>1</v>
@@ -2049,17 +2049,17 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>3.095</v>
+        <v>3.084</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="D5" s="15" t="inlineStr"/>
       <c r="E5" s="15" t="n">
-        <v>0.019</v>
+        <v>0.047</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>-0.066</v>
+        <v>-0.077</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>1</v>
@@ -2086,20 +2086,20 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>2.609</v>
+        <v>2.574</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>1.127</v>
+        <v>1.123</v>
       </c>
       <c r="D6" s="15" t="inlineStr"/>
       <c r="E6" s="15" t="n">
-        <v>0.016</v>
+        <v>-0.018</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>-0.051</v>
+        <v>-0.022</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>-0.004</v>
+        <v>-0.014</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>1</v>
@@ -2125,23 +2125,23 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>8.890000000000001</v>
+        <v>9.047000000000001</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>4.787</v>
+        <v>4.817</v>
       </c>
       <c r="D7" s="15" t="inlineStr"/>
       <c r="E7" s="15" t="n">
-        <v>0.902</v>
+        <v>0.901</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0.018</v>
+        <v>0.007</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0.01</v>
+        <v>0.039</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>0.037</v>
+        <v>0.002</v>
       </c>
       <c r="I7" s="15" t="n">
         <v>1</v>
@@ -2166,26 +2166,26 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>2.349</v>
+        <v>2.347</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>1.511</v>
+        <v>1.487</v>
       </c>
       <c r="D8" s="15" t="inlineStr"/>
       <c r="E8" s="15" t="n">
-        <v>0.199</v>
+        <v>0.175</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>-0.024</v>
+        <v>-0.004</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.004</v>
+        <v>-0.001</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-0.006</v>
+        <v>-0.004</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>0.163</v>
+        <v>0.143</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>1</v>
@@ -2209,29 +2209,29 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>3.249</v>
+        <v>3.298</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>1.076</v>
+        <v>1.082</v>
       </c>
       <c r="D9" s="15" t="inlineStr"/>
       <c r="E9" s="15" t="n">
-        <v>-0.001</v>
+        <v>-0.012</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.081</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.051</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-0.074</v>
+        <v>-0.111</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>0.008</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>-0.046</v>
+        <v>-0.081</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>1</v>
@@ -2254,34 +2254,34 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>4.009</v>
+        <v>4.075</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.572</v>
+        <v>0.604</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0.023</v>
+        <v>0.033</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.089</v>
+        <v>0.08</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-0.045</v>
+        <v>-0.099</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-0.03</v>
+        <v>-0.048</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>0.058</v>
+        <v>0.037</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>-0.002</v>
+        <v>0.012</v>
       </c>
       <c r="L10" s="15" t="n">
         <v>1</v>
@@ -2303,37 +2303,37 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>4.92</v>
+        <v>4.881</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0.637</v>
+        <v>0.616</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>0.87</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.015</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>-0.029</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.046</v>
+        <v>0.049</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-0.046</v>
+        <v>-0.028</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-0.019</v>
+        <v>0.039</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>-0.059</v>
+        <v>-0.022</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>-0.055</v>
+        <v>-0.034</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>-0.369</v>
+        <v>-0.382</v>
       </c>
       <c r="M11" s="15" t="n">
         <v>1</v>
@@ -2354,40 +2354,40 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>3.466</v>
+        <v>3.485</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.894</v>
+        <v>0.913</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>0.79</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>-0.032</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.078</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>-0.024</v>
+        <v>-0.026</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>0.064</v>
+        <v>0.076</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>0.034</v>
+        <v>0.013</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>0.043</v>
+        <v>0.049</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>-0.022</v>
+        <v>-0.057</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>0.037</v>
+        <v>0.003</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>0.038</v>
+        <v>0.073</v>
       </c>
       <c r="N12" s="15" t="n">
         <v>1</v>
@@ -2407,43 +2407,43 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>4.583</v>
+        <v>4.625</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.893</v>
+        <v>0.883</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>0.74</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>-0.095</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.062</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>-0.049</v>
+        <v>-0.03</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>0.093</v>
+        <v>0.06</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-0.079</v>
+        <v>-0.067</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>-0.079</v>
+        <v>-0.113</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>-0.098</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="L13" s="15" t="n">
-        <v>-0.029</v>
+        <v>-0.046</v>
       </c>
       <c r="M13" s="15" t="n">
-        <v>-0.076</v>
+        <v>-0.044</v>
       </c>
       <c r="N13" s="15" t="n">
-        <v>-0.008</v>
+        <v>0.001</v>
       </c>
       <c r="O13" s="15" t="n">
         <v>1</v>
@@ -2462,46 +2462,46 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>4.527</v>
+        <v>4.467</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>1.239</v>
+        <v>1.229</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>0.84</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>-0.026</v>
+        <v>0.018</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>-0.053</v>
+        <v>-0.064</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>-0.015</v>
+        <v>-0.001</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>0.04</v>
+        <v>0.042</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>0.04</v>
+        <v>0.076</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>-0.045</v>
+        <v>-0.033</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>-0.068</v>
+        <v>-0.043</v>
       </c>
       <c r="L14" s="15" t="n">
-        <v>-0.359</v>
+        <v>-0.37</v>
       </c>
       <c r="M14" s="15" t="n">
-        <v>0.371</v>
+        <v>0.339</v>
       </c>
       <c r="N14" s="15" t="n">
-        <v>0.004</v>
+        <v>0.015</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>-0.024</v>
+        <v>-0.012</v>
       </c>
       <c r="P14" s="15" t="n">
         <v>1</v>
@@ -2519,49 +2519,49 @@
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>3.024</v>
+        <v>3.078</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>1.157</v>
+        <v>1.189</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.021</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0.043</v>
+        <v>0.039</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>-0.004</v>
+        <v>-0.006</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-0.033</v>
+        <v>-0.063</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-0.039</v>
+        <v>-0.035</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>-0.012</v>
+        <v>0.01</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>0.033</v>
+        <v>0.026</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>0.306</v>
+        <v>0.323</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.352</v>
+        <v>-0.341</v>
       </c>
       <c r="N15" s="15" t="n">
-        <v>0.033</v>
+        <v>0.027</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.095</v>
       </c>
       <c r="P15" s="15" t="n">
-        <v>-0.46</v>
+        <v>-0.446</v>
       </c>
       <c r="Q15" s="15" t="n">
         <v>1</v>
@@ -2578,52 +2578,52 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>4.389</v>
+        <v>4.38</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>0.621</v>
+        <v>0.626</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>0.044</v>
+        <v>-0.021</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>0.019</v>
+        <v>0.012</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>-0.042</v>
+        <v>-0.049</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>0.058</v>
+        <v>0.049</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>0.043</v>
+        <v>-0.036</v>
       </c>
       <c r="J16" s="15" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K16" s="15" t="n">
+        <v>-0.036</v>
+      </c>
+      <c r="L16" s="15" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="M16" s="15" t="n">
+        <v>-0.075</v>
+      </c>
+      <c r="N16" s="15" t="n">
+        <v>-0.166</v>
+      </c>
+      <c r="O16" s="15" t="n">
+        <v>-0.032</v>
+      </c>
+      <c r="P16" s="15" t="n">
         <v>-0.021</v>
       </c>
-      <c r="K16" s="15" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="L16" s="15" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="M16" s="15" t="n">
-        <v>-0.024</v>
-      </c>
-      <c r="N16" s="15" t="n">
-        <v>-0.102</v>
-      </c>
-      <c r="O16" s="15" t="n">
-        <v>-0.028</v>
-      </c>
-      <c r="P16" s="15" t="n">
-        <v>-0.004</v>
-      </c>
       <c r="Q16" s="15" t="n">
-        <v>0.045</v>
+        <v>0.068</v>
       </c>
       <c r="R16" s="15" t="n">
         <v>1</v>
@@ -2639,55 +2639,55 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>4.51</v>
+        <v>4.515</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>0.805</v>
+        <v>0.778</v>
       </c>
       <c r="D17" s="15" t="n">
         <v>0.85</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>-0.021</v>
+        <v>-0.025</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.01</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>-0.023</v>
+        <v>-0.019</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>0.027</v>
+        <v>0.078</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>0.025</v>
+        <v>-0.001</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>-0.026</v>
+        <v>0.019</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>-0.043</v>
+        <v>-0.031</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>-0.237</v>
+        <v>-0.222</v>
       </c>
       <c r="M17" s="15" t="n">
-        <v>0.311</v>
+        <v>0.269</v>
       </c>
       <c r="N17" s="15" t="n">
-        <v>-0.041</v>
+        <v>-0.127</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="P17" s="15" t="n">
-        <v>0.571</v>
+        <v>0.596</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>-0.595</v>
+        <v>-0.598</v>
       </c>
       <c r="R17" s="15" t="n">
-        <v>0.43</v>
+        <v>0.367</v>
       </c>
       <c r="S17" s="15" t="n">
         <v>1</v>
@@ -2705,55 +2705,55 @@
         <v>4.698</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>1.193</v>
+        <v>1.273</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.029</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>-0.025</v>
+        <v>0.006</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>0</v>
+        <v>-0.081</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-0.026</v>
+        <v>0.022</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-0.046</v>
+        <v>0.004</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>-0.023</v>
+        <v>0.021</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>0.001</v>
+        <v>-0.007</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>-0.3</v>
+        <v>-0.362</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>0.535</v>
+        <v>0.439</v>
       </c>
       <c r="N18" s="15" t="n">
-        <v>-0.092</v>
+        <v>0.014</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>-0.091</v>
+        <v>-0.113</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0.376</v>
+        <v>0.442</v>
       </c>
       <c r="Q18" s="15" t="n">
-        <v>-0.345</v>
+        <v>-0.319</v>
       </c>
       <c r="R18" s="15" t="n">
-        <v>0.021</v>
+        <v>-0.039</v>
       </c>
       <c r="S18" s="15" t="n">
-        <v>0.266</v>
+        <v>0.339</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>1</v>
@@ -2767,61 +2767,61 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>2.672</v>
+        <v>2.608</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>1.045</v>
+        <v>1.051</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>0.78</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>0.03</v>
+        <v>0.017</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>0.054</v>
+        <v>0.041</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>0.015</v>
+        <v>-0.007</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-0.019</v>
+        <v>-0.018</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-0.008</v>
+        <v>-0.016</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>0.042</v>
+        <v>-0.05</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>0.54</v>
+        <v>0.404</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>-0.4</v>
+        <v>-0.327</v>
       </c>
       <c r="N19" s="15" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.051</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>-0.052</v>
+        <v>-0.054</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>-0.365</v>
+        <v>-0.299</v>
       </c>
       <c r="Q19" s="15" t="n">
-        <v>0.316</v>
+        <v>0.273</v>
       </c>
       <c r="R19" s="15" t="n">
-        <v>0.089</v>
+        <v>-0.024</v>
       </c>
       <c r="S19" s="15" t="n">
-        <v>-0.251</v>
+        <v>-0.189</v>
       </c>
       <c r="T19" s="15" t="n">
-        <v>-0.419</v>
+        <v>-0.364</v>
       </c>
       <c r="U19" s="15" t="n">
         <v>1</v>

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>30.832</v>
+        <v>30.781</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>4.55</v>
+        <v>4.593</v>
       </c>
       <c r="D3" s="15" t="inlineStr"/>
       <c r="E3" s="15" t="n">
@@ -2014,14 +2014,14 @@
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>0.529</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>0.5</v>
+        <v>0.497</v>
       </c>
       <c r="D4" s="15" t="inlineStr"/>
       <c r="E4" s="15" t="n">
-        <v>0.044</v>
+        <v>0.017</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>1</v>
@@ -2049,17 +2049,17 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>3.084</v>
+        <v>3.118</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.913</v>
       </c>
       <c r="D5" s="15" t="inlineStr"/>
       <c r="E5" s="15" t="n">
-        <v>0.047</v>
+        <v>0.04</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>-0.077</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>1</v>
@@ -2086,20 +2086,20 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>2.574</v>
+        <v>2.584</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>1.123</v>
+        <v>1.119</v>
       </c>
       <c r="D6" s="15" t="inlineStr"/>
       <c r="E6" s="15" t="n">
-        <v>-0.018</v>
+        <v>-0.017</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>-0.022</v>
+        <v>-0.011</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>-0.014</v>
+        <v>-0.057</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>1</v>
@@ -2125,23 +2125,23 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>9.047000000000001</v>
+        <v>8.997</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>4.817</v>
+        <v>4.82</v>
       </c>
       <c r="D7" s="15" t="inlineStr"/>
       <c r="E7" s="15" t="n">
-        <v>0.901</v>
+        <v>0.905</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0.039</v>
+        <v>0.038</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>0.002</v>
+        <v>0.017</v>
       </c>
       <c r="I7" s="15" t="n">
         <v>1</v>
@@ -2166,26 +2166,26 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>2.347</v>
+        <v>2.359</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>1.487</v>
+        <v>1.476</v>
       </c>
       <c r="D8" s="15" t="inlineStr"/>
       <c r="E8" s="15" t="n">
-        <v>0.175</v>
+        <v>0.178</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>-0.004</v>
+        <v>-0.027</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>-0.001</v>
+        <v>-0.011</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-0.004</v>
+        <v>0.016</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>0.143</v>
+        <v>0.151</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>1</v>
@@ -2209,29 +2209,29 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>3.298</v>
+        <v>3.296</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>1.082</v>
+        <v>1.071</v>
       </c>
       <c r="D9" s="15" t="inlineStr"/>
       <c r="E9" s="15" t="n">
-        <v>-0.012</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.081</v>
+        <v>0.101</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>-0.051</v>
+        <v>-0.06</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-0.111</v>
+        <v>-0.102</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>-0.081</v>
+        <v>-0.079</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>1</v>
@@ -2254,34 +2254,34 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>4.075</v>
+        <v>4.083</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.604</v>
+        <v>0.598</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>0.005</v>
+        <v>0.033</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0.033</v>
+        <v>-0.01</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.08</v>
+        <v>0.064</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-0.099</v>
+        <v>-0.091</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-0.048</v>
+        <v>-0.014</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>0.037</v>
+        <v>0.04</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>0.012</v>
+        <v>0.052</v>
       </c>
       <c r="L10" s="15" t="n">
         <v>1</v>
@@ -2303,37 +2303,37 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>4.881</v>
+        <v>4.898</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0.616</v>
+        <v>0.651</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>0.87</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>-0.015</v>
+        <v>-0.057</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>-0.029</v>
+        <v>-0.006</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.049</v>
+        <v>0.056</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-0.028</v>
+        <v>-0.05</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>0.039</v>
+        <v>-0.005</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>-0.022</v>
+        <v>-0.044</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>-0.034</v>
+        <v>-0.055</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>-0.382</v>
+        <v>-0.393</v>
       </c>
       <c r="M11" s="15" t="n">
         <v>1</v>
@@ -2354,40 +2354,40 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>3.485</v>
+        <v>3.479</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.913</v>
+        <v>0.885</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>0.79</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.032</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>-0.078</v>
+        <v>-0.05</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>-0.026</v>
+        <v>-0.04</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>0.076</v>
+        <v>0.02</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>0.013</v>
+        <v>0.039</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>0.049</v>
+        <v>0.06</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>-0.057</v>
+        <v>-0.066</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>0.003</v>
+        <v>0.044</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>0.073</v>
+        <v>0.053</v>
       </c>
       <c r="N12" s="15" t="n">
         <v>1</v>
@@ -2407,43 +2407,43 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>4.625</v>
+        <v>4.599</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.883</v>
+        <v>0.893</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>0.74</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.061</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>-0.062</v>
+        <v>-0.092</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>-0.03</v>
+        <v>-0.029</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>0.06</v>
+        <v>0.054</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-0.067</v>
+        <v>-0.042</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>-0.113</v>
+        <v>-0.08</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.076</v>
       </c>
       <c r="L13" s="15" t="n">
-        <v>-0.046</v>
+        <v>-0.016</v>
       </c>
       <c r="M13" s="15" t="n">
-        <v>-0.044</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="N13" s="15" t="n">
-        <v>0.001</v>
+        <v>-0.024</v>
       </c>
       <c r="O13" s="15" t="n">
         <v>1</v>
@@ -2462,46 +2462,46 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>4.467</v>
+        <v>4.46</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>1.229</v>
+        <v>1.236</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>0.84</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>0.018</v>
+        <v>0.029</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>-0.064</v>
+        <v>-0.042</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>-0.001</v>
+        <v>0.008</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>0.042</v>
+        <v>0.074</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>0.076</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>-0.033</v>
+        <v>0.007</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>-0.043</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="L14" s="15" t="n">
-        <v>-0.37</v>
+        <v>-0.382</v>
       </c>
       <c r="M14" s="15" t="n">
-        <v>0.339</v>
+        <v>0.374</v>
       </c>
       <c r="N14" s="15" t="n">
-        <v>0.015</v>
+        <v>0.001</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>-0.012</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="P14" s="15" t="n">
         <v>1</v>
@@ -2519,49 +2519,49 @@
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>3.078</v>
+        <v>3.095</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>1.189</v>
+        <v>1.208</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>0.021</v>
+        <v>0.004</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0.039</v>
+        <v>0.002</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>-0.006</v>
+        <v>-0.026</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-0.063</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-0.035</v>
+        <v>-0.047</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>0.01</v>
+        <v>-0.067</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>0.026</v>
+        <v>0.04</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>0.323</v>
+        <v>0.326</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.341</v>
+        <v>-0.345</v>
       </c>
       <c r="N15" s="15" t="n">
-        <v>0.027</v>
+        <v>0.042</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.095</v>
+        <v>-0.076</v>
       </c>
       <c r="P15" s="15" t="n">
-        <v>-0.446</v>
+        <v>-0.431</v>
       </c>
       <c r="Q15" s="15" t="n">
         <v>1</v>
@@ -2578,52 +2578,52 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>4.38</v>
+        <v>4.399</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>0.626</v>
+        <v>0.644</v>
       </c>
       <c r="D16" s="15" t="n">
         <v>0.82</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>-0.021</v>
+        <v>-0.019</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>-0.049</v>
+        <v>-0.062</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>0.049</v>
+        <v>0.031</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-0.036</v>
+        <v>-0.035</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>0.015</v>
+        <v>-0.026</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>-0.036</v>
+        <v>-0.025</v>
       </c>
       <c r="L16" s="15" t="n">
-        <v>0.081</v>
+        <v>0.116</v>
       </c>
       <c r="M16" s="15" t="n">
-        <v>-0.075</v>
+        <v>-0.081</v>
       </c>
       <c r="N16" s="15" t="n">
-        <v>-0.166</v>
+        <v>-0.135</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>-0.032</v>
+        <v>-0.076</v>
       </c>
       <c r="P16" s="15" t="n">
-        <v>-0.021</v>
+        <v>0.003</v>
       </c>
       <c r="Q16" s="15" t="n">
-        <v>0.068</v>
+        <v>0.08</v>
       </c>
       <c r="R16" s="15" t="n">
         <v>1</v>
@@ -2639,55 +2639,55 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>4.515</v>
+        <v>4.498</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>0.778</v>
+        <v>0.766</v>
       </c>
       <c r="D17" s="15" t="n">
         <v>0.85</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>-0.025</v>
+        <v>0.005</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>-0.01</v>
+        <v>-0.026</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>-0.019</v>
+        <v>0.019</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>0.078</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-0.001</v>
+        <v>0.043</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>0.019</v>
+        <v>0.04</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>-0.031</v>
+        <v>-0.068</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>-0.222</v>
+        <v>-0.252</v>
       </c>
       <c r="M17" s="15" t="n">
-        <v>0.269</v>
+        <v>0.289</v>
       </c>
       <c r="N17" s="15" t="n">
-        <v>-0.127</v>
+        <v>-0.041</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>0.002</v>
+        <v>0.011</v>
       </c>
       <c r="P17" s="15" t="n">
-        <v>0.596</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>-0.598</v>
+        <v>-0.602</v>
       </c>
       <c r="R17" s="15" t="n">
-        <v>0.367</v>
+        <v>0.398</v>
       </c>
       <c r="S17" s="15" t="n">
         <v>1</v>
@@ -2702,58 +2702,58 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>4.698</v>
+        <v>4.754</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>1.273</v>
+        <v>1.192</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>-0.029</v>
+        <v>-0.028</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>0.006</v>
+        <v>0.013</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>-0.081</v>
+        <v>-0.091</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>0.022</v>
+        <v>0.011</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>0.021</v>
+        <v>-0.04</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>-0.007</v>
+        <v>0.055</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>-0.362</v>
+        <v>-0.412</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>0.439</v>
+        <v>0.441</v>
       </c>
       <c r="N18" s="15" t="n">
         <v>0.014</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>-0.113</v>
+        <v>-0.037</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0.442</v>
+        <v>0.396</v>
       </c>
       <c r="Q18" s="15" t="n">
         <v>-0.319</v>
       </c>
       <c r="R18" s="15" t="n">
-        <v>-0.039</v>
+        <v>-0.074</v>
       </c>
       <c r="S18" s="15" t="n">
-        <v>0.339</v>
+        <v>0.283</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>1</v>
@@ -2767,61 +2767,61 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>2.608</v>
+        <v>2.561</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>1.051</v>
+        <v>0.995</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>0.78</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>0.017</v>
+        <v>0.003</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>0.041</v>
+        <v>0.065</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>-0.007</v>
+        <v>0.056</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-0.018</v>
+        <v>-0.044</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-0.016</v>
+        <v>-0.006</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>-0.05</v>
+        <v>-0.114</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>0.02</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>0.404</v>
+        <v>0.431</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>-0.327</v>
+        <v>-0.481</v>
       </c>
       <c r="N19" s="15" t="n">
-        <v>0.051</v>
+        <v>-0.024</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>-0.054</v>
+        <v>-0.02</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>-0.299</v>
+        <v>-0.359</v>
       </c>
       <c r="Q19" s="15" t="n">
-        <v>0.273</v>
+        <v>0.326</v>
       </c>
       <c r="R19" s="15" t="n">
-        <v>-0.024</v>
+        <v>0.06</v>
       </c>
       <c r="S19" s="15" t="n">
-        <v>-0.189</v>
+        <v>-0.265</v>
       </c>
       <c r="T19" s="15" t="n">
-        <v>-0.364</v>
+        <v>-0.457</v>
       </c>
       <c r="U19" s="15" t="n">
         <v>1</v>

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>30.781</v>
+        <v>30.794</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>4.593</v>
+        <v>4.649</v>
       </c>
       <c r="D3" s="15" t="inlineStr"/>
       <c r="E3" s="15" t="n">
@@ -2014,14 +2014,14 @@
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="C4" s="15" t="n">
         <v>0.497</v>
       </c>
       <c r="D4" s="15" t="inlineStr"/>
       <c r="E4" s="15" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>1</v>
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>3.118</v>
+        <v>3.119</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>0.913</v>
+        <v>0.903</v>
       </c>
       <c r="D5" s="15" t="inlineStr"/>
       <c r="E5" s="15" t="n">
@@ -2086,20 +2086,20 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>2.584</v>
+        <v>2.57</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>1.119</v>
+        <v>1.129</v>
       </c>
       <c r="D6" s="15" t="inlineStr"/>
       <c r="E6" s="15" t="n">
-        <v>-0.017</v>
+        <v>-0.015</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>-0.011</v>
+        <v>-0.004</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>-0.057</v>
+        <v>-0.076</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>1</v>
@@ -2125,23 +2125,23 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>8.997</v>
+        <v>9.018000000000001</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>4.82</v>
+        <v>4.857</v>
       </c>
       <c r="D7" s="15" t="inlineStr"/>
       <c r="E7" s="15" t="n">
         <v>0.905</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0.038</v>
+        <v>0.048</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>0.017</v>
+        <v>0.024</v>
       </c>
       <c r="I7" s="15" t="n">
         <v>1</v>
@@ -2166,26 +2166,26 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>2.359</v>
+        <v>2.374</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>1.476</v>
+        <v>1.486</v>
       </c>
       <c r="D8" s="15" t="inlineStr"/>
       <c r="E8" s="15" t="n">
-        <v>0.178</v>
+        <v>0.18</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>-0.027</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>-0.011</v>
+        <v>-0.001</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>0.016</v>
+        <v>0.027</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>0.151</v>
+        <v>0.149</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>1</v>
@@ -2209,29 +2209,29 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>3.296</v>
+        <v>3.291</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>1.071</v>
+        <v>1.078</v>
       </c>
       <c r="D9" s="15" t="inlineStr"/>
       <c r="E9" s="15" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.01</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.101</v>
+        <v>0.09</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>-0.06</v>
+        <v>-0.056</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-0.102</v>
+        <v>-0.1</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>0.007</v>
+        <v>0.01</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>-0.079</v>
+        <v>-0.055</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>1</v>
@@ -2254,34 +2254,34 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>4.083</v>
+        <v>4.068</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.598</v>
+        <v>0.605</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>0.033</v>
+        <v>0.012</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>-0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.064</v>
+        <v>0.065</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-0.091</v>
+        <v>-0.107</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-0.014</v>
+        <v>-0.034</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>0.04</v>
+        <v>0.044</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>0.052</v>
+        <v>0.066</v>
       </c>
       <c r="L10" s="15" t="n">
         <v>1</v>
@@ -2303,37 +2303,37 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>4.898</v>
+        <v>4.918</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0.651</v>
+        <v>0.648</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>0.87</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>-0.057</v>
+        <v>-0.054</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>-0.006</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.056</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H11" s="15" t="n">
+        <v>-0.041</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>-0.061</v>
+      </c>
+      <c r="K11" s="15" t="n">
         <v>-0.05</v>
       </c>
-      <c r="I11" s="15" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="J11" s="15" t="n">
-        <v>-0.044</v>
-      </c>
-      <c r="K11" s="15" t="n">
-        <v>-0.055</v>
-      </c>
       <c r="L11" s="15" t="n">
-        <v>-0.393</v>
+        <v>-0.376</v>
       </c>
       <c r="M11" s="15" t="n">
         <v>1</v>
@@ -2354,40 +2354,40 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>3.479</v>
+        <v>3.477</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>0.885</v>
+        <v>0.886</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>0.79</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>-0.032</v>
+        <v>-0.037</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>-0.05</v>
+        <v>-0.066</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>-0.04</v>
+        <v>-0.021</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>-0.066</v>
+        <v>-0.063</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>0.044</v>
+        <v>0.062</v>
       </c>
       <c r="M12" s="15" t="n">
-        <v>0.053</v>
+        <v>0.029</v>
       </c>
       <c r="N12" s="15" t="n">
         <v>1</v>
@@ -2407,43 +2407,43 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>4.599</v>
+        <v>4.609</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>0.893</v>
+        <v>0.889</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>0.74</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>-0.061</v>
+        <v>-0.048</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>-0.092</v>
+        <v>-0.096</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>-0.029</v>
+        <v>-0.021</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>0.054</v>
+        <v>0.04</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-0.042</v>
+        <v>-0.024</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>-0.08</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>-0.076</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="L13" s="15" t="n">
-        <v>-0.016</v>
+        <v>-0.005</v>
       </c>
       <c r="M13" s="15" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.1</v>
       </c>
       <c r="N13" s="15" t="n">
-        <v>-0.024</v>
+        <v>-0.023</v>
       </c>
       <c r="O13" s="15" t="n">
         <v>1</v>
@@ -2462,46 +2462,46 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>4.46</v>
+        <v>4.439</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>1.236</v>
+        <v>1.259</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>0.84</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>0.029</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>-0.042</v>
+        <v>0.004</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0.008</v>
+        <v>0.034</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>0.074</v>
+        <v>0.015</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>0.007</v>
+        <v>0.015</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.031</v>
       </c>
       <c r="L14" s="15" t="n">
-        <v>-0.382</v>
+        <v>-0.31</v>
       </c>
       <c r="M14" s="15" t="n">
-        <v>0.374</v>
+        <v>0.366</v>
       </c>
       <c r="N14" s="15" t="n">
-        <v>0.001</v>
+        <v>-0.022</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.058</v>
       </c>
       <c r="P14" s="15" t="n">
         <v>1</v>
@@ -2519,49 +2519,49 @@
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>3.095</v>
+        <v>3.137</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>1.208</v>
+        <v>1.201</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>0.004</v>
+        <v>-0.008</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0.002</v>
+        <v>-0.076</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>-0.026</v>
+        <v>0.06</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.016</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-0.047</v>
+        <v>-0.029</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>-0.067</v>
+        <v>0.056</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>0.04</v>
+        <v>0.028</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>0.326</v>
+        <v>0.393</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.345</v>
+        <v>-0.311</v>
       </c>
       <c r="N15" s="15" t="n">
-        <v>0.042</v>
+        <v>0.038</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.076</v>
+        <v>0.051</v>
       </c>
       <c r="P15" s="15" t="n">
-        <v>-0.431</v>
+        <v>-0.427</v>
       </c>
       <c r="Q15" s="15" t="n">
         <v>1</v>
@@ -2578,52 +2578,52 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>4.399</v>
+        <v>4.398</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>0.644</v>
+        <v>0.65</v>
       </c>
       <c r="D16" s="15" t="n">
         <v>0.82</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>-0.019</v>
+        <v>-0.011</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>0.015</v>
+        <v>0.048</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>-0.062</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>0.031</v>
+        <v>0.027</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-0.035</v>
+        <v>-0.031</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>-0.026</v>
+        <v>-0.015</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>-0.025</v>
+        <v>-0.017</v>
       </c>
       <c r="L16" s="15" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="M16" s="15" t="n">
+        <v>-0.07199999999999999</v>
+      </c>
+      <c r="N16" s="15" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="O16" s="15" t="n">
+        <v>-0.08799999999999999</v>
+      </c>
+      <c r="P16" s="15" t="n">
         <v>0.116</v>
       </c>
-      <c r="M16" s="15" t="n">
-        <v>-0.081</v>
-      </c>
-      <c r="N16" s="15" t="n">
-        <v>-0.135</v>
-      </c>
-      <c r="O16" s="15" t="n">
-        <v>-0.076</v>
-      </c>
-      <c r="P16" s="15" t="n">
-        <v>0.003</v>
-      </c>
       <c r="Q16" s="15" t="n">
-        <v>0.08</v>
+        <v>-0.074</v>
       </c>
       <c r="R16" s="15" t="n">
         <v>1</v>
@@ -2639,55 +2639,55 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>4.498</v>
+        <v>4.49</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>0.766</v>
+        <v>0.781</v>
       </c>
       <c r="D17" s="15" t="n">
         <v>0.85</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>0.005</v>
+        <v>-0.056</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>-0.026</v>
+        <v>0.024</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>0.019</v>
+        <v>-0.129</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.075</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>0.043</v>
+        <v>-0.042</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>-0.068</v>
+        <v>-0.022</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>-0.252</v>
+        <v>-0.158</v>
       </c>
       <c r="M17" s="15" t="n">
-        <v>0.289</v>
+        <v>0.213</v>
       </c>
       <c r="N17" s="15" t="n">
-        <v>-0.041</v>
+        <v>-0.056</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>0.011</v>
+        <v>-0.038</v>
       </c>
       <c r="P17" s="15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.482</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>-0.602</v>
+        <v>-0.407</v>
       </c>
       <c r="R17" s="15" t="n">
-        <v>0.398</v>
+        <v>0.389</v>
       </c>
       <c r="S17" s="15" t="n">
         <v>1</v>
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>4.754</v>
+        <v>4.628</v>
       </c>
       <c r="C18" s="15" t="n">
         <v>1.192</v>
@@ -2711,37 +2711,37 @@
         <v>0.86</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>-0.028</v>
+        <v>0.079</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>0.013</v>
+        <v>0.046</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>-0.091</v>
+        <v>0.003</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>0.011</v>
+        <v>-0.02</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>0.007</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>-0.04</v>
+        <v>0.115</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>0.055</v>
+        <v>-0.007</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>-0.412</v>
+        <v>-0.192</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>0.441</v>
+        <v>0.113</v>
       </c>
       <c r="N18" s="15" t="n">
-        <v>0.014</v>
+        <v>-0.066</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>-0.037</v>
+        <v>-0.018</v>
       </c>
       <c r="P18" s="15" t="n">
         <v>0.396</v>
@@ -2750,10 +2750,10 @@
         <v>-0.319</v>
       </c>
       <c r="R18" s="15" t="n">
-        <v>-0.074</v>
+        <v>0.03</v>
       </c>
       <c r="S18" s="15" t="n">
-        <v>0.283</v>
+        <v>0.284</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>1</v>
@@ -2767,61 +2767,61 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>2.561</v>
+        <v>2.652</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>0.995</v>
+        <v>0.993</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>0.78</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>0.003</v>
+        <v>-0.057</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>0.065</v>
+        <v>-0.019</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>0.056</v>
+        <v>-0.037</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-0.044</v>
+        <v>0.078</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-0.006</v>
+        <v>-0.03</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>-0.114</v>
+        <v>-0.047</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>0.06900000000000001</v>
+        <v>-0.025</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>0.431</v>
+        <v>0.195</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>-0.481</v>
+        <v>-0.119</v>
       </c>
       <c r="N19" s="15" t="n">
-        <v>-0.024</v>
+        <v>0.107</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>-0.02</v>
+        <v>0.019</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>-0.359</v>
+        <v>-0.357</v>
       </c>
       <c r="Q19" s="15" t="n">
-        <v>0.326</v>
+        <v>0.331</v>
       </c>
       <c r="R19" s="15" t="n">
-        <v>0.06</v>
+        <v>-0.066</v>
       </c>
       <c r="S19" s="15" t="n">
-        <v>-0.265</v>
+        <v>-0.267</v>
       </c>
       <c r="T19" s="15" t="n">
-        <v>-0.457</v>
+        <v>-0.361</v>
       </c>
       <c r="U19" s="15" t="n">
         <v>1</v>
@@ -2907,14 +2907,14 @@
         </is>
       </c>
       <c r="C4" s="15" t="n">
-        <v>-0.142</v>
+        <v>-0.496</v>
       </c>
       <c r="D4" s="15" t="n">
-        <v>0.052</v>
+        <v>0.064</v>
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>[-0.244, -0.040]</t>
+          <t>[-0.621, -0.370]</t>
         </is>
       </c>
       <c r="F4" s="15" t="inlineStr">
@@ -2935,14 +2935,14 @@
         </is>
       </c>
       <c r="C5" s="15" t="n">
-        <v>0.267</v>
+        <v>0.523</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>0.049</v>
+        <v>0.059</v>
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>[0.171, 0.363]</t>
+          <t>[0.407, 0.640]</t>
         </is>
       </c>
       <c r="F5" s="15" t="inlineStr">
@@ -2963,14 +2963,14 @@
         </is>
       </c>
       <c r="C6" s="15" t="n">
-        <v>0.312</v>
+        <v>0.571</v>
       </c>
       <c r="D6" s="15" t="n">
-        <v>0.058</v>
+        <v>0.061</v>
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>[0.198, 0.426]</t>
+          <t>[0.451, 0.690]</t>
         </is>
       </c>
       <c r="F6" s="15" t="inlineStr">
@@ -2991,14 +2991,14 @@
         </is>
       </c>
       <c r="C7" s="15" t="n">
-        <v>-0.145</v>
+        <v>-0.402</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>0.052</v>
+        <v>0.057</v>
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>[-0.247, -0.043]</t>
+          <t>[-0.513, -0.291]</t>
         </is>
       </c>
       <c r="F7" s="15" t="inlineStr">
@@ -3031,14 +3031,14 @@
         </is>
       </c>
       <c r="C9" s="15" t="n">
-        <v>0.234</v>
+        <v>0.199</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>0.046</v>
+        <v>0.034</v>
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>[0.144, 0.324]</t>
+          <t>[0.132, 0.266]</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
@@ -3059,14 +3059,14 @@
         </is>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.203</v>
+        <v>0.284</v>
       </c>
       <c r="D10" s="15" t="n">
-        <v>0.048</v>
+        <v>0.052</v>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>[0.109, 0.297]</t>
+          <t>[0.182, 0.386]</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
@@ -3087,14 +3087,14 @@
         </is>
       </c>
       <c r="C11" s="15" t="n">
-        <v>-0.112</v>
+        <v>-0.212</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>0.044</v>
+        <v>0.046</v>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>[-0.198, -0.026]</t>
+          <t>[-0.303, -0.121]</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
@@ -3115,14 +3115,14 @@
         </is>
       </c>
       <c r="C12" s="15" t="n">
-        <v>-0.198</v>
+        <v>-0.137</v>
       </c>
       <c r="D12" s="15" t="n">
-        <v>0.051</v>
+        <v>0.035</v>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>[-0.298, -0.098]</t>
+          <t>[-0.206, -0.068]</t>
         </is>
       </c>
       <c r="F12" s="15" t="inlineStr">
@@ -3143,14 +3143,14 @@
         </is>
       </c>
       <c r="C13" s="15" t="n">
-        <v>-0.156</v>
+        <v>-0.17</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>0.053</v>
+        <v>0.055</v>
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>[-0.260, -0.052]</t>
+          <t>[-0.278, -0.063]</t>
         </is>
       </c>
       <c r="F13" s="15" t="inlineStr">
@@ -3171,14 +3171,14 @@
         </is>
       </c>
       <c r="C14" s="15" t="n">
-        <v>0.278</v>
+        <v>0.184</v>
       </c>
       <c r="D14" s="15" t="n">
-        <v>0.055</v>
+        <v>0.049</v>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>[0.170, 0.386]</t>
+          <t>[0.088, 0.279]</t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
@@ -3211,14 +3211,14 @@
         </is>
       </c>
       <c r="C16" s="15" t="n">
-        <v>-0.082</v>
+        <v>-0.011</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>0.041</v>
+        <v>0.047</v>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>[-0.162, -0.002]</t>
+          <t>[-0.104, 0.081]</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
@@ -3239,14 +3239,14 @@
         </is>
       </c>
       <c r="C17" s="15" t="n">
-        <v>0.118</v>
+        <v>0.051</v>
       </c>
       <c r="D17" s="15" t="n">
         <v>0.043</v>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>[0.034, 0.202]</t>
+          <t>[-0.033, 0.136]</t>
         </is>
       </c>
       <c r="F17" s="15" t="inlineStr">
@@ -3267,14 +3267,14 @@
         </is>
       </c>
       <c r="C18" s="15" t="n">
-        <v>-0.067</v>
+        <v>-0.066</v>
       </c>
       <c r="D18" s="15" t="n">
-        <v>0.04</v>
+        <v>0.078</v>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>[-0.145, 0.011]</t>
+          <t>[-0.220, 0.087]</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
@@ -3295,14 +3295,14 @@
         </is>
       </c>
       <c r="C19" s="15" t="n">
-        <v>0.094</v>
+        <v>-0.028</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>0.041</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>[0.014, 0.174]</t>
+          <t>[-0.168, 0.113]</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
@@ -3323,14 +3323,14 @@
         </is>
       </c>
       <c r="C20" s="15" t="n">
-        <v>0.103</v>
+        <v>0.002</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>0.044</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>[0.017, 0.189]</t>
+          <t>[-0.133, 0.136]</t>
         </is>
       </c>
       <c r="F20" s="15" t="inlineStr">
@@ -3351,14 +3351,14 @@
         </is>
       </c>
       <c r="C21" s="15" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.02</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>0.04</v>
+        <v>0.063</v>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>[-0.149, 0.007]</t>
+          <t>[-0.103, 0.143]</t>
         </is>
       </c>
       <c r="F21" s="15" t="inlineStr">
@@ -3394,11 +3394,11 @@
         <v>0.412</v>
       </c>
       <c r="D23" s="15" t="n">
-        <v>0.058</v>
+        <v>0.053</v>
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>[0.298, 0.526]</t>
+          <t>[0.308, 0.516]</t>
         </is>
       </c>
       <c r="F23" s="15" t="inlineStr">
@@ -3419,14 +3419,14 @@
         </is>
       </c>
       <c r="C24" s="15" t="n">
-        <v>-0.118</v>
+        <v>-0.052</v>
       </c>
       <c r="D24" s="15" t="n">
-        <v>0.046</v>
+        <v>0.061</v>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>[-0.208, -0.028]</t>
+          <t>[-0.171, 0.067]</t>
         </is>
       </c>
       <c r="F24" s="15" t="inlineStr">
@@ -3447,14 +3447,14 @@
         </is>
       </c>
       <c r="C25" s="15" t="n">
-        <v>0.214</v>
+        <v>0.056</v>
       </c>
       <c r="D25" s="15" t="n">
-        <v>0.047</v>
+        <v>0.058</v>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>[0.122, 0.306]</t>
+          <t>[-0.057, 0.170]</t>
         </is>
       </c>
       <c r="F25" s="15" t="inlineStr">

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -2086,20 +2086,20 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>2.57</v>
+        <v>2.641</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>1.129</v>
+        <v>0.78</v>
       </c>
       <c r="D6" s="15" t="inlineStr"/>
       <c r="E6" s="15" t="n">
-        <v>-0.015</v>
+        <v>-0.065</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>-0.004</v>
+        <v>0.012</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>-0.076</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>1</v>
@@ -2141,7 +2141,7 @@
         <v>0.048</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>0.024</v>
+        <v>-0.012</v>
       </c>
       <c r="I7" s="15" t="n">
         <v>1</v>
@@ -2182,7 +2182,7 @@
         <v>-0.001</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>0.027</v>
+        <v>-0.001</v>
       </c>
       <c r="I8" s="15" t="n">
         <v>0.149</v>
@@ -2225,7 +2225,7 @@
         <v>-0.056</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="I9" s="15" t="n">
         <v>0.01</v>
@@ -2272,7 +2272,7 @@
         <v>0.065</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-0.107</v>
+        <v>-0.125</v>
       </c>
       <c r="I10" s="15" t="n">
         <v>-0.034</v>
@@ -2372,7 +2372,7 @@
         <v>-0.021</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>0.03</v>
+        <v>0.051</v>
       </c>
       <c r="I12" s="15" t="n">
         <v>0.03</v>
@@ -2425,7 +2425,7 @@
         <v>-0.021</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="I13" s="15" t="n">
         <v>-0.024</v>
@@ -2480,7 +2480,7 @@
         <v>0.034</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>0.015</v>
+        <v>0.004</v>
       </c>
       <c r="I14" s="15" t="n">
         <v>0.08599999999999999</v>
@@ -2537,7 +2537,7 @@
         <v>0.06</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>0.016</v>
+        <v>-0.006</v>
       </c>
       <c r="I15" s="15" t="n">
         <v>-0.029</v>
@@ -2596,7 +2596,7 @@
         <v>-0.07199999999999999</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="I16" s="15" t="n">
         <v>-0.031</v>
@@ -2657,7 +2657,7 @@
         <v>-0.129</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>0.075</v>
+        <v>0.095</v>
       </c>
       <c r="I17" s="15" t="n">
         <v>-0.042</v>
@@ -2720,7 +2720,7 @@
         <v>0.003</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-0.02</v>
+        <v>-0.027</v>
       </c>
       <c r="I18" s="15" t="n">
         <v>0.06900000000000001</v>
@@ -2785,7 +2785,7 @@
         <v>-0.037</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>0.078</v>
+        <v>0.117</v>
       </c>
       <c r="I19" s="15" t="n">
         <v>-0.03</v>

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -2519,49 +2519,49 @@
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>3.137</v>
+        <v>3.156</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>1.201</v>
+        <v>1.172</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>-0.008</v>
+        <v>0.034</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>-0.076</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0.06</v>
+        <v>0.068</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-0.006</v>
+        <v>-0.039</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-0.029</v>
+        <v>0.007</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>0.056</v>
+        <v>0.082</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>0.028</v>
+        <v>0.05</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>0.393</v>
+        <v>0.405</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.311</v>
+        <v>-0.31</v>
       </c>
       <c r="N15" s="15" t="n">
-        <v>0.038</v>
+        <v>-0.005</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>0.051</v>
+        <v>-0.001</v>
       </c>
       <c r="P15" s="15" t="n">
-        <v>-0.427</v>
+        <v>-0.08</v>
       </c>
       <c r="Q15" s="15" t="n">
         <v>1</v>
@@ -2623,7 +2623,7 @@
         <v>0.116</v>
       </c>
       <c r="Q16" s="15" t="n">
-        <v>-0.074</v>
+        <v>-0.068</v>
       </c>
       <c r="R16" s="15" t="n">
         <v>1</v>
@@ -2639,55 +2639,55 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>4.49</v>
+        <v>4.486</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
       <c r="D17" s="15" t="n">
         <v>0.85</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>-0.056</v>
+        <v>-0.052</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>0.024</v>
+        <v>0.032</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>-0.129</v>
+        <v>-0.125</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>0.095</v>
+        <v>0.096</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-0.042</v>
+        <v>-0.034</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>-0.03</v>
+        <v>-0.029</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>-0.022</v>
+        <v>-0.045</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>-0.158</v>
+        <v>-0.241</v>
       </c>
       <c r="M17" s="15" t="n">
-        <v>0.213</v>
+        <v>0.27</v>
       </c>
       <c r="N17" s="15" t="n">
-        <v>-0.056</v>
+        <v>-0.047</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>-0.038</v>
+        <v>-0.026</v>
       </c>
       <c r="P17" s="15" t="n">
-        <v>0.482</v>
+        <v>0.494</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>-0.407</v>
+        <v>-0.42</v>
       </c>
       <c r="R17" s="15" t="n">
-        <v>0.389</v>
+        <v>0.39</v>
       </c>
       <c r="S17" s="15" t="n">
         <v>1</v>
@@ -2702,58 +2702,58 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>4.628</v>
+        <v>4.631</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>1.192</v>
+        <v>1.191</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>0.079</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>0.046</v>
+        <v>0.051</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-0.027</v>
+        <v>-0.007</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>0.115</v>
+        <v>0.092</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>-0.007</v>
+        <v>-0.021</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>-0.192</v>
+        <v>-0.268</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>0.113</v>
+        <v>0.182</v>
       </c>
       <c r="N18" s="15" t="n">
-        <v>-0.066</v>
+        <v>-0.055</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>-0.018</v>
+        <v>-0.005</v>
       </c>
       <c r="P18" s="15" t="n">
         <v>0.396</v>
       </c>
       <c r="Q18" s="15" t="n">
-        <v>-0.319</v>
+        <v>-0.318</v>
       </c>
       <c r="R18" s="15" t="n">
-        <v>0.03</v>
+        <v>-0.001</v>
       </c>
       <c r="S18" s="15" t="n">
-        <v>0.284</v>
+        <v>0.283</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>1</v>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>2.652</v>
+        <v>2.653</v>
       </c>
       <c r="C19" s="15" t="n">
         <v>0.993</v>
@@ -2776,49 +2776,49 @@
         <v>0.78</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>-0.057</v>
+        <v>-0.054</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>-0.019</v>
+        <v>-0.032</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>-0.037</v>
+        <v>-0.04</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>0.117</v>
+        <v>0.127</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-0.03</v>
+        <v>-0.034</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>-0.047</v>
+        <v>-0.022</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>-0.025</v>
+        <v>-0.026</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>0.195</v>
+        <v>0.251</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>-0.119</v>
+        <v>-0.184</v>
       </c>
       <c r="N19" s="15" t="n">
-        <v>0.107</v>
+        <v>0.1</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>0.019</v>
+        <v>0.013</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>-0.357</v>
+        <v>-0.361</v>
       </c>
       <c r="Q19" s="15" t="n">
-        <v>0.331</v>
+        <v>0.323</v>
       </c>
       <c r="R19" s="15" t="n">
-        <v>-0.066</v>
+        <v>-0.038</v>
       </c>
       <c r="S19" s="15" t="n">
-        <v>-0.267</v>
+        <v>-0.268</v>
       </c>
       <c r="T19" s="15" t="n">
         <v>-0.361</v>
@@ -2963,14 +2963,14 @@
         </is>
       </c>
       <c r="C6" s="15" t="n">
-        <v>0.571</v>
+        <v>0.588</v>
       </c>
       <c r="D6" s="15" t="n">
-        <v>0.061</v>
+        <v>0.058</v>
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>[0.451, 0.690]</t>
+          <t>[0.473, 0.702]</t>
         </is>
       </c>
       <c r="F6" s="15" t="inlineStr">
@@ -2991,14 +2991,14 @@
         </is>
       </c>
       <c r="C7" s="15" t="n">
-        <v>-0.402</v>
+        <v>-0.385</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>0.057</v>
+        <v>0.054</v>
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>[-0.513, -0.291]</t>
+          <t>[-0.492, -0.279]</t>
         </is>
       </c>
       <c r="F7" s="15" t="inlineStr">
@@ -3031,14 +3031,14 @@
         </is>
       </c>
       <c r="C9" s="15" t="n">
-        <v>0.199</v>
+        <v>0.249</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>0.034</v>
+        <v>0.037</v>
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>[0.132, 0.266]</t>
+          <t>[0.175, 0.322]</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
@@ -3059,14 +3059,14 @@
         </is>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.284</v>
+        <v>0.319</v>
       </c>
       <c r="D10" s="15" t="n">
-        <v>0.052</v>
+        <v>0.057</v>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>[0.182, 0.386]</t>
+          <t>[0.206, 0.431]</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
@@ -3087,14 +3087,14 @@
         </is>
       </c>
       <c r="C11" s="15" t="n">
-        <v>-0.212</v>
+        <v>-0.282</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>0.046</v>
+        <v>0.052</v>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>[-0.303, -0.121]</t>
+          <t>[-0.383, -0.181]</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
@@ -3115,14 +3115,14 @@
         </is>
       </c>
       <c r="C12" s="15" t="n">
-        <v>-0.137</v>
+        <v>-0.222</v>
       </c>
       <c r="D12" s="15" t="n">
-        <v>0.035</v>
+        <v>0.041</v>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>[-0.206, -0.068]</t>
+          <t>[-0.301, -0.142]</t>
         </is>
       </c>
       <c r="F12" s="15" t="inlineStr">
@@ -3143,14 +3143,14 @@
         </is>
       </c>
       <c r="C13" s="15" t="n">
-        <v>-0.17</v>
+        <v>-0.257</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>0.055</v>
+        <v>0.064</v>
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>[-0.278, -0.063]</t>
+          <t>[-0.383, -0.131]</t>
         </is>
       </c>
       <c r="F13" s="15" t="inlineStr">
@@ -3171,14 +3171,14 @@
         </is>
       </c>
       <c r="C14" s="15" t="n">
-        <v>0.184</v>
+        <v>0.268</v>
       </c>
       <c r="D14" s="15" t="n">
-        <v>0.049</v>
+        <v>0.057</v>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>[0.088, 0.279]</t>
+          <t>[0.155, 0.380]</t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
@@ -3211,14 +3211,14 @@
         </is>
       </c>
       <c r="C16" s="15" t="n">
-        <v>-0.011</v>
+        <v>-0.008</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>0.047</v>
+        <v>0.052</v>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>[-0.104, 0.081]</t>
+          <t>[-0.111, 0.095]</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
@@ -3239,14 +3239,14 @@
         </is>
       </c>
       <c r="C17" s="15" t="n">
-        <v>0.051</v>
+        <v>0.046</v>
       </c>
       <c r="D17" s="15" t="n">
-        <v>0.043</v>
+        <v>0.046</v>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>[-0.033, 0.136]</t>
+          <t>[-0.045, 0.136]</t>
         </is>
       </c>
       <c r="F17" s="15" t="inlineStr">
@@ -3267,14 +3267,14 @@
         </is>
       </c>
       <c r="C18" s="15" t="n">
-        <v>-0.066</v>
+        <v>-0.089</v>
       </c>
       <c r="D18" s="15" t="n">
-        <v>0.078</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>[-0.220, 0.087]</t>
+          <t>[-0.261, 0.082]</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
@@ -3295,14 +3295,14 @@
         </is>
       </c>
       <c r="C19" s="15" t="n">
-        <v>-0.028</v>
+        <v>0.006</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.078</v>
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>[-0.168, 0.113]</t>
+          <t>[-0.146, 0.158]</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
@@ -3323,14 +3323,14 @@
         </is>
       </c>
       <c r="C20" s="15" t="n">
-        <v>0.002</v>
+        <v>-0.021</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.077</v>
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>[-0.133, 0.136]</t>
+          <t>[-0.173, 0.130]</t>
         </is>
       </c>
       <c r="F20" s="15" t="inlineStr">
@@ -3351,14 +3351,14 @@
         </is>
       </c>
       <c r="C21" s="15" t="n">
-        <v>0.02</v>
+        <v>0.029</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>0.063</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>[-0.103, 0.143]</t>
+          <t>[-0.106, 0.163]</t>
         </is>
       </c>
       <c r="F21" s="15" t="inlineStr">
@@ -3391,14 +3391,14 @@
         </is>
       </c>
       <c r="C23" s="15" t="n">
-        <v>0.412</v>
+        <v>0.392</v>
       </c>
       <c r="D23" s="15" t="n">
-        <v>0.053</v>
+        <v>0.051</v>
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>[0.308, 0.516]</t>
+          <t>[0.293, 0.491]</t>
         </is>
       </c>
       <c r="F23" s="15" t="inlineStr">
@@ -3447,14 +3447,14 @@
         </is>
       </c>
       <c r="C25" s="15" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="D25" s="15" t="n">
         <v>0.056</v>
       </c>
-      <c r="D25" s="15" t="n">
-        <v>0.058</v>
-      </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>[-0.057, 0.170]</t>
+          <t>[-0.113, 0.105]</t>
         </is>
       </c>
       <c r="F25" s="15" t="inlineStr">

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -3031,14 +3031,14 @@
         </is>
       </c>
       <c r="C9" s="15" t="n">
-        <v>0.249</v>
+        <v>0.239</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>0.037</v>
+        <v>0.036</v>
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>[0.175, 0.322]</t>
+          <t>[0.168, 0.310]</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
@@ -3059,14 +3059,14 @@
         </is>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.319</v>
+        <v>0.3</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0.057</v>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>[0.206, 0.431]</t>
+          <t>[0.188, 0.411]</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
@@ -3087,14 +3087,14 @@
         </is>
       </c>
       <c r="C11" s="15" t="n">
-        <v>-0.282</v>
+        <v>-0.264</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>[-0.383, -0.181]</t>
+          <t>[-0.364, -0.164]</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
@@ -3115,14 +3115,14 @@
         </is>
       </c>
       <c r="C12" s="15" t="n">
-        <v>-0.222</v>
+        <v>-0.219</v>
       </c>
       <c r="D12" s="15" t="n">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>[-0.301, -0.142]</t>
+          <t>[-0.303, -0.136]</t>
         </is>
       </c>
       <c r="F12" s="15" t="inlineStr">
@@ -3143,14 +3143,14 @@
         </is>
       </c>
       <c r="C13" s="15" t="n">
-        <v>-0.257</v>
+        <v>-0.252</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>0.064</v>
+        <v>0.065</v>
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>[-0.383, -0.131]</t>
+          <t>[-0.379, -0.124]</t>
         </is>
       </c>
       <c r="F13" s="15" t="inlineStr">
@@ -3171,14 +3171,14 @@
         </is>
       </c>
       <c r="C14" s="15" t="n">
-        <v>0.268</v>
+        <v>0.262</v>
       </c>
       <c r="D14" s="15" t="n">
-        <v>0.057</v>
+        <v>0.058</v>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>[0.155, 0.380]</t>
+          <t>[0.148, 0.377]</t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
@@ -3211,14 +3211,14 @@
         </is>
       </c>
       <c r="C16" s="15" t="n">
-        <v>-0.008</v>
+        <v>-0.018</v>
       </c>
       <c r="D16" s="15" t="n">
         <v>0.052</v>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>[-0.111, 0.095]</t>
+          <t>[-0.119, 0.084]</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
@@ -3239,14 +3239,14 @@
         </is>
       </c>
       <c r="C17" s="15" t="n">
-        <v>0.046</v>
+        <v>0.052</v>
       </c>
       <c r="D17" s="15" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>[-0.045, 0.136]</t>
+          <t>[-0.036, 0.141]</t>
         </is>
       </c>
       <c r="F17" s="15" t="inlineStr">
@@ -3267,14 +3267,14 @@
         </is>
       </c>
       <c r="C18" s="15" t="n">
-        <v>-0.089</v>
+        <v>-0.105</v>
       </c>
       <c r="D18" s="15" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>[-0.261, 0.082]</t>
+          <t>[-0.277, 0.066]</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
@@ -3295,14 +3295,14 @@
         </is>
       </c>
       <c r="C19" s="15" t="n">
-        <v>0.006</v>
+        <v>0.018</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>0.078</v>
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>[-0.146, 0.158]</t>
+          <t>[-0.135, 0.170]</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
@@ -3323,14 +3323,14 @@
         </is>
       </c>
       <c r="C20" s="15" t="n">
-        <v>-0.021</v>
+        <v>-0.007</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>0.077</v>
+        <v>0.078</v>
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>[-0.173, 0.130]</t>
+          <t>[-0.159, 0.145]</t>
         </is>
       </c>
       <c r="F20" s="15" t="inlineStr">
@@ -3351,14 +3351,14 @@
         </is>
       </c>
       <c r="C21" s="15" t="n">
-        <v>0.029</v>
+        <v>0.018</v>
       </c>
       <c r="D21" s="15" t="n">
         <v>0.06900000000000001</v>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>[-0.106, 0.163]</t>
+          <t>[-0.116, 0.153]</t>
         </is>
       </c>
       <c r="F21" s="15" t="inlineStr">
@@ -3391,14 +3391,14 @@
         </is>
       </c>
       <c r="C23" s="15" t="n">
-        <v>0.392</v>
+        <v>0.39</v>
       </c>
       <c r="D23" s="15" t="n">
-        <v>0.051</v>
+        <v>0.048</v>
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>[0.293, 0.491]</t>
+          <t>[0.295, 0.485]</t>
         </is>
       </c>
       <c r="F23" s="15" t="inlineStr">

--- a/results/主模型结果填答表.xlsx
+++ b/results/主模型结果填答表.xlsx
@@ -2639,55 +2639,55 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>4.486</v>
+        <v>4.493</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>0.78</v>
+        <v>0.789</v>
       </c>
       <c r="D17" s="15" t="n">
         <v>0.85</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>-0.052</v>
+        <v>-0.098</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>0.032</v>
+        <v>0.018</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>-0.125</v>
+        <v>-0.14</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>0.096</v>
+        <v>0.104</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-0.034</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>-0.029</v>
+        <v>-0.033</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>-0.045</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>-0.241</v>
+        <v>-0.121</v>
       </c>
       <c r="M17" s="15" t="n">
-        <v>0.27</v>
+        <v>0.154</v>
       </c>
       <c r="N17" s="15" t="n">
-        <v>-0.047</v>
+        <v>-0.017</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>-0.026</v>
+        <v>0.013</v>
       </c>
       <c r="P17" s="15" t="n">
-        <v>0.494</v>
+        <v>0.187</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <v>-0.42</v>
+        <v>-0.249</v>
       </c>
       <c r="R17" s="15" t="n">
-        <v>0.39</v>
+        <v>0.134</v>
       </c>
       <c r="S17" s="15" t="n">
         <v>1</v>
@@ -2702,58 +2702,58 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>4.631</v>
+        <v>4.627</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>1.191</v>
+        <v>1.192</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>0.86</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.039</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>0.051</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>0.007</v>
+        <v>-0.031</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-0.007</v>
+        <v>-0.022</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.017</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>0.092</v>
+        <v>0.116</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>-0.021</v>
+        <v>0</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>-0.268</v>
+        <v>-0.096</v>
       </c>
       <c r="M18" s="15" t="n">
-        <v>0.182</v>
+        <v>-0.004</v>
       </c>
       <c r="N18" s="15" t="n">
-        <v>-0.055</v>
+        <v>-0.063</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>-0.005</v>
+        <v>0.026</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0.396</v>
+        <v>0.099</v>
       </c>
       <c r="Q18" s="15" t="n">
-        <v>-0.318</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R18" s="15" t="n">
         <v>-0.001</v>
       </c>
       <c r="S18" s="15" t="n">
-        <v>0.283</v>
+        <v>0.284</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>1</v>
@@ -2767,61 +2767,61 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>2.653</v>
+        <v>2.658</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>0.993</v>
+        <v>0.998</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>0.78</v>
       </c>
       <c r="E19" s="15" t="n">
+        <v>-0.063</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="G19" s="15" t="n">
+        <v>-0.022</v>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>-0.032</v>
+      </c>
+      <c r="J19" s="15" t="n">
         <v>-0.054</v>
       </c>
-      <c r="F19" s="15" t="n">
-        <v>-0.032</v>
-      </c>
-      <c r="G19" s="15" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="H19" s="15" t="n">
-        <v>0.127</v>
-      </c>
-      <c r="I19" s="15" t="n">
-        <v>-0.034</v>
-      </c>
-      <c r="J19" s="15" t="n">
-        <v>-0.022</v>
-      </c>
       <c r="K19" s="15" t="n">
-        <v>-0.026</v>
+        <v>-0.025</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>0.251</v>
+        <v>0.156</v>
       </c>
       <c r="M19" s="15" t="n">
-        <v>-0.184</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="N19" s="15" t="n">
-        <v>0.1</v>
+        <v>0.103</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>-0.361</v>
+        <v>-0.359</v>
       </c>
       <c r="Q19" s="15" t="n">
-        <v>0.323</v>
+        <v>0.068</v>
       </c>
       <c r="R19" s="15" t="n">
-        <v>-0.038</v>
+        <v>-0.074</v>
       </c>
       <c r="S19" s="15" t="n">
-        <v>-0.268</v>
+        <v>-0.267</v>
       </c>
       <c r="T19" s="15" t="n">
-        <v>-0.361</v>
+        <v>-0.354</v>
       </c>
       <c r="U19" s="15" t="n">
         <v>1</v>
@@ -3031,14 +3031,14 @@
         </is>
       </c>
       <c r="C9" s="15" t="n">
-        <v>0.239</v>
+        <v>0.09</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>0.036</v>
+        <v>0.044</v>
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>[0.168, 0.310]</t>
+          <t>[0.003, 0.177]</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
@@ -3059,14 +3059,14 @@
         </is>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.3</v>
+        <v>0.053</v>
       </c>
       <c r="D10" s="15" t="n">
-        <v>0.057</v>
+        <v>0.064</v>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>[0.188, 0.411]</t>
+          <t>[-0.071, 0.178]</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
@@ -3087,14 +3087,14 @@
         </is>
       </c>
       <c r="C11" s="15" t="n">
-        <v>-0.264</v>
+        <v>-0.28</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>0.051</v>
+        <v>0.053</v>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>[-0.364, -0.164]</t>
+          <t>[-0.384, -0.176]</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
@@ -3115,14 +3115,14 @@
         </is>
       </c>
       <c r="C12" s="15" t="n">
-        <v>-0.219</v>
+        <v>-0.122</v>
       </c>
       <c r="D12" s="15" t="n">
-        <v>0.042</v>
+        <v>0.054</v>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>[-0.303, -0.136]</t>
+          <t>[-0.229, -0.016]</t>
         </is>
       </c>
       <c r="F12" s="15" t="inlineStr">
@@ -3143,14 +3143,14 @@
         </is>
       </c>
       <c r="C13" s="15" t="n">
-        <v>-0.252</v>
+        <v>-0.034</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>0.065</v>
+        <v>0.075</v>
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>[-0.379, -0.124]</t>
+          <t>[-0.180, 0.113]</t>
         </is>
       </c>
       <c r="F13" s="15" t="inlineStr">
@@ -3171,14 +3171,14 @@
         </is>
       </c>
       <c r="C14" s="15" t="n">
-        <v>0.262</v>
+        <v>0.04</v>
       </c>
       <c r="D14" s="15" t="n">
-        <v>0.058</v>
+        <v>0.061</v>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>[0.148, 0.377]</t>
+          <t>[-0.079, 0.160]</t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
@@ -3211,14 +3211,14 @@
         </is>
       </c>
       <c r="C16" s="15" t="n">
-        <v>-0.018</v>
+        <v>-0.014</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>0.052</v>
+        <v>0.066</v>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>[-0.119, 0.084]</t>
+          <t>[-0.142, 0.115]</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
@@ -3242,11 +3242,11 @@
         <v>0.052</v>
       </c>
       <c r="D17" s="15" t="n">
-        <v>0.045</v>
+        <v>0.057</v>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>[-0.036, 0.141]</t>
+          <t>[-0.060, 0.165]</t>
         </is>
       </c>
       <c r="F17" s="15" t="inlineStr">
@@ -3267,14 +3267,14 @@
         </is>
       </c>
       <c r="C18" s="15" t="n">
-        <v>-0.105</v>
+        <v>-0.111</v>
       </c>
       <c r="D18" s="15" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>[-0.277, 0.066]</t>
+          <t>[-0.306, 0.084]</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
@@ -3295,14 +3295,14 @@
         </is>
       </c>
       <c r="C19" s="15" t="n">
-        <v>0.018</v>
+        <v>-0.02</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>0.078</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>[-0.135, 0.170]</t>
+          <t>[-0.193, 0.154]</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
@@ -3323,14 +3323,14 @@
         </is>
       </c>
       <c r="C20" s="15" t="n">
-        <v>-0.007</v>
+        <v>0.008</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>0.078</v>
+        <v>0.081</v>
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>[-0.159, 0.145]</t>
+          <t>[-0.151, 0.167]</t>
         </is>
       </c>
       <c r="F20" s="15" t="inlineStr">
@@ -3351,14 +3351,14 @@
         </is>
       </c>
       <c r="C21" s="15" t="n">
-        <v>0.018</v>
+        <v>0.022</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>[-0.116, 0.153]</t>
+          <t>[-0.119, 0.162]</t>
         </is>
       </c>
       <c r="F21" s="15" t="inlineStr">
@@ -3391,14 +3391,14 @@
         </is>
       </c>
       <c r="C23" s="15" t="n">
-        <v>0.39</v>
+        <v>0.142</v>
       </c>
       <c r="D23" s="15" t="n">
-        <v>0.048</v>
+        <v>0.061</v>
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>[0.295, 0.485]</t>
+          <t>[0.023, 0.262]</t>
         </is>
       </c>
       <c r="F23" s="15" t="inlineStr">
